--- a/EU_Delegation_Lebanon.xlsx
+++ b/EU_Delegation_Lebanon.xlsx
@@ -12283,7 +12283,6 @@
           <t>https://www.eeas.europa.eu/delegations/lebanon/imagine-europe-digital-creative-contest-celebration-europe-day-2021-lebanon_en?s=203</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12329,7 +12328,6 @@
           <t>https://www.eeas.europa.eu/delegations/lebanon/first-consultative-group-meeting-reform-recovery-and-reconstruction-framework_en?s=203</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12375,7 +12373,6 @@
           <t>https://www.eeas.europa.eu/eeas/foreign-affairs-council-remarks-high-representativevice-president-josep-borrell-press-conference-1_en?s=203</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12489,7 +12486,6 @@
           <t>https://www.eeas.europa.eu/eeas/world-water-day-joint-statement-high-representativevice-president-josep-borrell-and-commissioner-1_en?s=203</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12566,7 +12562,6 @@
           <t>https://www.eeas.europa.eu/eeas/world-ngo-day-statement-high-representativevice-president-josep-borrell-1_en?s=203</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12640,7 +12635,6 @@
           <t>https://www.eeas.europa.eu/eeas/international-day-against-use-child-soldiers-joint-statement-hrvp-josep-borrell-and-un-special_en?s=203</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12686,7 +12680,6 @@
           <t>https://www.eeas.europa.eu/eeas/renewed-partnership-southern-neighbourhood-new-agenda-mediterranean_en?s=203</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12732,7 +12725,6 @@
           <t>https://www.eeas.europa.eu/eeas/european-union-host-brussels-v-conference-syria-0_en?s=203</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12810,7 +12802,6 @@
           <t>https://www.eeas.europa.eu/delegations/lebanon/tarraf-%C3%A0-%C2%AB-l%E2%80%99orient-le-jour-%C2%BB-nous-sommes-soucieux-de-la-situation-s%C3%A9curitaire-au-liban_und_en?s=203</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12887,7 +12878,6 @@
           <t>https://www.eeas.europa.eu/eeas/gcc-statement-high-representative-josep-borrell-normalisation-relations-among-gulf-countries_en?s=203</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -12933,7 +12923,6 @@
           <t>https://www.eeas.europa.eu/delegations/lebanon/help-helping-hands_en?s=203</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -13078,7 +13067,6 @@
           <t>https://www.eeas.europa.eu/eeas/eu-reaffirms-its-commitment-strengthen-relations-its-partners-southern-neighbourhood_en?s=203</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -13124,7 +13112,6 @@
           <t>https://www.eeas.europa.eu/delegations/lebanon/eu-un-and-wbg-launch-18-month-reform-recovery-and-reconstruction-framework-response-beirut-port_en?s=203</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.
@@ -13264,7 +13251,6 @@
           <t>https://www.eeas.europa.eu/delegations/lebanon/statement-international-support-group-lebanon-0_en?s=203</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>Извиняваме се за неудобството. Моля, опитайте пак по-късно.

--- a/EU_Delegation_Lebanon.xlsx
+++ b/EU_Delegation_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13285,6 +13285,1498 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>UN Country Team in Mongolia: Statement on Proposed Amendments to the Law on National Naadam Festival Concerning Child Jockeys</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/mongolia/un-country-team-mongolia-statement-proposed-amendments-law-national-naadam-festival-concerning-child_en</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>UN Country Team in Mongolia: Statement on Proposed Amendments to the Law on National Naadam Festival Concerning Child Jockeys
+The United Nations Country Team (UNCT) in Mongolia expresses its concern regarding the proposed amendments to the Law on National Naadam that would permit children aged 14 to 17 to participate as jockeys in spring horse racing. While the UNCT fully recognizes horse racing as an important element of Mongolia’s cultural heritage and national identity, cultural traditions must continue to evolve in ways that uphold the human rights, dignity and best interests of all children.
+The proposed amendments would authorize children to participate in long-distance horse races held during or immediately after the Lunar New Year period, when severe winter conditions often persist across much of the country. These circumstances expose children to significant risks associated with high-speed racing over extended distances in extreme cold, snow, ice and difficult terrain. Such risks include serious injury, disability and loss of life, as documented by incidents and national data on child jockey accidents in recent years. Evidence indicates that hundreds of children have been injured in horse racing-related activities, while fatalities and permanent disabilities continue to occur despite the introduction of safety measures and protective equipment.
+The UNCT notes the efforts made in the draft legislation to enhance safety through protective gear, insurance coverage and medical support. However, the central concern is not solely the adequacy of protective measures, but the continued involvement of children in an activity recognized internationally as hazardous by its nature. The ILO Committee of Experts on the Application of Conventions and Recommendations has repeatedly called upon Mongolia to ensure that no person under the age of 18 is engaged as a horse jockey, consistent with the principles and obligations of ILO Convention No. 182 on the Worst forms of child labour.
+Raising the minimum age from childhood to 14 years does not address this underlying concern, as children aged 14 to 17 remain entitled to protection from hazardous work under international law.
+Beyond the immediate physical risks, the participation of children in horse racing may adversely affect their education, development and future opportunities. Available data indicates that large numbers of children continue to be engaged as jockeys, often resulting in prolonged absences from school and reduced educational attainment. Protecting children from hazardous activities is therefore not only a matter of safety, but also of safeguarding their long-term development and well-being.
+The UNCT recalls the important progress Mongolia has made in recent years to strengthen child protection and restrict the participation of child jockeys in winter and spring horse racing. These measures have represented positive steps toward implementing Mongolia’s commitments under the Convention on the Rights of the Child and relevant ILO conventions. Preserving this progress is essential to ensuring that Mongolia’s rich cultural heritage continues to be celebrated in a manner consistent with international human rights standards and the best interests of the child.
+The UNCT therefore respectfully encourages the State Great Khural of Mongolia to ensure that any amendments to the Law on National Naadam fully uphold the best interests of the child and remain consistent with Mongolia’s national and international commitments on child protection. The UNCT remains ready to support continued dialogue and evidence-based solutions that safeguard both Mongolia's valued traditions and the rights, safety and well-being of every child.
+About United Nations
+The United Nations is an international organization founded in 1945. Currently made up of 193 Member States, the UN and its work are guided by the purposes and principles contained in its founding Charter.</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:10:56.607097+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Honduras inicia las pruebas de legalidad del sector forestal, un paso concreto en la aplicación del AVA FLEGT con la Unión Europea</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/honduras/honduras-inicia-las-pruebas-de-legalidad-del-sector-forestal-un-paso-concreto-en-la-aplicacion-del_en</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Honduras inicia las pruebas de legalidad del sector forestal, un paso concreto en la aplicación del AVA FLEGT con la Unión Europea
+Tegucigalpa, Honduras, 23 de octubre de 2026.
+En el marco del Acuerdo Voluntario de Asociación (AVA FLEGT) entre Honduras y la Unión Europea, el Instituto Nacional de Conservación y Desarrollo Forestal, Áreas Protegidas y Vida Silvestre (ICF) y la Unión Europea lanzaron oficialmente las Pruebas de Legalidad del Sector Forestal. Esta intervención técnica es implementada por BFConsult, con financiamiento de la Unión Europea a través de la Agencia Francesa de Desarrollo (AFD).
+El taller de lanzamiento reunió a representantes del ICF, la Delegación de la Unión Europea, la AFD, gremios del sector privado forestal, la Secretaría Técnica del AVA FLEGT (SETAVA) y organizaciones de la sociedad civil.
+Un acuerdo de país que pasa del papel al terreno
+El AVA FLEGT fue negociado durante ocho años y firmado al más alto nivel en 2021. Tras su ratificación por el Congreso Nacional de Honduras y el Parlamento Europeo, hoy es un compromiso de Estado, con fuerza de ley, que trasciende a las personas y a los gobiernos.
+Las pruebas de legalidad son una muestra concreta de que el AVA FLEGT avanza en Honduras y de que la lucha contra la ilegalidad forestal sale del papel para convertirse en una realidad en el terreno.
+¿En qué consisten las pruebas de legalidad?
+Las pruebas medirán el nivel de legalidad con el que trabajan los operadores forestales, tomando como referencia las tablas de legalidad establecidas en el Anexo 2 del AVA FLEGT. En total, se evaluarán 6 principios, 17 criterios y 56 medios de verificación, en más de 20 categorías de operadores (aprovechamiento, transformación, comercialización e importación/exportación).
+Gracias a este ejercicio, Honduras y la Unión Europea contarán con una fotografía real del nivel de legalidad del sector. Sus resultados permitirán:
+- Identificar brechas: conocer con precisión dónde están los principales desafíos de cumplimiento, antes de la entrada en vigor obligatoria del Sistema de Aseguramiento de la Legalidad de Honduras (SALH).
+- Definir el apoyo que necesitan los operadores: orientar las medidas concretas de acompañamiento para que cada operador avance, paso a paso, hacia la plena legalidad.
+- Simplificar la gestión forestal: distinguir entre las limitaciones propias de las empresas y los cuellos de botella en los trámites e instituciones públicas.
+- Garantizar derechos: verificar el respeto de los derechos de las comunidades locales, los pueblos indígenas y afrodescendientes en la cadena de suministro.
+Metodología y cobertura
+El plan de trabajo consta de cuatro fases, que incluyen análisis documental, pruebas de auditoría en sitio y talleres de validación. Las verificaciones de campo abarcarán las principales zonas productivas del país, entre ellas Atlántida, Comayagua, Francisco Morazán, Olancho y Yoro.
+Las visitas de campo a las empresas del sector forestal privado comenzaron el 12 de octubre en La Ceiba, Atlántida, y continúan en paralelo en Guaimaca, Francisco Morazán, durante los próximos 2 meses. Estas pruebas de auditoría en sitio permiten verificar cómo se aplican las tablas de legalidad del AVA FLEGT en las operaciones de cada empresa, identificar brechas de cumplimiento y determinar qué medidas de acompañamiento necesita el sector para avanzar hacia la plena legalidad, previo a la entrada en vigor obligatoria del Sistema de Aseguramiento de la Legalidad de Honduras (SALH).
+El Acuerdo Voluntario de Asociación sobre la aplicación de las leyes, la gobernanza y el comercio forestales (AVA FLEGT) es un acuerdo comercial bilateral entre Honduras y la Unión Europea. Su objetivo es fortalecer la gobernanza forestal, combatir la tala ilegal y garantizar que la madera producida y comercializada por Honduras provenga de fuentes legales.</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:02.498856+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>MEPs push for continued engagement and concrete results on trade with China</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/china/meps-push-continued-engagement-and-concrete-results-trade-china_en</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>MEPs push for continued engagement and concrete results on trade with China
+(Original publication: link)
+Concluding the three-day visit, the Chair of the International Trade Committee (INTA) and head of the delegation Bernd Lange (S&amp;D, DE), said: “The world has drastically changed since our last visit to China in 2018. The opportunity to exchange viewpoints on the continuation of the Trade and Investment Consultation (TIC) framework has come at a pivotal moment in EU-China relations. The recent TIC agreement on hybrid car imports is a good starting point in stabilising fair trade and producing benefits for people on the ground. However, we made clear to our Chinese counterparts that we expect to see more sectors following the same approach in the future, alongside the credible implementation of existing commitments. This is important not only for improving trade relations, but also to strengthen economic and political ties between us. I also welcome the fruitful exchanges on increasing transparency on subsidies and supply chains.”
+Pascal Canfin (Renew, FR), INTA standing rapporteur for trade relations with China added: “It was important for the European Parliament to convey a sense of urgency during our mission, to stabilise and rebalance the EU-China trade relationship. Interdependence is at the heart of our relations; this is not necessarily a bad thing. However, the Chinese export model is simply not sustainable for the EU. Once we see an imbalance on one side, the EU can trigger measures. The EU’s strategy is based on dialogue, but we also need to see results. The TIC talks created momentum and produced concrete outcomes. We hope to continue in the same spirit and deliver more for our citizens on both sides, in the near future.”
+In their meetings with Chinese counterparts, the MEPs said increasing the frequency of dialogue between the EU and China is essential in building trust on both sides, and they stressed that neither side would benefit from a trade conflict. The INTA delegation used the opportunity to expand on their concerns related to the obstacles facing EU companies in China, unpredictable supply chains, access to critical raw materials, excess production capacity, as well as Chinese decrees negatively impacting foreign companies. MEPs discussed EU regulations currently in development and which are intended to strengthen EU industrial capacity. Strengthening the multilateral trade framework within the WTO was also discussed.
+Programme
+The delegation met with Wang Wentao, Minister of Commerce; Cai Dafeng and Li Hongzhong, Vice-Chairs of the National Party Congress (NPC) Standing Committee; and Zhong Shan, NPC Chairperson of Financial and Economic Affairs Committee. They exchanged views with the EU Chamber of Commerce on the growing barriers facing EU companies based in China. In Hangzhou, a major Chinese technology hub, the delegation visited robotics company Unitree, as well as neurotech company BrainCo. In Shanghai, the delegation met with Lu Shan, the city’s Vice-Mayor.
+Composition
+INTA chair Bernd Lange was the head of the delegation. He was accompanied by: Pascal Canfin, INTA standing rapporteur for China; Juan Ignacio Zoido Álvarez (EPP, ES); Kathleen Van Brempt (S&amp;D, BE); Enikő Győri (PfE, HU); Jaak Madison (ECR, ET); Markéta Gregorová (Greens/EFA, CS); Rudi Kennes (The Left, BE); Angelika Niebler (EPP, DE); Jörgen Warborn (EPP, SV); Brando Benifei (S&amp;D, IT); and Engin Eroglu (Renew, DE), chair of the Delegation for Relations with the People’s Republic of China.
+Context
+The INTA delegation was in Beijing, Hangzhou and Shanghai (China) from 27 to 29 October. This was the second time an INTA delegation has visited China, the last time was in 2018. This was the fourth delegation from the European Parliament to travel to China in 2026. The timing was also pivotal for EU-China trade relations, considering the recent agreement on curbing hybrid car exports.
+China is the EU's third largest trading partner for goods and services combined, while the EU is among China's top trading partners. The EU’s deficit with China has been growing steadily, recently reaching €1 billion a day. The EU’s economic relationship with China is perceived as unbalanced, due to a significant asymmetry in respective market openings.</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:08.284720+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Chair of the Working Group on the issue of human rights and transnational corporations and other business enterprises, Mr. Robert McCORQUODALE</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-chair-working-group-issue-human_en</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Chair of the Working Group on the issue of human rights and transnational corporations and other business enterprises, Mr. Robert McCORQUODALE
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States.
+We thank the UN Working Group on Business and Human Rights for its report on the responsibilities of directors and senior executives in large companies. We also thank the Working Group for organising the first Forum on Business and Human Rights for Western Europe, held in Strasbourg in September, as well as the Annual Forum and the regional forums, which remain important multistakeholder spaces to sustain momentum and exchange on practical implementation.
+As we mark the 15th anniversary of the UN Guiding Principles and 50 years since the endorsement of the OECD Guidelines for Multinational Enterprises, the EU reaffirms its strong commitment to ensuring that business activity goes hand in hand with respect for human rights, including labour rights, and environmental protection.
+The EU and its Member States will continue to step up efforts to uphold international law and human rights, including through our trade relations and development cooperation, with particular attention to persons in vulnerable situations.
+We recognise the profound impact that corporate activities can have on individuals and remain committed to ensuring that companies uphold their responsibility to respect human rights. In this regard, EU legislation on corporate sustainability due diligence and on combating forced labour provides an important basis for supporting these efforts and advancing responsible business conduct.
+We will continue to promote the effective implementation of the UN Guiding Principles on Business and Human Rights, including the ILO’s Fundamental Principles and Rights at Work. We also reaffirm our support for the UN Working Group and remain constructively engaged in discussions towards a consensus-based global instrument on business and human rights.
+Mr. McCorouodale,
+Could you share further reflections on the Working Group’s cooperation across the United Nations system, including with the specialised agencies? Where do you see scope for further improvement and how can Member States contribute to enhancing synergies?</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:14.118219+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Special Rapporteur on the right to education, Ms. Farida SHAHEED</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-special-rapporteur-right_en</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Special Rapporteur on the right to education, Ms. Farida SHAHEED
+Chair,
+The European Union welcomes the report of the Special Rapporteur on the right to education.
+The EU and its Member States reaffirm the right to education for all, without discrimination of any kind, and our commitment to achieving SDG 4.
+Your report addresses the impacts of the growing debt crisis, the prioritization of debt servicing and fiscal adjustment in limiting States’ ability to invest in essential public services, including in education, with unequal effects on marginalized groups.
+Sustained public financing is key to achieve free, equal, inclusive and quality education. The international financial architecture can shape States’ capacity to comply with their minimum core obligations under ICESCR, including the mobilization of maximum available resources and refraining from adopting regressive measures that undermine the realization of economic, social and cultural rights.
+The EU supports efforts to enhance debt transparency, responsible lending and borrowing, and effective debt relief mechanisms to enable long-term, rights-based development strategies. Strengthening tax systems, tackling illicit financial flows, and improving governance are also necessary to accelerate progress towards the SDGs. Moving beyond GDP is also essential to designing human rights economies, including through advancing the right to education.
+These efforts must be supported by effective, accountable and inclusive institutions and a global financial system that allows all countries to mobilise resources. Finally, the meaningful participation of youth on issues that directly concern them is key.
+The EU and its Member States remain the world’s largest official development assistance donor and the main investor in education worldwide, investing more than 10% of its International Partnerships budget, over 6 billion EUR, to education.
+Madam Special Rapporteur,
+What best practices can States, IFIs and the international community implement as priority measures to allow for adequate public financing to advance the right to education?</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:20.014905+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogues on climate change and the human right to a clean, healthy and sustainable environment</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogues-climate-change-and-human-right_en</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogues on climate change and the human right to a clean, healthy and sustainable environment
+Thank you, Chair.
+I have the honour to speak on behalf of the European Union and its Member States.
+We thank the Special Rapporteurs for their continued work and reaffirm our support for their mandates.
+As confirmed by the ICJ Advisory Opinion, the EU reaffirms that a clean, healthy and sustainable environment is inseparable from the enjoyment of all human rights. We promote a human rights-based approach to climate and environmental action, including to address biodiversity loss and pollution both on land and in water, with particular attention to those most exposed to harm. This process is guided by EU's binding objective to reaching climate neutrality by 2050.
+Madam Special Rapporteur Puentes Riano, we thank you for your report on the integration of human rights and environmental protection into planning from the outset. Long-term planetary stability and human well-being must be prioritised over short-term economic gains.
+For a fully just transition, the meaningful participation and full respect of the rights of Indigenous Peoples, as set out in UNDRIP, as well as on women and girls, future generations, persons with disabilities and people living in poverty, is of utmost importance.
+Madam Special Rapporteur Morgera, we thank you for your timely report on carbon credits. The EU maintains that credits cannot substitute for substantial and rapid domestic emissions reductions. Any use of credits must ensure environmental integrity, avoid double-counting and protect the rights of local communities. The EU also remains deeply concerned by threats against environmental human rights defenders, including through strategic lawsuits against public participation (SLAPPs).
+To Special Rapporteur Puentes Riaño:
+Which practical steps would you prioritise to overcome fragmented planning across sectors and levels of government, and ensure that the participation of affected communities leads to measurable improvements in their enjoyment of the right to a healthy environment?
+To Special Rapporteur Morgera:
+Your report calls upon States to determine under which specific conditions certain categories of carbon credit projects could genuinely protect the climate and human rights. How should this assessment be carried out in practice, and who should be involved, including affected communities?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:25.789884+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly: Report of the International Court of Justice</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-report-international-court-justice_en</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly: Report of the International Court of Justice
+– CHECK AGAINST DELIVERY –
+Señor Presidente
+Tengo el honor de intervenir en nombre de la Unión Europea y de sus Estados miembros.
+Los países candidatos —Macedonia del Norte*, Montenegro*, Albania*, Ucrania, la República de Moldavia, y Bosnia y Herzegovina* —así como, Mónaco y San Marino, se alinean con esta declaración.
+En primer lugar, permítame expresar mi agradecimiento a Su Excelencia el Presidente Iwasawa por la presentación ante la Asamblea General del informe sobre las actividades de la Corte Internacional de Justicia durante el período comprendido entre el 1 de agosto de 2025 y el 31 de julio de 2026.
+Señor Presidente:
+Quisiera comenzar recordando que este año la Corte celebra el 80.º aniversario de su primera sesión, que tuvo lugar en La Haya, en el Palacio de la Paz, el 3 de abril de 1946.
+Durante la sesión solemne conmemorativa del 80.º aniversario de la Corte, celebrada el 17 de abril de 2026, Su Excelencia el Sr. António Guterres, Secretario General de las Naciones Unidas, recordó que la creación de la Corte se ha guiado por una convicción fundamental:
+La fuerza del derecho debe prevalecer siempre sobre el derecho de la fuerza.
+Esta convicción constituye también el núcleo del compromiso de la Unión Europea con el Estado de Derecho, el respeto del derecho internacional y el arreglo pacífico de las controversias. Mediante este compromiso, la Unión procura garantizar que las relaciones internacionales sigan rigiéndose por el derecho y no por el ejercicio del poder.
+En este contexto, la concesión del Premio Nobel de la Paz de 2026 a Navi Pillay, «por sus esfuerzos para promover la paz y el derecho internacional», resulta especialmente oportuna. La Sra. Pillay ha dedicado su vida a la justicia, y su compromiso inquebrantable, su dedicación y su valentía constituyen una valiosa brújula para todos nosotros en estos tiempos difíciles.
+Permítanme expresar, en nombre de la Unión Europea y de sus Estados miembros, nuestras más calurosas felicitaciones a la profesora Phoebe Okowa por su elección como jueza de la Corte Internacional de Justicia, y al Sr. Santiago Villalpando por su elección como secretario de la Corte.
+Les deseamos a ambos el mayor de los éxitos en el desempeño de sus nuevas responsabilidades y esperamos con interés sus contribuciones a la labor de la Corte.
+Monsieur le Président,
+En tant qu’organe judiciaire principal des Nations Unies, la Cour occupe une place prééminente dans le règlement pacifique des différends au niveau international. En tranchant les différends entre États et en rendant des avis consultatifs, la Cour internationale de Justice contribue de manière significative, aux côtés des autres organes des Nations Unies, au maintien de la paix et de la sécurité internationales, ainsi qu’au développement de relations amicales et de la coopération entre les États. Bien entendu, la contribution de la Cour ne peut être pleinement efficace que si les États mettent en œuvre ses décisions. Nous rappelons que les ordonnances et les arrêts de la Cour ont un caractère obligatoire pour les parties au différend.
+L’augmentation significative du nombre d’affaires soumises à la Cour, portant sur une grande diversité de questions, témoigne du rôle crucial qu’elle joue dans le règlement pacifique des différends. Cette évolution n’a été possible que grâce au dévouement des juges ainsi qu’à leurs normes éthiques et professionnelles élevées. Elle témoigne également du haut degré de confiance que les États et les organes des Nations Unies accordent à la Cour. En plus, l’Union européenne salue la décision de l’Islande d’accepter la juridiction obligatoire de la Cour conformément au paragraphe 2 de l’article 36 de son Statut.
+Nous remercions le Président de la Cour, ses juges, le Greffier ainsi que l’ensemble du personnel de la Cour pour leur engagement sans faille au service de la justice internationale.
+Mr. President,
+The European Union takes note of Court’s latest advisory opinions. They provide important and authoritative clarifications on questions of international law submitted by authorized UN organs and agencies and encourage the continued pursuit by the international community of constructive dialogue. Advisory proceedings may also provide a distinct avenue for international organizations to participate in the proceedings before the Court.
+The European Union takes note of the Advisory Opinion delivered on 22 October 2025 on obligations of Israel in relation to the presence and Activities of the United Nations, Other International Organisations and third States in and in relation to the Occupied Palestinian Territory.
+The European Union considers that the role of the UN, international human rights law and international humanitarian law must be respected in all situations of armed conflict. The protection of civilians, medical personnel and facilities, as well as the facilitation of rapid and unimpeded humanitarian relief, are fundamental obligations under international law.
+UN personnel, entities, premises and operations must be protected and respected also in the context of armed conflict. These safeguards are indispensable to the UN’s ability to carry out its purpose.
+The European Union has taken further note of clarifications provided by the Opinion on the application of the general principle of co-operation with the UN under Article 2(5) of the Charter, and good-faith performance of Charter obligations provided for in Article 2(2) of the Charter.
+The European Union has also taken note of the Advisory Opinion delivered on 21 May 2026 concerning the right to strike under International Labour Convention No. 87 in which the Court concluded that the right to strike is protected under ILO Convention, as an essential component of workers’ freedom of association. The European Union fully respects the right to freedom of association and recognises its fundamental importance to a democratic society. The protection of the right to strike is encompassed in the protection of the right to collective action, under Article 28 of the Charter of Fundamental Rights of the EU to which freedom of association is inherent, as the Court noted in points 131-132 of its Opinion. The Union welcomes the comparative analysis of the various regional legal frameworks, including the European legal framework, which the Court has provided for in the Opinion.
+In May 2025, Lithuania, an EU Member State, initiated proceedings against Republic of Belarus for alleged breaches of obligations under the Protocol against the Smuggling of Migrants by Land, Sea and Air, supplementing the United Nations Convention against Transnational Organized Crime. As a party to the Protocol and the Convention, the European Union submitted on 20 July 2026 its observations on the construction of several provisions of the Protocol on the basis of Article 43, paragraph 2, of the Rules of Court. Let us stress that this is the first time that the European Union used this possibility provided for in the Rules of Court.
+Mr. President,
+The European Union courts refer repeatedly to the jurisprudence of the ICJ to interpret and apply international law within the Union’s legal order. Recently, the Court of Justice of the European Union (CJEU) referred to the Nottebohm judgment (Lichtenstein v. Guatemala) when interpreting the requirement of “prior genuine link” between an applicant and a State before nationality can be granted.A reference to the judgement delivered by the Court in the Barcelona Traction case appears in the opinion delivered by the Advocate General of the CJEU in relation to the exercise of diplomatic protection by a State. As mentioned before in the context of the Advisory Opinion concerning the right to strike, the Court also refers to regional case law, including that of the CJEU, when needed. These reciprocal references to each other’s case law illustrate the mutual interaction between international and regional courts in the interpretation and development of international law.
+Monsieur le Président,
+Permettez-moi de conclure.
+Alors que la Cour célèbre 80 années au service de la communauté internationale, l’Union européenne ne saurait trouver meilleure occasion pour réaffirmer l’importance primordiale qu’elle attache aux travaux de la Cour, ainsi que sa profonde reconnaissance pour la contribution de celle-ci au règlement pacifique des différends et à la clarification et au développement du droit international.
+Face à la multiplication et à la diversité des menaces qui pèsent sur la paix et la sécurité internationales, ainsi qu’aux violations généralisées de la Charte des Nations Unies et du droit international, le rôle de la Cour internationale de Justice, son indépendance et son autorité n’ont jamais revêtu une importance aussi grande.
+Je vous remercie.
+- Points 120-132 of the Advisory Opinion
+- Case C-181/23, Commission v. Malta, judgement of 29 Aril 2026, point 71.
+- Case C-819/25PPU, Opinion of AG Norkus of 5 March 2026, paragraph 63, footnote 54.</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:31.701658+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>EU Statement – UN Security Council: Emerging Technologies and Maritime Security</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-security-council-emerging-technologies-and-maritime-security_en</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>EU Statement – UN Security Council: Emerging Technologies and Maritime Security
+Mr. President,
+I have the honour to speak on behalf of the European Union and its Member States.
+The Candidate Countries North Macedonia, Montenegro*, Albania*, Ukraine, the Republic of Moldova, Bosnia and Herzegovina* and Georgia, as well as San Marino align themselves with this statement.
+We commend the Greek Presidency for bringing this vital debate to the Security Council and we can only share their assessment of the urgency of addressing the topic.
+The threat environment at sea is evolving quickly. The proliferation and misuse of autonomous and uncrewed systems — aerial, surface, and submarine — enable State and non-State actors to disrupt freedom of navigation, target commercial shipping, subsea cables, and pipelines, and hold global supply chains hostage. Increasing digitalization introduces acute cyber-vulnerabilities to port operations and critical undersea infrastructure. Incidents affecting maritime infrastructure can also have serious consequences for the marine environment and coastal communities. These tech-driven disruptions directly threaten international economic stability, energy and food security. They also endanger the life and safety of innocent seafarers, who must remain at the centre of our protection efforts. We cannot accept a reality where new technologies are used to bully, intimidate, or disrupt the global commons and to imperil human life and undermine the protection of civilians.
+Conversely, innovation can be harnessed to protect the global order. When used responsibly, advanced surveillance, AI, drones, advanced sensor and data sharing act as powerful tools for security. They allow the international community to monitor the oceans, predict threats, and protect critical infrastructure and trade routes. AI in the maritime sector must remain under human control and in full compliance with international law.
+The EU recalls the universal and unified character of the United Nations Convention on the Law of the Sea, which sets out the legal framework within which all activities in the oceans and seas must be carried out. New and emerging technologies must always respect international law, including international human rights and humanitarian law. Innovation must always remain subject to human oversight and state accountability.
+On 12 October, the EU launched a global “Pledge on Maintaining the Integrity of the International Law of the Sea – No Fees/No Tolls”. Together with 62 countries, we firmly reject any unlawful fees, compulsory tolls, or arbitrary restrictions designed to choke strategic international straits. Recent developments in the Strait of Hormuz, the Bab-el Mandeb, and the Black Sea illustrate the urgency of our discussions. Weaponizing global lifelines for political leverage or financial gain is unacceptable.
+The EU is translating these principles into political resolve. We are building defensive, non-escalatory capabilities, as we invest in cyber-resilient naval capabilities, maritime domain awareness, autonomous underwater and mines countermeasures, advanced sensing, and AI, with a focus on interoperable systems to ensure a more comprehensive and effective response to maritime threats. Not to project power, but to protect the rule of law. EU naval operations ATALANTA in the Western Indian Ocean, ASPIDES in the Red Sea, and IRINI in the Mediterranean — whose mandates now also address shadow fleets —, together with our Coordinated Maritime Presence in the Gulf of Guinea, are substantial European contributions to safeguarding freedom of navigation, including against tech-driven violence, and to the safety of seafarers.
+As emerging technologies rapidly reshape maritime threats, our collective responses must evolve just as quickly. The EU calls on all UN member states to ensure that the future of maritime security, in its broad sense, is defined by multilateral cooperation, transparency, and technological cooperation, to allow for the rapid detection of malicious activities, facilitate real-time information sharing, strengthen maritime domain awareness, build capacity, prevent escalation, and enhance the operational resilience of international shipping.
+We must ensure that innovation serves as a pillar of global stability, firmly anchored in international law.
+Thank you.
+- North Macedonia, Montenegro, Serbia, Albania and Bosnia and Herzegovina continue to be part of the Stabilisation and Association Process.</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:37.472210+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Haiti: Statement by the Spokesperson on the latest developments</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/haiti-statement-spokesperson-latest-developments_en</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+The European Union takes note of recent developments in Haiti’s electoral preparations, and reiterates its support for the organisation of elections. Credible, transparent and democratic elections are essential to ensuring institutional legitimacy.
+The EU welcomes the extension by the United Nations Security Council of the mandate of the Gang Suppression Force (GSF) until 31 March 2027. The GSF plays a crucial role in improving the security conditions necessary for the holding of elections. The EU commends the countries contributing personnel to the GSF and expresses its solidarity with El Salvador following the disappearance of Salvadorian military personnel.
+The EU recalls the existence of various international sanctions regimes, including the EU’s own sanctions regime targeting persons responsible for threats to the peace, stability or security of Haiti, or for undermining democracy and the rule of law. The EU reaffirms the importance of these frameworks in safeguarding the credibility and the integrity of the electoral process.
+The EU remains committed to working with Haiti’s regional and international partners in support of efforts to address the ongoing crisis. In particular, the EU is working closely with the Organisation of American States, to support the Haitian National Police, including in its joint operations with the GSF, through the establishment of five Forward Operating Bases, contributing to wider stabilisation efforts.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:43.522880+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly: Informal meeting of the AHWG on Mandate Implementation Review</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-informal-meeting-ahwg-mandate-implementation-review_en</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly: Informal meeting of the AHWG on Mandate Implementation Review
+Distinguished co-Chairs, excellencies, colleagues,
+I have the honour to speak on behalf of the European Union and its Member States.
+The European Union would like to thank you for convening this meeting and for your continued efforts to advance the work of the Ad Hoc Working Group. We also thank the Secretariat for the comprehensive and useful note on possible review mechanisms and implementation models for clustered and collective mandate implementation reviews.
+We welcome the work undertaken so far, including the Co-Chairs' report on criteria and modalities, which provides a useful and balanced framework for taking forward the implementation of General Assembly resolution 80/251.
+We would like to underline three points.
+First, on the overall approach, we believe it is important to maintain a clear focus on the ultimate objective of this exercise: improving the effectiveness, coherence and impact of UN mandates, and ultimately ensuring better delivery on the ground.
+The ambition of the mandate implementation review must be to ensure that the UN system is focused on the objectives where Member States expect it to deliver.
+In this regard, the criteria of relevance, impact and coherence provide a useful basis for assessing not only whether mandates are being implemented, but also whether they are collectively contributing to the intended results.
+At the same time, applying these criteria consistently will require a shared understanding of how they are measured. We would welcome further guidance, informed by the pilots and with support from the Secretariat, on the evidence needed to assess relevance, impact and coherence, and on how to distinguish functional duplication from complementarity.
+Second, on the review mechanisms, we see considerable value in exploring collective and clustered approaches, particularly where mandates contribute to shared objectives across different parts of the UN system.
+The Secretariat's note offers useful examples of how different approaches could be combined, including thematic clustering, coordinated multi-organ reviews and common evidence frameworks.
+We would encourage us to make full use of this flexibility. In particular, we should look beyond institutional and committee boundaries where this can provide a more comprehensive understanding of how mandates interact, where complementarities exist and where implementation could be made more effective.
+Third, on the pilot program, we believe this offers a particularly important opportunity to translate our discussions into practical experience.
+This should be a collaborative and comprehensive exercise, bringing together Member States across different regions and working across all three pillars of the United Nations.
+We would therefore encourage the Co-Chairs to consider a cross-cutting, cross-regional approach, whereby different UN Missions work together on the pilots, drawing on expertise and perspectives from across the membership and across the pillars.
+We see merit in ensuring that the pilots are not developed as separate, siloed exercises, but rather as part of a coordinated effort, with opportunities to identify linkages and lessons across thematic areas. Individual pilots could retain a manageable thematic scope, while contributing to a broader and more comprehensive assessment of mandate implementation across the UN system.
+Such an approach would also allow us to test how different review modalities can work in practice, including how mandates originating in different bodies can be examined collectively, how evidence and analysis can be shared, and how complementarities and potential overlaps can be better identified, while safeguarding essential functions.
+Importantly, we would like to see Member States from different regions actively working together on these exercises. This would help foster collective ownership, build confidence in the process and ensure that the lessons learned are relevant across the membership.
+We believe that the pilots should be practical and help us understand where the UN makes a difference and where improvements are needed. Their findings should inform possible mandate rationalization efforts and feed into the further refinement and codification of the criteria and modalities, as well as their broader application.
+We hope this pilot phase can start as soon as possible around a first limited set of thematic priorities and will support the co-Chairs’ proposals and leadership in this regard. Also, as the pilots are envisaged for the main part of this session, we would welcome an update from the Co-Chairs on the next steps. An early launch would allow their findings to inform our consideration of the Secretary-General’s report on inactive, duplicative and fully implemented mandates requested in paragraph 24 of resolution 80/251, expected by the end of December.
+Finally, we would underline the importance of maintaining momentum in the implementation of resolution 80/251 during the current Committee season. The use of concept notes, review clauses and more systematic consideration of existing mandates should become an integral part of our working methods.
+To this end, we would encourage the Co-Chairs to continue liaising closely with the Chairs and Bureaux of the Main Committees to gather clear data on how resolution 80/251 has been applied during this session: for example, how many resolution processes started with a concept note or how many resolutions included a review clause. Sharing this overview in the Working Group would give us a factual basis for assessing progress and identifying where further support is needed.
+Co-Chairs, colleagues, the EU stands ready to engage constructively in this next phase of the work, including in the development and implementation of the pilot exercises.
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:49.317001+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Sarajevo to host EU TAIEX workshop on transposing the EU Roaming acquis into the legal framework of Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/bosnia-and-herzegovina/sarajevo-host-eu-taiex-workshop-transposing-eu-roaming-acquis-legal-framework-bosnia-and-herzegovina_en</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Sarajevo to host EU TAIEX workshop on transposing the EU Roaming acquis into the legal framework of Bosnia and Herzegovina
+On 29–30 October 2026, a TAIEX workshop on the transposition of the EU Roaming acquis into the legal framework of Bosnia and Herzegovina, with practical case studies, will take place in Sarajevo, Bosnia and Herzegovina. The event is organised in co-operation with the Communications Regulatory Agency of Bosnia and Herzegovina (CRA) and the Ministry of Communications and Transport of Bosnia and Herzegovina.
+Aligning Bosnia and Herzegovina’s electronic communications legal framework with the EU acquis is an obligation stemming from its EU integration commitments. This event is particularly relevant in view of the further alignment with and implementation of the EU roaming acquis required for BiH to join the EU’s “Roam Like at Home” area.
+The workshop aims to strengthen understanding of the EU Roaming acquis and support participants in preparing for its effective transposition and implementation. It will focus on the two key pillars of the EU Roaming acquis assessment: transposition compliance and implementation capacity.
+The agenda foresees practical examples and experiences from countries that have already advanced in implementing the EU roaming acquis, including Moldova and Ukraine, as well as case studies from EU Member States such as Austria, Greece, Romania and Croatia. These sessions are intended to highlight key steps, challenges and lessons learned relevant to Bosnia and Herzegovina
+The workshop brings together experts from RTR Austria, EETT Greece, ANCOM Romania, HAKOM Croatia, the Communications Regulatory Agency of Bosnia and Herzegovina, and the Ministry of Communications and Transport of Bosnia and Herzegovina.
+The expected results of the workshop include improved understanding of the EU Roaming acquis, stronger capacity of the national regulatory authority and other stakeholders to ensure complete and accurate transposition, better knowledge of the European Commission’s methodology for assessing compliance and strengthened institutional and regulatory readiness for implementation and enforcement. The workshop is also expected to contribute to fair competition and consumer protection in the roaming market.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:11:55.277402+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Bukhara to Host EU-Supported “Yashil Uyim” Eco-Festival on 31 October</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/uzbekistan/bukhara-host-eu-supported-yashil-uyim-eco-festival-31-october_en</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Bukhara to Host EU-Supported “Yashil Uyim” Eco-Festival on 31 October
+29 October 2026, Bukhara, Uzbekistan. The “Yashil Uyim” (“My Green Home”) eco-festival will take place in Bukhara on 31 October, with financial support from the European Union as part of the Green Diplomacy Weeks 2026 campaign. The festival will offer an engaging programme of educational activities, interactive workshops, discussions and live performances, encouraging participants to explore practical ways to protect the environment and make more sustainable choices in their daily lives.
+Designed for adults, young people, children and parents, the festival will combine environmental education with science, creativity and entertainment. Through interactive activities and opportunities to exchange ideas, participants will discover how individual actions and collective initiatives can contribute to a cleaner, healthier and more sustainable future.
+A programme for all generations
+The festival’s main zone, dedicated to adults and young people, will open at 12:00 with a DJ setand a prize draw. At 13:00, sign language specialist E'zoza Ahmedova will lead an introductory session on sign language, promoting awareness of inclusive communication. This will be followed by a team game, “The City of Our Dreams”, inviting participants to imagine the cities they would like to live in.
+At 15:00, environmental activist – initiator and organiser of the Festival Moʻtabar Xushvaqtova will lead an interactive session titled “Plastic Is Not a Problem?” exploring the challenges and opportunities associated with plastic waste. At the same time, journalist and documentary filmmaker – participant of the EU Youth Sounding Board in 2023 Shakhzoda Mirakova will conduct an English-language discussion, “Ecofeminism: Is Climate Change Affecting Men and Women Equally?”, examining the gender dimension of climate change.
+The programme will conclude with a musical evening featuring live performances by Mansur Toshmatov and Sevara Toʻlanova from 17:00 to 18:00.
+The Kids’ Zone will offer activities for children and parents, including scientific experiment demonstrations, a robotics lesson, neurogymnastics games and practical methods for preparing children for school without stress. These activities will encourage curiosity, learning and creative thinking in a welcoming environment.
+Discover, exchange and act for the environment
+From 13:00 to 16:00, visitors will also be able to explore the Science Zone, visit a fair of environmentally friendly products, take part in a book-swap initiative and enjoy chess games.
+Dedicated collection points will accept used batteries, cooking oil, paper, plastic bags and aluminium, helping raise awareness of waste separation, recycling and responsible resource management. These initiatives will demonstrate how simple everyday practices can support more sustainable consumption and reduce environmental impact.
+The EU has managed to grow its economy by 71% while reducing emissions by 37% since 1990. European companies have played a crucial role in this achievement, drawing on decades of experience to develop innovative and reliable clean technology solutions. From wind and hydropower to solar thermal systems, heat pumps, electricity grids and transformers, European clean technologies offer high-quality solutions based on transparent standards and long-term partnerships. Water and agricultural technologies can also help communities adapt to climate change.
+The EU continues to support clean technology investment and sustainable development beyond its borders through initiatives such as the Global Gateway strategy, which promotes sustainable infrastructure, connectivity and mutually beneficial partnerships. By encouraging dialogue, environmental awareness and cooperation, the European Union aims to support efforts towards a greener and more resilient future.
+Green Diplomacy Weeks 2026
+The “Yashil Uyim” eco-festival in Bukhara is part of the European Union’s Green Diplomacy Weeks 2026 campaign, which promotes environmental awareness, climate action and sustainable development through activities involving local communities, civil society, young people and other partners.
+By bringing environmental topics into public spaces and making them accessible through practical activities, learning and cultural engagement, the festival aims to inspire participants to take action in their homes and communities.
+Date: 31 October 2026
+Location: Bukhara, Uzbekistan
+Main programme: 12:00–18:00
+Open activities: 13:00–16:00
+The festival is organised with financial support from the European Union under the Green Diplomacy Weeks 2026 campaign.</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:01.096778+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>IOM Standing Committee on Programmes and Finance - EU Statement - Item 2 Update by the Director General</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-geneva/iom-standing-committee-programmes-and-finance-eu-statement-item-2-update-director-general_en</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>IOM Standing Committee on Programmes and Finance - EU Statement - Item 2 Update by the Director General
+Statement on behalf of the European Union and its Member States
+International Organisation for Migration
+39th Session of the Standing Committee on Programmes and Finance
+29-30 October 2026
+________
+Item 2
+Update by the Director General
+________
+Geneva, 29 October 2026
+- CHECK AGAINST DELIVERY -
+International Organisation for Migration
+39th Session of the Standing Committee on Programmes and Finance
+29-30 October 2026
+Item 2 – Update by the Director General
+Statement on behalf of the European Union and its Member States
+Chair,
+I speak on behalf of the European Union and its Member States.
+The candidate countries North Macedonia, Montenegro, Serbia, Albania*, Ukraine and Republic of Moldova align themselves with this statement.
+Director General,
+- We thank you for your presentation and express our appreciation for the dedication and resilience of IOM staff in challenging operational environments. We reaffirm our steadfast commitment to multilateralism and international cooperation, with IOM as a key partner in promoting humane and effective migration governance, and we remain IOM's largest collective contributor.
+- We reaffirm our comprehensive, 360-degree, whole-of-government and whole-of-route approach to migration governance, grounded in international law and obligations thereunder, human rights and human dignity, and attach particular importance to migration diplomacy as a way of fostering practical cooperation with partners along migratory routes. This includes saving lives, protecting the human rights of migrants, addressing displacement and its drivers, preventing irregular migration, combating migrant smuggling and trafficking in human beings, promoting regular pathways in line with national competences, and facilitating safe, dignified and sustainable returns, readmission and reintegration through effective cooperation with countries of origin and transit.
+- We value the cooperation with IOM in implementing the EU Pact on Migration and Asylum. We welcome IOM’s engagement in the Eastern Corridor initiative, connecting countries from South Asia through North Africa to Europe, as well as our cooperation along the Atlantic and Mediterranean routes. These efforts should strengthen comprehensive cooperation among countries of origin, transit and destination along the entire migration route.
+- We welcome the stabilisation of IOM’s financial situation in 2026 and the prospect of modest growth in 2027. We also welcome the presentation of resources at outcome level in the 2027 Programme and Budget, as a further step towards enhanced results-based budgeting. We note the significant shift in IOM’s operational portfolio towards migration management and solutions to displacement. At the same time, substantial humanitarian needs and funding gaps persist, notably in Sudan, the Occupied Palestinian Territory, Syria and Ukraine. Preserving emergency response capacity remains essential.
+- Reliable data are critical for evidence-based responses. The EU supports an IOM-led consortium of UN agencies on humanitarian data initiative with EUR 22.8 million, including for the Displacement Tracking Matrix, complemented by another EUR 20 million support to collaboration among international humanitarian organisations and NGOs. These initiatives aim to strengthen joint data production, analysis and interoperability, treating humanitarian data as a global public good. Additional EU support includes a EUR 2 million IOM-UNHCR initiative on mixed migration data and interoperability, a EUR 5 million data programme with IOM for North Africa establishing a comprehensive picture of migration flows and a planned EUR 3.5 million action to support IOM’s DTM and innovative data methodologies.
+- We welcome the ongoing discussions on budget reform, recognising the need to strengthen the predictability and stability of financing of IOM’s core structure. While we continue to reflect on the options presented, we seek greater clarity on how this reform relates to system-wide reforms, on which core functions face the greatest funding pressures, as well as on the criteria for allocating any additional flexible resources, should they become available as a result of the reform.
+- UN80 and the Humanitarian Reset should deliver concrete efficiencies and clearer complementarity. A stronger One UN approach requires closer IOM-UNHCR cooperation, from headquarters to country level, including in operationalising the Route-Based Approach. We encourage both organisations to enhance complementarity and operational synergies, while respecting their distinct mandates and expertise, and to hold joint briefings at headquarters level, particularly on country and regional situations of shared engagement.
+- We encourage IOM to maintain its strong focus, within available resources, on the interlinkages between mobility and climate change], and on the cross-cutting priority of equality, diversity and inclusion across its operations and workplace. Strong core functions and independent oversight, including audit, evaluation, risk management, ethics and prevention of sexual exploitation, abuse and harassment, remain indispensable.
+We remain committed to an effective, accountable and resilient IOM.
+Thank you.
+* North Macedonia, Montenegro, Serbia and Albania continue to be part of the Stabilisation and Association Process</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:06.875095+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>EU Statement on Russia’s war of aggression against Ukraine, OSCE Forum for Security Co-operation N°1151 - Vienna, 28 October 2026</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/vienna-international-organisations/eu-statement-russias-war-aggression-against-ukraine-osce-forum-security-co-operation-ndeg1151-vienna_en</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>EU Statement on Russia’s war of aggression against Ukraine, OSCE Forum for Security Co-operation N°1151 - Vienna, 28 October 2026
+- The intensification of attacks by the Russian Federation across Ukraine in September continued a pattern of civilian casualties in 2026 far exceeding levels verified in previous years, with devastating consequences for civilians.
+- Mr Chair, what we just quoted is what the United Nations Human Rights Monitoring Mission in Ukraine said when it released its latest monthly update on civilian harm earlier this month. Independent reporting continues to show the impact of Russia’s illegal, unprovoked and unjustifiable war of aggression against Ukraine on the country and its population. The EU and its Member States strongly condemn the recent serious escalation by Russia, including large-scale missile and drone attacks against civilians in Ukraine.
+- Coming back to the latest update from the Monitoring Mission, it reported at least 328 civilians killed and 2 105 injured in September, making the total number of killed and injured that month 85 per cent higher than in September 2025. In Kyiv alone civilian casualties were recorded on 22 of 30 days, more frequently than in any previous month since the start of the full-scale invasion. The trend of high civilian casualties continues this month, making the first two weeks of October one of the deadliest periods for civilians in years.
+- The Mission’s update also highlighted Russia’s resumed large-scale coordinated attacks on electricity and heating infrastructure across Ukraine. We strongly condemn Russia for systematically and deliberately targeting Ukraine’s civilian and energy infrastructure.
+- As High Representative Kallas underlined last week, “Ukraine wants peace more than anybody because they have been under bombardment for already four years now, and the fifth year is going on [...] Ukraine agreed to a ceasefire, already one and a half years ago. Who hasn't agreed is Russia.”
+- The EU and its Member States support a comprehensive, just and lasting peace in Ukraine based on the principles of the UN Charter and international law and underpinned by robust and credible security guarantees for Ukraine. We urge Russia to show genuine willingness regarding peace, agree to a full, unconditional and immediate ceasefire and engage in meaningful negotiations.
+- On 23 October, the cargo ship Khoryv was struck by a drone in the exclusive economic zone of Romania, one nautical mile outside its territorial waters. The ship caught fire and sank. Of the crew, nine were rescued, one died, and three remain missing. The EU and its Member States express solidarity with Romania and strongly condemn the attack. In light of continued Russian attacks on maritime transport, the EU is engaging with international partners to promote safe passage for civilian and commercial shipping in the Black Sea. We call on Russia to abide by international law and its OSCE commitments.
+- The European Union strongly condemns the act of sabotage in Brașov on 14 September. After a thorough assessment, Romanian authorities confirmed that a network co-ordinated from the Russian Federation deliberately set fire to an industrial site, next to defence industry manufacturer Carfil. The EU stands in full solidarity with Romania.
+- What happened in Brasov was not an isolated incident. Since 2022, we have seen persistent, coordinated, and long-standing hybrid campaigns aimed at threatening and undermining the security, resilience and democratic foundations of the EU, its Member States and its partners, as well as undermining support to Ukraine and its ability to defend itself. Acts of sabotage, disruption of critical infrastructure, information manipulation and interference are becoming more frequent and more brazen. We stand in full solidarity with all EU Member States and countries that are affected by Russia’s actions.
+- Mr Chair, Europe’s support for Ukraine, together with our international partners, is stronger than ever and remains steadfast. We will continue our multi-faceted support, including political, financial, economic, humanitarian, military and diplomatic support to Ukraine and its people.
+- The EU and its Member States continue to call on Russia to stop its aggression and immediately, completely and unconditionally withdraw all of its forces and military equipment from the entire territory of Ukraine within its internationally recognised borders.
+- We reiterate our call on all countries to immediately cease any assistance to Russia in its war of aggression against Ukraine, whether direct or indirect, and notably through the provision of dual-use goods and components. In particular, we strongly condemn the deployment of the DPRK’s military forces in the war against Ukraine as well as the continued military support provided to Russia by Belarus, Iran and the DPRK, among others.
+- Mr Chair, the EU and its Member States resolutely condemn Russia’s war of aggression against Ukraine, which constitutes a manifest violation of international law including the UN Charter as well as the OSCE’s core principles and commitments.
+- We reaffirm our strong commitment to ensuring full accountability for war crimes and the other most serious crimes committed in connection with Russia’s war of aggression against Ukraine.
+Thank you.
+Albania, Andorra, Bosnia and Herzegovina, Georgia, Iceland, Lichtenstein, Republic of Moldova, Montenegro, North Macedonia, Norway, and Ukraine align themselves with this statement.</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:12.721251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Media advisory: HR/VP Kallas attends the G20 Foreign Ministers’ Meeting in Atlanta</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/media-advisory-hrvp-kallas-attends-g20-foreign-ministers-meeting-atlanta_en</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:18.646187+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>EU Statement on UNTOC COP13 resolution on the Effective Implementation of the Convention, 23 October 2026</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/vienna-international-organisations/eu-statement-untoc-cop13-resolution-effective-implementation-convention-23-october-2026_en</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>EU Statement on UNTOC COP13 resolution on the Effective Implementation of the Convention, 23 October 2026
+Mr. President,
+I have the honour to speak on behalf of the European Union (EU) and its Member States.
+We thank the United States for their efforts in advancing this important initiative, as well as all delegations for their constructive engagement throughout the negotiations and their willingness to work towards a common outcome.
+More than two decades after its entry into force, the Palermo Convention remains a cornerstone of international cooperation against transnational organized crime.
+As criminal threats continue to evolve, our collective efforts must increasingly focus on effective implementation, tangible results and the efficient use of available resources.
+Against this background, we must ensure that the Convention and its Protocols are not only widely supported, but effectively implemented and capable of delivering concrete results.
+The European Union and its Member States attach particular importance to strengthening the effectiveness of the Conference and its subsidiary bodies. More focused and inclusive discussions, streamlined working methods, better coordination and meaningful follow-up to agreed commitments can contribute to making our collective efforts more effective, while ensuring the inclusive and intergovernmental character of our work.
+We also reiterate our strong support for the Review Mechanism as an essential instrument for assessing implementation, identifying challenges, sharing good practices and promoting international cooperation. Its slow progress and persistent funding difficulties remain a source of concern.
+Ensuring adequate, predictable and sustainable resources, alongside greater efficiency in its functioning, is essential if the Mechanism is to fulfil its mandate and deliver meaningful results within a reasonable timeframe
+Mr. President,
+We see today’s resolution as an important contribution to our shared efforts to strengthen the implementation of the Palermo Convention and improve the effectiveness of the institutional framework supporting it.
+The adoption of this resolution is not an end in itself. Its success will ultimately depend on our collective ability to translate its provisions into practical improvements and tangible results.
+The European Union and its Member States remain fully committed to working constructively with all States Parties and UNODC to advance these objectives and ensure that the Palermo Convention continues to provide an effective framework for our common response to transnational organized crime.
+Mr. President.
+As this is the last time I take the floor in this session, let me add a few more general remarks.
+The European Union and its Member States would like to express their sincere and warm appreciation to the President of the Conference of the Parties, H.E. Gabriel Orellana Zabalza, for his excellent leadership, clear vision and steadfast stewardship of our work throughout this session. Under his guidance, proceedings were conducted in a spirit of openness, inclusiveness and cooperation, which greatly contributed to the constructive atmosphere that has prevailed during the week.
+We also wish to convey our deep thanks to the Chair of the Committee of the Whole, H.E. Delphine Hournau-Pouëzat, for the remarkable patience, skill and dedication with which she guided the negotiations on the six resolutions. Her calm, balanced and highly capable handling of our deliberations, and her ability to navigate complex discussions with both tact and determination, were instrumental in bringing our work to a successful conclusion.
+We further thank all members of the Bureau for their valuable contribution and support, as well as the Secretariat for its excellent support and professionalism throughout the session.
+Finally, we wish to extend our gratitude to all those whose indispensable efforts behind the scenes made this week possible, including the interpreters, technicians and cleaning personnel.
+Mr President
+Throughout this session, the European Union and its Member States engaged actively, constructively and in a spirit of compromise in all discussions. We worked consistently to support balanced, forward-looking and actionable outcomes, and we lent our support to all six resolutions under consideration.
+We regret that not all resolutions could be adopted by consensus as this does not reflect the shared commitment of all delegations to advancing our common objectives in a cooperative and pragmatic manner and look forward to joining forces for their implementation.
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:24.418750+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Egypt: Statement by the Spokesperson</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/egypt/egypt-statement-spokesperson_en</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Egypt: Statement by the Spokesperson
+On 28-29 September, the Matsadaash newsroom was arrested and its members remain in custody. On 27 October, the Editor in Chief and co-founder of the Egyptian independent media organization Mada Masr was convicted, leading to its closure.
+Freedom of expression is a fundamental right for both the European Union and Egypt.
+Our Association Agreement and our Strategic and Comprehensive Partnership entail a shared commitment to the universal values of democracy, the rule of law and respect for human rights and fundamental freedoms.
+Egypt’s National Human Rights Strategy seeks to enhance a culture of pluralism and diversity of opinions and views. Egypt’s laws recognize the right to freedom of opinion and expression, which is a fundamental right.
+In light of such, the preservation and the protection of independent media outlets are essential.</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:30.190567+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>New Job Vacancy Notice: Secretary (Admin Section - Local Agent, Group 3)</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/sudan/new-job-vacancy-notice-secretary-admin-section-local-agent-group-3_en</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>New Job Vacancy Notice: Secretary (Admin Section - Local Agent, Group 3)
+Who we are
+The European Union (EU) is an economic and political partnership between 27 European countries. It plays an important role in international affairs through diplomacy, trade, development aid and working with global organizations. Abroad, the European Union is represented through more than 140 diplomatic representations, known also as EU Delegations, which have a similar function to those of an embassy.
+The EU Delegation to the Arab Republic of Egypt, Cairo works in close coordination with the Embassies and Consulates of the 27 EU Member States. We are a fully-fledged diplomatic mission and represent the European Union in dealings with the Egyptian government in areas that are part of the EU’s remit.
+What we offer
+A post of Secretary (Local Agent Group 3 - Ref: 499719) in the Delegation’s Administration Section under a fixed-term employment contract of 2 years, with a possibility of renewal under reserve of budgetary availability and operational considerations. The team consists of 25 people and there are occasional atypical working hours.
+Under this post, the recruited person will be attributed to functions depending on the needs of the Delegation, and on the changes of these needs. The successful candidate will serve under the supervision and responsibility of the Head of Administration Section, providing support, expertise and assistance in Accounting, Infrastructure and Logistics.
+Key Responsibilities will be to assist in:
+- Staff recruitment process; maintain accurate and up-to-date employee records;
+- Payroll preparation and monitor employee attendance, leave, and absences;
+- Management of the Delegation’s office premises and logistics (including maintenance of office premises and Residence, management of housing, management of cars and drivers, archiving, …);
+- Initiation and follow up of procurements procedures;
+- Accountancy of administrative expenditure;
+- Management of budget;
+- Financial transactions and relation with the Delegation’s bank;
+- Cash management;
+- Management of missions;
+- First back-up for protocol, consular and Customs matters;
+- Basic IT Support activities, under supervision;
+- Handling employee queries in coordination with line managers;
+- Back-up of Administration Section as required;
+- Any other task as instructed by the Head of Administration.
+Functions and duties:
+- Operational &amp; administrative support and coordination (Missions)
+- Human resource management – Assistance in management of local staff (permanent or temporary)
+- Infrastructure &amp; logistics – Assistance to users and in management of Delegation’s premises
+- Procurement and contacts with suppliers
+- Budget, finance, contracts &amp; accounting management
+Minimum requirements / eligibility criteria (necessary for the application to be considered):
+- High School Degree or equivalent;
+- Minimum 3 years of experience as Secretary in several of the relevant fields indicated above. The professional experience must be acquired after the date on which the qualification allowing access to the post was obtained;
+- Excellent knowledge (C2 level in CEFR) of English and Arabic (written and spoken);
+- Excellent computer skills and knowledge of office software and IT tools (Words, Excel…);
+- Right to residence and work in Egypt (if no Egyptian national, please add a copy of your residence visa and work permit in your application).
+- Assets/selection criteria (basis for awarding points to select the best applicant)
+- University level education;
+- IT Support experience;
+- Experience of working in a team in multi-disciplinary and multi-cultural environment;
+- Having a good understanding of the values and of the mission of the European Union;
+- Previous experience in European and/or international organization’s cooperation;
+- Previous professional experience in Member States of the European Union;
+- Knowledge of other EU language(s);
+- Performing high professional standards with regards to reliability, confidentiality, personal integrity, loyalty and flexibility;
+- Having the capacity to focus on priorities and to organize work to deliver on time;
+- Teamwork fluency and capacity to work under pressure and to respond quickly to new demands;
+- Having the capacity to communicate clearly and concisely (orally and in writing);
+- Resilience to stress.
+The base salary will depend on relevant and verified employment experience, typically starting from EUR 1,145 payable in Egyptian Pounds based on the InforEuro exchange rate of the month of payment (see: https://commission.europa.eu/funding-tenders/procedures-guidelines-tenders/information-contractors-and-beneficiaries/exchange-rate-inforeuro_en).
+There is a competitive benefits package, subject to certain conditions, including personal leave days and public holidays, health insurances and a retirement savings plan.
+The expected start date will be 01/12/2026.
+The process:
+After the deadline for applications, the eligible applications will be admitted to the Selection by the Committee set up for this purpose.
+Depending on the number of applications received, successive phases of selection may include shortlisting of candidates based on the assessment of the information provided in the cover letter and the Europass CV, practical testing and interviews. 3 best candidates will be invited to the final interview.
+Only candidates admitted to each successive selection phase will be contacted individually.
+The Delegation will use the same means of publication as for this job advertisement to inform the remaining candidates once the recruitment procedure has been completed and that a candidate has (or has not) been recruited.
+How to apply?
+Please submit your application, consisting mandatorily of a cover letter signed and a CV using one of the Europass templates available athttps://europass.europa.eu/en to the following email address:
+Mentioning in the subject line the following reference: “Ref: 499719 – JOB TITLE: Secretary LA-3-ADMIN” no later than 10/11/2026 17h00 (GMT +2).
+Only complete applications received on time via the above-mentioned email address will be considered.</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:35.985835+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>EU and CCCPA Host Road to Schuman Forum for Security &amp; Defence in Cairo</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/egypt/eu-and-cccpa-host-road-schuman-forum-security-defence-cairo_en</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>EU and CCCPA Host Road to Schuman Forum for Security &amp; Defence in Cairo
+The EU Delegation to Egypt, in collaboration with the Cairo International Center for Conflict Resolution, Peacekeeping and Peacebuilding (CCCPA), hosted the Road to Schuman Forum for Security &amp; Defence.
+Bringing together government officials, diplomats, experts and academics, the conference explored pressing regional security challenges, the EU–Egypt strategic partnership, and the role of multilateral cooperation in advancing peace and stability.
+Discussions focused on navigating protracted conflicts, counterterrorism and maritime security threats, strengthening EU–Egypt cooperation for regional resilience, and reinforcing multilateral efforts in an increasingly complex geopolitical landscape.
+Through dialogue and partnership, the EU and Egypt continue to engage on shared security challenges and work towards a more peaceful and stable region.</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:41.752952+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Egypt: Statement by the Spokesperson</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/egypt-statement-spokesperson_en</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+On 28-29 September, the Matsadaash newsroom was arrested and its members remain in custody. On 27 October, the Editor in Chief and co-founder of the Egyptian independent media organization Mada Masr was convicted, leading to its closure.
+Freedom of expression is a fundamental right for both the European Union and Egypt.
+Our Association Agreement and our Strategic and Comprehensive Partnership entail a shared commitment to the universal values of democracy, the rule of law and respect for human rights and fundamental freedoms.
+Egypt’s National Human Rights Strategy seeks to enhance a culture of pluralism and diversity of opinions and views. Egypt’s laws recognize the right to freedom of opinion and expression, which is a fundamental right.
+In light of such, the preservation and the protection of independent media outlets are essential.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:47.732869+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Philippines-EU Reaffirm Partnership on Governance, Green Transition, Digital Economy, and Mindanao Development</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/philippines/philippines-eu-reaffirm-partnership-governance-green-transition-digital-economy-and-mindanao_en</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Philippines-EU Reaffirm Partnership on Governance, Green Transition, Digital Economy, and Mindanao Development
+The meeting was co-chaired by Undersecretary Joven Z. Balbosa of the Department of Finance (DOF)-International Finance Group and Head of Unit South and South-East Asia from the European Commission’s Directorate General for International Partnerships Ovidiu Mic.
+The Sub-Committee conducted a comprehensive review of ongoing cooperation and investment programs, focusing on two priority areas: (1) the Mindanao peace process and good governance; and (2) the green and digital economy.
+Both sides expressed their intent to deepen cooperation under Global Gateway and the Enhanced Partnership signed on 24 July 2026. Priority areas include sustainable connectivity, green transition, digital transformation, and inclusive growth, while continuing support for good governance and peace and development in Mindanao.
+Discussions highlighted the development of Global Gateway investment projects for both Government-to-Government cooperation and the private sector level. Also covered were ongoing investment operations on climate resilience, disaster risk reduction and water access, reflecting the shared commitment to strengthening the country’s adaptive capacity amid climate impacts and development challenges.
+New investments in key areas, such as green transition, circular economy, environmental protection, development in Mindanao, and prospective loan financing will be supported with EU grants (blended finance) and EU guarantees to de-risk upfront investment risks.
+Under the Europe Team Approach, the roles of the European Investment Bank (EIB), other European Development Finance Institutions (EDFIs), and the EU private sector will be crucial, alongside potential cooperation with multilateral development banks, particularly with the Asian Development Bank (ADB).
+The meeting also explored cooperation on the sustainable use of critical raw materials and recognised the relevance of regional cooperation within the framework of the EU-ASEAN Team Europe Initiatives, including the specific support for the seafarers’ action under the EU-ASEAN Sustainable Connectivity Package as well as the expansion of EU Copernicus Earth Observation actions from the Philippines to Southeast Asian countries.
+The EU and the Philippines highlighted the strategic importance of the ASEAN Power Grid as a key initiative for regional connectivity, energy integration, and the green transition, and further welcomed ongoing Team Europe support in this area.
+The discussions also considered the Philippines’ transition to an upper middle-income country (UMIC) status and the Luzon Economic Corridor (LEC) as an emerging platform for strategic connectivity and investment.
+The Philippine Government was represented by the DOF, Department of Economy, Planning, and Development (DepDev), Department of Foreign Affairs (DFA), Supreme Court, Court of Appeals (CA), Department of Energy (DOE), Department of Environment and Natural Resources (DENR), Department of Trade and Industry (DTI), Mindanao Development Authority (MinDA), Ministry of Agriculture, Fisheries, and Agrarian Reform of the Bangsamoro Autonomous Region in Muslim Mindanao (BARMM), Bangsamoro Planning and Development Authority, Department of Science and Technology (DOST), and Philippine Space Agency (PhilSA).
+The EU side was represented by the European Commission Directorate General for International Partnerships, EU Delegation to the Philippines, and the European Investment Bank.</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:53.652689+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue on Afghanistan</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-afghanistan_en</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue on Afghanistan
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States.
+We thank the Special Rapporteur for his latest report, which documents the worsening human rights situation in Afghanistan, including the devastating impact of the Taliban’s policies on children and young persons, in particular girls, returnee children, and children with disabilities. Five years after the Taliban takeover, these policies not only violate human rights on a massive scale, but are also reshaping Afghanistan’s social fabric through fear, exclusion, and ideological control.
+The EU strongly condemns all human rights violations and abuses, including the institutionalised and grave gender-based discrimination and oppression against women and girls. These systematic and systemic violations of women and girls’ human rights may amount to gender persecution, which is a crime against humanity under the Rome Statute of the ICC to which Afghanistan is a State party. Afghanistan remains the only country globally where women and girls are banned from education beyond the age of twelve. The exclusion of women and girls from education and public life is an affront to basic rights and freedoms.
+We are further alarmed by severe poverty and malnutrition, increases in child labour and child, early and forced marriage, the worsening mental health crisis among young persons, the repression of civic space and independent media, as well as the widespread use of corporal punishment and the death penalty. We call on the Taliban to immediately impose a moratorium and abolish the death penalty, end corporal punishment, ensure women and girls’ full enjoyment of human rights, and to respect and protect the rights of persons belonging to ethnic and religious minorities, persons in vulnerable situations, and LGBTI persons.
+The EU remains firmly committed to supporting the people of Afghanistan. We continue to support UNAMA’s comprehensive mandate with its strong human rights component, and the mandate of the Special Rapporteur. We also contributed to the establishment of the Independent Investigative Mechanism for Afghanistan and call for sustained political and financial support for its rapid operationalisation. The EU remains steadfast in supporting accountability, including through the ICC, and an Afghan-led political process inclusive of all Afghans, including with the full, equal and meaningful participation of women.
+At the same time, we continue our principled humanitarian engagement. Since 1994, the EU has provided around EUR 2 billion in humanitarian assistance to Afghanistan, including EUR 320 million in 2024–2025.
+In this context, we ask:
+How can international actors react to the Taliban’s systematic reshaping of Afghan society, with the aim of preserving the agency and participation of Afghans, especially women and young persons?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:12:59.481980+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Chair of the International Fact-Finding Mission for the Sudan</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-chair-international-fact-finding_en</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Chair of the International Fact-Finding Mission for the Sudan
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States.
+We commend the Fact-Finding Mission (FFM) for its vital work and commitment to advancing justice and accountability efforts in Sudan. We support its mandate and recent extension for another year.
+The latest FFM report once again underlines the alarming scale and pervasiveness of human rights violations and abuses in Sudan.
+We express our great concern at the detailed, concrete and grave findings, and we call on all States and external actors to refrain from any support to the warring parties and actions that fuel the conflict, aggravate the fallout on civilians and constrain prospects for an end to the conflict. We reiterate our support to the unity and territorial integrity of Sudan and for an inclusive Sudanese-led transition process that will lead up to civilian governance.
+The EU strongly condemns the deliberate and indiscriminate targeting of civilians, humanitarian personnel, and critical infrastructure, aggravated through the increasing use of drones, and the endangerment of water infrastructure, leaving up to 19 million civilians without access to safe drinking water, with consequences extending beyond the point of impact, particularly on women and children, as documented by the FFM. We express grave concern at the acute food insecurity and risk of famine affecting millions of civilians in Sudan. We call on all parties to the conflict to comply fully with their obligations under international humanitarian law and human rights law and strongly emphasize that this must be strictly observed. The protection of civilians and humanitarian personnel must be an immediate priority, and accountability for violations and abuses of human rights and of international humanitarian law, is essential. We also condemn, in the strongest possible terms, the unprecedented scale of conflict-relative sexual violence and its widespread use as a method of war. The EU calls for the immediate end to attacks on civilians, including gender-based violence, and critical infrastructure and urges both the SAF and RSF to agree to an immediate cessation of hostilities.
+We strongly call on all States to respect the UN arms embargo and refrain from arms deliveries.
+The EU will continue to do its utmost, including with international accountability mechanisms, to bring perpetrators to justice. The EU continues to support the work of the ICC and the UN and calls on Sudan to cooperate with the Independent Expert in Sudan and with the Independent International Fact-Finding Mission. The EU will continue to advocate for expanding the mandate of the ICC and of the arms embargo to the whole country.
+Chair, how can we support your work to enhance accountability for human rights violations in Sudan?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:05.261503+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Special Rapporteur on the situation of human rights in Burundi, Mr Fortuné Gaetan ZONGO</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-special-rapporteur-situation-1_en</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Special Rapporteur on the situation of human rights in Burundi, Mr Fortuné Gaetan ZONGO
+Chair,
+I have the honour to speak on behalf of the EU and its Member States.
+The EU thanks the Special Rapporteur for his work and reiterates its support for his mandate, which was recently renewed by the Human Rights Council, and which is being carried out under difficult conditions. The EU takes good note of the Special Rapporteur’s recommendations in support of human rights for all in Burundi.
+The EU encourages Burundi to provide full and unhindered access to the Special Rapporteur, to fully cooperate with OHCHR on reopening of a country office, and to effectively implement the recommendations of the former Commission of Inquiry and independence of the National Human Rights Commission.
+The Special Rapporteur’s report documents a persistent pattern of serious human rights violations and abuses. Despite some positive developments in recent years, the political and civic space continues to shrink.
+Ahead of the 2027 Presidential election, we are particularly concerned about growing restrictions targeting opposition parties, the media, human rights defenders, and civil society. An open and pluralistic political environment, and the full enjoyment of rights to freedom of expression, association and peaceful assembly, are essential to free, inclusive and credible elections.
+The European Union remains deeply committed to the promotion and protection of human rights in Burundi. We call on the authorities to ensure independent, impartial, and effective investigations into all allegations of human rights violations and to combat impunity. We look to Burundi to ensure, conditions necessary for an electoral process respectful of human rights. We reaffirm our firm support for the people of Burundi.
+Special Rapporteur,
+the EU echoes your concerns regarding the 2027 elections. How can the international community work with the Government of Burundi to ensure the full implementation of your recommendations as a preventive measure against human rights violations?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:11.036991+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Special Rapporteur on the situation of human rights in Eritrea, Mr Mohamed Abdelsalam BABIKER</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-special-rapporteur-situation-0_en</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Special Rapporteur on the situation of human rights in Eritrea, Mr Mohamed Abdelsalam BABIKER
+Chair,
+I have the honour to speak on behalf of the EU and its Member States.
+The EU thanks the Special Rapporteur for his work over these years and will continue to support this mandate at this time of change. We continue to call on Eritrea to engage constructively with the Human Rights Council and the new Special Rapporteur and grant the mandate full and unhindered access.
+The EU notes continued efforts to reduce the prevalence of female genital mutilation and maternal mortality. The EU has welcomed Eritrea’s ratification of the Convention on the Rights of Persons with Disabilities in 2025 and stands ready to support Eritrea in its swift implementation. The EU encourages Eritrea to make full use of cooperation with OHCHR, including considering inviting further technical assistance and capacity building.
+We welcome the release of some arbitrarily detained persons, and call on the Government to continue the releases. The whereabouts those disappeared in the past must be revealed.
+The EU welcomes Eritrea’s cooperation with the Human Rights Council during the Universal Periodic Review and in particular Eritrea’s acceptance of 126 recommendations.
+However, the challenges are still many, and we remain gravely concerned by the human rights situation in the country, as indicated by the Special Rapporteur. The lack of progress, and persisting structural impunity, strongly underline the need to maintain monitoring and reporting.
+A particular concern is the continued practice of long-term national service and widespread conscription, as well as reports of gender-based violence and forced labour. The right to conscientious objection must be respected. We are also particularly concerned about reports of transnational repression voiced by Eritreans in the diaspora, including the targeting of human rights defenders and government critics.
+Recent tensions between Eritrea and Ethiopia raise the spectre of renewed conflict. In view of this, the EU reiterates its call for immediate de-escalation on all fronts and urges those involved to refrain from actions or rhetoric which could increase tensions. The EU stresses that the territorial integrity and sovereignty of States must be respected by all parties involved. The EU is encouraging Eritrea to accede to the UNCLOS Convention which would strengthen Eritrea’s sovereign rights over its coastlines and ports, whilst at the same time providing a predictable basis under international law for peaceful transit and trade agreements with its neighbouring States – on an equal footing and by mutual consent.
+Mr Special Rapporteur.
+How do you view the potential of the international community to engage more with human rights in Eritrea?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:16.811990+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Special Rapporteur on the situation of human rights in Afghanistan, Mr. Richard Bennett</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-special-rapporteur-situation_en</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Special Rapporteur on the situation of human rights in Afghanistan, Mr. Richard Bennett
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States.
+We thank the Special Rapporteur for his latest report, which documents the worsening human rights situation in Afghanistan, including the devastating impact of the Taliban’s policies on children and young persons, in particular girls, returnee children, and children with disabilities. Five years after the Taliban takeover, these policies not only violate human rights on a massive scale, but are also reshaping Afghanistan’s social fabric through fear, exclusion, and ideological control.
+The EU strongly condemns all human rights violations and abuses, including the institutionalised and grave gender-based discrimination and oppression against women and girls. These systematic and systemic violations of women and girls’ human rights may amount to gender persecution, which is a crime against humanity under the Rome Statute of the ICC to which Afghanistan is a State party. Afghanistan remains the only country globally where women and girls are banned from education beyond the age of twelve. The exclusion of women and girls from education and public life is an affront to basic rights and freedoms.
+We are further alarmed by severe poverty and malnutrition, increases in child labour and child, early and forced marriage, the worsening mental health crisis among young persons, the repression of civic space and independent media, as well as the widespread use of corporal punishment and the death penalty. We call on the Taliban to immediately impose a moratorium and abolish the death penalty, end corporal punishment, ensure women and girls’ full enjoyment of human rights, and to respect and protect the rights of persons belonging to ethnic and religious minorities, persons in vulnerable situations, and LGBTI persons.
+The EU remains firmly committed to supporting the people of Afghanistan. We continue to support UNAMA’s comprehensive mandate with its strong human rights component, and the mandate of the Special Rapporteur. We also contributed to the establishment of the Independent Investigative Mechanism for Afghanistan and call for sustained political and financial support for its rapid operationalisation. The EU remains steadfast in supporting accountability, including through the ICC, and an Afghan-led political process inclusive of all Afghans, including with the full, equal and meaningful participation of women.
+At the same time, we continue our principled humanitarian engagement. Since 1994, the EU has provided around EUR 2 billion in humanitarian assistance to Afghanistan, including EUR 320 million in 2024–2025.
+In this context, we ask:
+How can international actors react to the Taliban’s systematic reshaping of Afghan society, with the aim of preserving the agency and participation of Afghans, especially women and young persons?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:22.585082+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogues on Iran</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogues-iran_en</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogues on Iran
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States. We thank the Special Rapporteur and the Fact-Finding Mission for their work and reports prepared under difficult circumstances and fully support their mandates.
+Last January, Iranian security forces answered the call of peaceful protesters for dignity, freedom, and a better life with lethal force and excessive violence, leading to tens of thousands of arrests and deaths, as well as forced confessions and persecutions under the cover of a nationwide internet shutdown. Since then, internal repression has only increased and the human rights situation remains dire. Accountability for these grave human rights violations is essential.
+The continuous and dramatic increase of the number of executions is unacceptable. The EU strongly condemns any use of the death penalty, torture and other cruel, inhumane and degrading treatment or punishment, including as a means to suppress internal dissent. We urge the Iranian authorities to immediately stop all executions and pursue a consistent policy towards the abolition of capital punishment.
+The EU is also gravely concerned about the restrictions on freedom of opinion, expression and peaceful assembly, offline and online, as well as the harassment and reprisals against all dissenting voices, including transnational repression. We call on the Iranian authorities to cease the violence and brutal repression against their own people, to provide due process and fair trial guarantees for all detainees, and to immediately and unconditionally release all arbitrarily detained citizens and individuals arrested for peacefully exercising their rights. The EU calls again for the respect of the universal human rights and fundamental freedoms of the Iranian people, including the right to choose their own future.
+We remain particularly concerned about the systematic discrimination against women and girls, and against persons belonging to ethnic and religious minorities, and call on Iran to end all forms of discrimination, in law and in practice against them.
+In light of the gravity of the repression, since the beginning of the year, the EU imposed additional sanctions on thirty-seven individuals and nine entities responsible for human rights violations in Iran. We stand ready to take further measures as necessary.
+The war has added another layer of suffering. We express deep concern over the loss of civilian life during the conflict, including those killed in the strike against a school in Minab on 28 February. We urge de-escalation and maximum restraint, the protection of civilians and civilian infrastructure in all circumstances, and full respect of international law and international humanitarian law, by all parties.
+In light of the scale of the crackdown against protesters, including widespread arrests, incommunicado detention, coerced confessions, and death penalty cases related to the protests, including public executions, I have two questions.
+Madam Special Rapporteur, what immediate actions should the international community take to prevent further violations, ensure access to legal representation and independent monitoring of detention facilities, and stop executions after unfair trials?
+Madam Member of the Commission, what concrete steps should the international community prioritise to ensure the preservation of evidence and strengthen accountability for serious violations of international human rights and humanitarian law?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:28.435137+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>La Unión Europea y el Programa Tinkuy presentan los resultados de su primer año y acuerdan con el Estado la hoja de ruta para avanzar en la transformación digital del Ecuador</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/ecuador/la-union-europea-y-el-programa-tinkuy-presentan-los-resultados-de-su-primer-ano-y-acuerdan-con-el_en</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>La Unión Europea y el Programa Tinkuy presentan los resultados de su primer año y acuerdan con el Estado la hoja de ruta para avanzar en la transformación digital del Ecuador
+Autoridades y representantes de las instituciones del Estado, la Delegación de la Unión Europea en Ecuador y los equipos del Programa Tinkuy durante los Subcomités Técnicos Anuales, Quito, 22 de octubre de 2026.
+El Programa de Interoperabilidad Digital del Ecuador – Tinkuy, financiado por la Unión Europea en el marco de la estrategia Global Gateway e implementado por la Fundación Internacional y para Iberoamérica de Políticas Públicas (FIAP), la e-Governance Academy (eGA) de Estonia y la Corporación Ecuatoriana para el Desarrollo de la Investigación y la Academia (CEDIA), realizó el 22 de octubre sus cuatro Subcomités Técnicos Anuales, un espacio de diálogo con las instituciones del Estado para presentar los resultados del primer año de implementación, recoger sus aportes y validar la hoja de ruta para el siguiente año.
+En la jornada participaron autoridades y equipos técnicos del Ministerio de Infraestructura y Tecnología (MIT) contraparte principal del Programa, la Presidencia y Vicepresidencia de la República, el Ministerio de Trabajo y Desarrollo Humano (MTDH), el Consejo de la Judicatura, el Ministerio del Interior, la Policía Nacional, la Dirección Nacional de Registros Públicos (DINARP), la Superintendencia de Protección de Datos Personales, la Fiscalía General del Estado, el Ministerio de Salud Pública, el EcuCERT y otras instituciones vinculadas a los servicios públicos digitales, la justicia, la protección social y la ciberseguridad, junto con la Delegación de la Unión Europea en Ecuador y las entidades implementadoras del programa, FIAP, eGA y CEDIA.
+El encuentro se organizó en subcomités, uno por cada componente del programa, en los que las instituciones contrapartes analizaron los avances alcanzados y aprobaron las hojas de ruta presentadas para cada componente.
+En materia de servicios públicos digitales centrados en la ciudadanía, se presentó la evaluación de la plataforma Gob.ec, construida a partir de entrevistas con más de 20 instituciones, y el análisis de los cuatro servicios priorizados para su rediseño: la inscripción de nacimientos en el Registro Civil, la emisión de la primera licencia de conducir de la Agencia Nacional de Tránsito, las denuncias laborales ante el Ministerio del Trabajo y el servicio de protección a víctimas de accidentes de tránsito. El MIT y el MTDH confirmaron estos servicios, seleccionados con enfoque ciudadano.
+En interoperabilidad, el programa acompaña al Consejo de la Judicatura y a las instituciones del sector de seguridad y justicia en la construcción de una visión común para el sistema de interoperabilidad del sector (SIREdeDJ), y apoya a la DINARP en el fortalecimiento de la plataforma nacional que permita el intercambio seguro de datos entre las entidades públicas. Durante la sesión, el Consejo de la Judicatura destacó que interoperar es lograr que la justicia llegue más rápido a las personas, mientras que la Fiscalía, el Ministerio de Salud Pública y la Policía Nacional resaltaron la importancia del programa para la transferencia de información.
+En el ámbito de la desnutrición crónica infantil, CEDIA presentó el diagnóstico del Sistema Unificado y Universal de Seguimiento Nominal (SUUSEN), elaborado con la participación de 34 personas de 8 instituciones, así como una revisión científica de 54 estudios que identificó 99 variables determinantes de la desnutrición crónica infantil. Estos insumos sientan las bases para avanzar hacia modelos de inteligencia artificial que permitan pasar de la alerta reactiva a la alerta predictiva.
+En ciberseguridad y lucha contra la ciberdelincuencia, se compartieron los resultados del diagnóstico situacional del país en estas materias, las jornadas de capacitación desarrolladas con el Centro Criptológico Nacional (CCN) de España con la participación de 14 instituciones. También se presentaron los avances y articulación que se está realizando en la construcción del Centro Cibernético, junto al Ministerio del Interior, Policía Nacional y Banco Interamericano de Desarrollo (BID) así como se presentó la plataforma de ciberinteligencia que se implementará el próximo año.
+Durante el encuentro, la Delegación de la Unión Europea destacó la relación de confianza con el Gobierno ecuatoriano, valoró la apertura de las instituciones a las observaciones técnicas y las invitó a aprovechar al máximo la experiencia europea y nacional movilizada a través del programa. Por su parte, la representante de la Presidencia de la República reafirmó su compromiso y acompañamiento a Tinkuy, y el Ministerio del Interior agradeció la cooperación de la Unión Europea en el fortalecimiento de las capacidades nacionales de ciberseguridad.
+Entre las principales acciones previstas para el próximo año se encuentran:
+- Nuevas fases de capacitación en diseño de servicios públicos.
+- Desarrollo del marco de gobernanza de datos.
+- Talleres para consensuar la arquitectura del sistema de interoperabilidad del sector de seguridad y justicia.
+- Acompañamiento a la DINARP en la implementación de la nueva plataforma nacional de interoperabilidad.
+- Exploración de modelos de inteligencia artificial y un hackatón de innovación abierta sobre desnutrición crónica infantil.
+- Instalación de un comité técnica para el modelo de gestión del Centro Cibernético y nuevas jornadas de capacitación especializada en ciberseguridad.
+- Visitas de estudio a Estonia y España.
+Los aportes recogidos en los subcomités serán incorporados en un informe que será validado por las contrapartes del Estado, y alimentarán el trabajo del Comité Directivo del programa, previsto para diciembre de 2026.
+La Unión Europea reafirma así su compromiso de acompañar al Ecuador en su transformación digital, promoviendo una administración pública más moderna, interconectada y segura, con servicios centrados en las personas.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:34.211452+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>European Union and Ecuador Strengthen Cooperation at the VI Technical Security Roundtable</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/ecuador/european-union-and-ecuador-strengthen-cooperation-vi-technical-security-roundtable_en</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>European Union and Ecuador Strengthen Cooperation at the VI Technical Security Roundtable
+Over the course of two days, the Roundtable brought together Ecuadorian authorities, representatives of the European Union and its Member States, and teams from EU-funded cooperation programmes to strengthen security, justice and human rights in addressing transnational organised crime, within a framework of shared responsibility.
+The opening session was also attended by Rosa Vásquez, Undersecretary for International Cooperation, and Silvia Viceconte, Team Leader for Security and Justice at the European Commission's Directorate-General for International Partnerships (DG INTPA). The meeting also brought together representatives of the European Commission and the European External Action Service (EEAS), as well as ambassadors and diplomatic representatives from Germany, France, Spain, Hungary, Belgium and the Netherlands.
+The Ecuadorian Government was represented by officials from the Ministries of Foreign Affairs and Human Mobility, Government, the Interior, National Defence and Public Health, among other ministries, as well as the Council of the Judiciary, the Attorney General's Office, the National Police, the penitentiary authorities and the Armed Forces.
+Angélica Arias, Vice-Minister for International Cooperation, reaffirmed the Government of Ecuador's commitment to strengthening security cooperation through a development-oriented approach based on interinstitutional coordination, mutual trust and shared responsibility. She emphasised the importance of linking security efforts with education, healthcare, social inclusion and development through preventive measures that complement the work of security and justice institutions, as well as border control efforts, while ensuring respect for human rights standards.
+She also recognised the importance of specialised EU cooperation programmes in addressing Ecuador's national priorities, noting that crimes such as drug trafficking, money laundering and illegal mining pose challenges that exceed the country's capacity to tackle them alone. In this context, she called for predictable cooperation aligned with Ecuador's priorities, with a view to jointly establishing a roadmap with the European Union and its Member States, setting out clear objectives and achievable commitments to protect citizens, strengthen the rule of law and promote socioeconomic development.
+For her part, Jekaterina Doródnova, Ambassador of the European Union to Ecuador, emphasised the shared nature of these security challenges and the EU's long-term commitment to Ecuador. She highlighted that EU cooperation combines law enforcement measures with institutional capacity-building, financial intelligence and prevention efforts focused on social inclusion and community cohesion.
+“A safe society is one that not only fights crime with the full institutional strength of the State, but also offers its young people opportunities for reintegration, education, employment and a future”
+The two-day Roundtable provided an opportunity to review progress made under cooperation programmes such as EL PAcCTO 2.0, COPOLAD III, EUROFRONT, SEACOP, CRIMARIO and AIRCOP, as well as the bilateral initiatives SERPAZ and EUFORT-EC. These initiatives support judicial cooperation, drug policies, border management, maritime, port and airport security, the fight against money laundering, prison management, and efforts to prevent violence and the recruitment of young people by criminal organisations. Discussions also covered cooperation in cybersecurity and the fight against cybercrime, including initiatives such as Tinkuy, LAC4 and EU-LAC CyberSHIELD.
+Through this engagement, the European Union reaffirms its commitment to supporting Ecuador through a Team Europe approach, promoting cooperation grounded in shared responsibility, institutional strengthening, democracy, the rule of law and respect for human rights.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:39.990236+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>EU Statement – UN Security Council: Open debate on Women, Peace and Security</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-security-council-open-debate-women-peace-and-security_en</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>EU Statement – UN Security Council: Open debate on Women, Peace and Security
+Check against delivery
+Mr. President, Mr. Secretary-General, Excellencies,
+I have the honour to speak on behalf of the European Union and its Member States.
+The Candidate Countries North Macedonia, Montenegro*, Albania*, Ukraine, the Republic of Moldova, and Georgia, as well as Andorra, Monaco, and San Marino align themselves with this statement.
+The EU thanks Greece for organising this crucial debate, and the distinguished briefers for their remarks.
+We are deeply concerned by the acute challenges highlighted in this year’s report, including the increase in conflict-related sexual violence, the rise in attacks against civilians, and the finding that one in five women and girls globally live in conflict-affected settings. Behind these figures are millions of lives uprooted and at risk in Sudan, the Democratic Republic of Congo, Gaza, Haiti, Afghanistan and in many other places. In Ukraine, Russia’s illegal, unprovoked and unjustified war of aggression continues to have a devastating impact on women and girls.
+We are also concerned that women are excluded from peace processes in many contexts, and that those speaking up often face coordinated harassment, hate speech and intimidation. In addition, many women’s rights organisations are beyond the breaking point, leaving millions without life-saving services.
+These disturbing trends are embedded in a wider pushback against gender equality and a coordinated and well-funded effort to undermine long-standing international norms and the multilateral system that upholds them. Gendered disinformation campaigns are deployed to destabilise societies. This backlash is not only an attack on the rights of women and girls – it is a threat to human rights, democracy, as well as peace and stability.
+Mr. President,
+In this light, the European Union has three key messages today.
+First, gender equality and the empowerment of all women and girls is not only a human rights issue but also a security imperative.
+Second, the Women, Peace and Security agenda is a central component to resolving today’s pressing security challenges. It strengthens our collective capacity to prevent and resolve conflict, ensure lasting peace, strengthen stability, prosperity and build more resilient societies.
+Third, commitments must translate into effective implementation. Women must be able to participate fully, equally and meaningfully and exercise leadership in decision-making, and at all stages of peace processes. A gender perspective must be mainstreamed across our peace and security policies and actions. The Security Council must lead by example by upholding the WPS framework and systematically integrating it into its decisions and mandates.
+The EU also calls for preventing and responding to conflict-related sexual violence, ensuring a survivor-centred approach and accountability for perpetrators. The International Criminal Court plays a crucial role in this regard, and we also welcome the creation of the CRSV Prosecution Network earlier this year.
+Mr. President,
+The European Union remains a reliable partner in these endeavours. We will continue to stand up for gender equality and the rights of all women and girls, especially when these rights are under pressure. And we will continue to support the WPS Agenda as a key enabler in this regard.
+We are embedding WPS into every strand of our external action, including our Common Foreign and Security Policy, as well as Common Security and Defence Policy (CSDP) missions and operations. We have placed WPS among the commitments of the twelve security and defence partnerships established with third countries.
+In addition, we have started the process of updating the EU WPS Action Plan, to make our foreign policy responses more systematic and result-oriented, and ensure that the plan responds to the evolving mediation landscape and emerging security threats, such as cyber and hybrid threats and foreign information manipulation and interference and climate change.
+Furthermore, the EU will continue to support women’s full, equal, meaningful and safe participation in decision-making and in all stages of peace processes. The EU has supported women peacebuilders, women-led and civil society organisations to advance mediation, conflict prevention and inclusive governance in conflict-affected communities across the world. For example, in Eastern DRC, local early-warning mechanisms established by women-led networks have reported critical information on activities of armed groups, allowing security forces to intervene and prevent attacks against communities.
+Moreover, the EU more than tripled its annual support to women’s rights organisations starting in 2021, reaching almost 300 million euros altogether in the past five years. Through its Human Rights Defenders Mechanism “ProtectDefenders.eu”, the EU assisted more than ten thousand human rights defenders in 2025 alone, including women human rights defenders.
+Mr President,
+The WPS agenda is a political and a security imperative. It is key to prevent wars and armed conflict, to end those ongoing, to build peace that lasts, and to secure justice for survivors.
+Today, more than ever, this agenda needs to be reinforced, politically and financially. The European Union remains committed to deliver on exactly that, in partnership with the UN, Member States and civil society.
+I thank you.
+- North Macedonia, Montenegro, Serbia, Albania and Bosnia and Herzegovina continue to be part of the Stabilisation and Association Process.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:45.875749+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Joint Statement on Democratic People’s Republic of Korea (DPRK) Sanctions</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/joint-statement-democratic-peoples-republic-korea-dprk-sanctions_en</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+The text of the following statement was released by Australia, Canada, France, Germany, Italy, Japan, the Netherlands, New Zealand, the Republic of Korea, the United Kingdom, the United States, and the European Union.
+Throughout October and today, the European Union (EU) and the governments of Australia and the United States have implemented sanctions to target the Democratic People’s Republic of Korea’s (DPRK) use of overseas workers, malicious cyber activities, and actors involved in unlawful DPRK-Russia cooperation. Their actions represent their efforts to disrupt the DPRK’s ability to support its unlawful development of weapons of mass destruction (WMD) and ballistic missiles, and to counter unlawful DPRK-Russia military cooperation.
+These designations build on detailed reporting published by the Multilateral Sanctions Monitoring Team (MSMT), which monitors and reports on DPRK’s non-compliance with UN Security Council resolutions in the absence of the UNSCR 1718 Committee Panel of Experts, whose mandate renewal was vetoed by Russia in 2024. The MSMT’s first and second reports outlined the DPRK’s unlawful military cooperation with Russia, along with cyber-enabled IT worker fraud, both of which serve to fund Pyongyang’s unlawful weapons programs. In September 2026, the MSMT released its third report detailing the DPRK’s deployment of overseas workers to generate revenue for its WMD and ballistic missile programs. The MSMT will continue to monitor, expose, and report on attempts to violate and evade UN sanctions by the DPRK.
+The MSMT and EU reaffirm our commitment to the complete, verifiable, and irreversible denuclearization of the DPRK, calling on it to abandon its unlawful WMD and ballistic missile programs, and taking action to counter DPRK attempts to violate and evade UN sanctions. We continue to strongly support the implementation of all DPRK-related UN Security Council resolutions. We call on all UN Member States, and especially permanent members of the Security Council, to fully implement these resolutions.</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:51.927551+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote – UN General Assembly: Draft Resolution A/81/L.5 on the Embargo imposed by the United States of America against Cuba</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-explanation-vote-un-general-assembly-draft-resolution-a81l5-embargo-imposed-united-states-america_en</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote – UN General Assembly: Draft Resolution A/81/L.5 on the Embargo imposed by the United States of America against Cuba
+President,
+I have the honour to speak on behalf of the European Union and its Member States.
+We reiterate today our conviction that the economic, commercial and financial embargo imposed by the United States on Cuba has adverse economic and humanitarian impact on the Cuban people.
+We reaffirm that the UN Charter is and remains the guiding framework, at a moment where Cubans are facing increasingly dire conditions. Humanitarian support and access must be protected under all circumstances.
+While responsibility for its domestic economic policies lies with Cuba, lifting the embargo could make economic reforms more effective and facilitate the further opening of the Cuban economy to the beneﬁt of the Cuban people.
+Millions of Cubans today face daily power outages, shortages of medicines and food, collapsing public services, and growing difficulties in accessing even the most basic healthcare. Hospitals struggle to function and the education system is under serious strain. Families spend hours searching for fuel, transport or essential products. In 2026, the EU stepped up its humanitarian assistance to Cuba to 16 million euro, implemented through international partners. The aid focuses on the most vulnerable, prioritising healthcare, emergency food assistance, access to water and energy.
+Nevertheless, the decisions made by the Cuban authorities, including longstanding structural weaknesses and inefficiencies in the economic system, lack of economic, judicial and political freedoms, and inadequate investment, have significantly contributed to the current crisis. Cubans, in particular young people, want a better life. They aspire to freedom and opportunity and deserve a brighter future.
+Meaningful political, economic, social and judicial reforms by the Cuban authorities are urgently needed to alleviate the suffering of the Cuban people. We call on Cuba to ensure that its reform agenda is implemented in a manner that addresses the key concerns of the Cuban population and meets the legitimate democratic aspirations of the Cuban people for more opportunities to participate in shaping the country's future.
+We remain deeply concerned about the human rights situation in Cuba, in particular following the events of July 2021, about the severe judgments issued by Cuban Courts so far, and about the respect of civil and political rights, including restrictions on freedom of expression, association and peaceful assembly, as well as continuing harassment of independent journalists, human rights defenders and members of civil society. We therefore reiterate our call on the Cuban Government to fully grant its citizens internationally recognized civil, political and economic rights and freedoms – including freedom of assembly, freedom of expression and opinion, including the freedom to seek, receive and impart information – to release all political prisoners and those arbitrarily detained, to ratify the UN Covenant for Civil and Political Rights and the Covenant for Economic, Social, and Cultural Rights, and to extend a standing invitation to all UN Special Procedures to visit Cuba. Moreover, the EU urges the Cuban authorities to make concrete advances towards opening spaces for a constructive and inclusive dialogue with civil society.
+We take note of the announcement of 176 economic and social measures adopted last June; what matters now is their swift implementation, and that they deliver concrete improvements in economic freedoms and transparency, for the Cuban people. These economic and social reforms need to be accompanied by rule of law, pluralism and democratic reforms, which must include the full respect for the human rights and fundamental freedoms of the Cuban people.
+Our approach to Cuba is grounded on the same principles that guide the European Union's relations with all its partners: respect for international law and the UN Charter, the sovereignty and territorial integrity of States, and the universal protection of human rights. These principles cannot be applied selectively.
+We deeply regret that Cuba's position on Russia's illegal war of aggression against Ukraine continues to be inconsistent with the principles of the UN Charter. This was exemplified by its vote against the 24 February 2026 General Assembly resolution on support for a ceasefire and lasting peace in Ukraine. In this context, the EU once again urges Cuba to refrain from providing any direct or indirect support to Russia’s aggression and to actively take all necessary and effective measures to prevent its nationals from joining Russian armed forces involved in the war. The EU expects all partners, including Cuba, to align with the principles of sovereignty and territorial integrity they invoke in other contexts.
+Extraterritorial measures negatively aﬀect EU economic interests and the lives of European residents in the island. As a matter of principle, we oppose such measures, due to their extraterritorial application, which is contrary to international law. To protect the interests of natural or legal persons residing in the EU against the extraterritorial application of the Helms-Burton Act, EU law forbids our Member States from implementing that legislation.
+The EU reaffirms its support to dialogue and a diplomatic solution between the US and Cuba, grounded in international law, including the principles of the UN Charter.
+To conclude,
+Neither isolation nor the absence of reform offers a sustainable path forward for Cuba.
+The EU will continue its critical yet constructive engagement with Cuba to support the country’s institutional, economic, social and political modernisation, while recalling that the swift implementation of reforms is the responsibility of Cuba. We stand ready to share our experience. We will also continue to support the Cuban population with humanitarian assistance to address its urgent needs.
+But let us be equally clear: humanitarian support alone will not solve Cuba’s crisis.
+Important sovereign decisions can no longer be postponed.
+I thank you.</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:13:57.697900+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COMUNICADO CONJUNTO - Diálogo local Argentina – Unión Europea en materia de Derechos Humanos</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/argentina/comunicado-conjunto-dialogo-local-argentina-union-europea-en-materia-de-derechos-humanos_und_en</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>COMUNICADO CONJUNTO - Diálogo local Argentina – Unión Europea en materia de Derechos Humanos
+COMUNICADO CONJUNTO
+Diálogo local Argentina – Unión Europea en materia de Derechos Humanos
+Buenos Aires, 28 de octubre de 2026
+La República Argentina y la Unión Europea celebraron el Diálogo local en materia de Derechos Humanos, realizado el 28 de octubre de 2026 en el Palacio San Martín, en la ciudad de Buenos Aires, como una instancia de intercambio constructivo y de fortalecimiento de los vínculos de cooperación entre ambas partes.
+El encuentro permitió abordar un amplio conjunto de cuestiones de interés común, entre ellas la cooperación multilateral en materia de derechos humanos, la protección de los derechos civiles y políticos, y de los derechos económicos, sociales y culturales. Ambas partes subrayaron la importancia de defender y promover los derechos humanos.
+La Argentina y la Unión Europea reconocieron que el intercambio franco y respetuoso constituye una herramienta fundamental para abordar cuestiones complejas, incluso cuando existen diferencias de enfoque o de interpretación.
+La realización de este encuentro constituye una oportunidad importante para consolidar una agenda de trabajo que permita dar continuidad a los intercambios y identificar áreas de cooperación.
+Ambas partes expresaron su voluntad de mantener este diálogo como un espacio de intercambio periódico, constructivo y respetuoso de las diferencias para profundizar el entendimiento mutuo y contribuir al fortalecimiento de las relaciones entre la República Argentina y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:14:03.470265+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Ms. Aude Maio-Coliche, Ambassador and Head of the European Union Delegation to Senegal, presented her credentials to President Bassirou Diomaye Faye.</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/senegal/ms-aude-maio-coliche-ambassador-and-head-european-union-delegation-senegal-presented-her-credentials_en</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Ms. Aude Maio-Coliche, Ambassador and Head of the European Union Delegation to Senegal, presented her credentials to President Bassirou Diomaye Faye.
+On Tuesday, October 27, Ambassador Aude Maio-Coliche presented her credentials to His Excellency Mr. Bassirou Diomaye Faye, President of the Republic of Senegal.
+H.E. Aude Maio-Coliche succeeds H.E. Jean-Marc Pisani. She assumes her duties at a pivotal moment in the historic and close relationship between the EU and Senegal, both of which share an ambition to further consolidate this strategic partnership. This partnership is characterized by regular dialogue and strengthened cooperation in key areas such as investment and economic development, peace and security, migration, and governance. The EU and Senegal share a commitment to promoting effective multilateralism and an international order based on law and justice.
+Her arrival also coincides with a new momentum for the EU’s presence in the region, marked by the launch of a new hub for international partnerships based in Dakar, which will cover six countries in the region. Furthermore, the EU Delegation to Senegal hosts several key regional offices, including those for the Foreign Policy Instrument (FPI), the European Civil Protection and Humanitarian Aid Operations (ECHO), and the European Investment Bank (EIB). In addition, 17 EU Member States—working as "Team Europe"—are engaged with Senegal alongside the Ambassador.
+Over the past five years, Ms. Maio-Coliche served as Director for Strategic Communication and Foresight. She also held the positions of Acting Deputy Managing Director for Africa and EU Ambassador for Equality within the European External Action Service.
+Previously, she served as the EU Ambassador to Argentina and Venezuela. Throughout her career, she has held various positions within the European Commission and the European External Action Service, focusing in particular on EU relations with Latin America and Central Africa. In 2011, she also contributed to the development of human resources policies for the then-newly established European External Action Service.
+Alongside her diplomatic and institutional experience, Ms. Maio-Coliche has worked in the private sector, providing consulting services on European affairs to international companies.
+Upon her appointment, Ms. Aude Maio-Coliche stated: "I am delighted to begin this new chapter in Senegal, working toward a strong, ambitious, and forward-looking partnership. I commend the strength and quality of the partnership between the European Union and Senegal, which is rooted in long-standing ties and a solid foundation." She added: "I look forward to meeting with political, economic, and civil society stakeholders, as well as young people—with whom we will continue to nurture and deepen our shared bonds—building upon the remarkable work accomplished by H.E. Jean-Marc Pisani."</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:14:09.470290+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EU_Delegation_Lebanon.xlsx
+++ b/EU_Delegation_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E325"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14777,6 +14777,1555 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 6th Committee: Cluster I: Report of the ILC on the work of its 76th and 77th sessions</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-6th-committee-cluster-i-report-ilc-work-its-76th-and-77th-sessions_en</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 6th Committee: Cluster I: Report of the ILC on the work of its 76th and 77th sessions
+Mr/Ms Chairperson,
+- The European Union would like to congratulate the ILC and the Special Rapporteur, Mr. Charles Chernor Jalloh, for the progress made on subsidiary means.
+- It welcomes the adoption of the entire set of draft conclusions with commentaries on first reading.
+Mr/Ms Chairperson,
+On the form
+- We welcome the form of “draft conclusions”. This is consistent with the ILC output on sources of international law and other related issues of international law.
+- Identification of customary international law; general principles of law; identification and legal consequences of peremptory norms of general international law (jus cogens); and subsequent agreements and subsequent practice in relation to the interpretation of treaties.1
+On the drafting
+- We have one observation on the drafting of conclusion 2. The chapeau uses the word ‘include’. This choice of word could indicate that the list in points (a) to (c) is not a closed one and that there are other subsidiary means than those listed below. At the same time, point (c) refers to ‘any other means generally used’. In view of this “catch-all” phrase, we wonder how the word “include” should be understood in the chapeau. In case there would be further means apart from those listed in points (a) to (c), “include” is the right choice. If that is not the case, it would be preferable to use another verb in the chapeau, such as “Subsidiary means for the determination of rules of international law are”.
+On the substance
+- First, the European Union welcomes that the commentaries to draft conclusion 2 explicitly refer to the Court of Justice of the European Union. Indeed, the CJEU has substantial case-law dealing with matters of international law and its jurisprudence could be an instructive subsidiary means for the determination of rules of international law.2
+- Second, the EU suggests that paragraph (9) of the commentary to draft conclusion 2 include criteria on how to define “courts and tribunals” and refer to our comments on previous years to this effect. 3
+- Third, draft conclusion 4 lists six criteria how to assess subsidiary means. The EU agrees that it is not possible to rank them in a hierarchical way. However, some means may still be more important than others. Therefore, the EU welcomes paragraph (7) of the commentary on draft conclusion 4, according to which the quality of reasoning is mentioned as ‘probably the most important consideration’.
+- Fourth, concerning paragraph (10) of the commentary to draft conclusion 6 the European Union would like to draw the attention of the ILC to the fact that the CJEU is also competent to provide binding decisions in reply to preliminary ruling requests coming from national courts of the Union’s Member States. Judgments in preliminary reference procedures “conclusively determine […] questions of [Union] law and [are] binding on the national court for the purposes of the decision to be given by it in the [national] proceedings”.4
+[1] Identification of customary international law; general principles of law; identification and legal consequences of peremptory norms of general international law (jus cogens); and subsequent agreements and subsequent practice in relation to the interpretation of treaties.
+[2] The latest cases deal with three aspects of important rules of customary international law, namely the principle of self-determination, including the requirement of consent and the relative effect of treaties. See C-778/21P and C-798/21P (‘Front Polisario’).
+[3] Examples of these criteria to define a “Court or Tribunal” could be: (1) whether the body is established by law, (2) whether the body's jurisdiction is compulsory and/or whether the body has the power to issue binding decisions for the parties to the dispute, (3) whether the body applies rules of law or decides on the basis of ex aequo et bono principles, (4) whether the body is independent and impartial. All other bodies which do not fulfil the criteria but yet their work may be useful for the determination of rules of international law, should fall under letter c) of draft conclusion 2 (i.e. “Any other means derived from the practices of States or international organizations”).
+[4] See Article 19 of the Treaty on European Union and Article 267 of the Treaty on the Functioning of the European Union.
+Settlement of disputes to which international organizations are parties
+(UNGA 6th Committee, 81st session, 2026)
+Ms./Mr. President,
+- I have the honour to speak on behalf of the European Union.
+- Let me start by warmly congratulating the Special Rapporteur, Mr. August Reinisch, for his work on the topic of ‘Settlement of disputes to which international organizations are parties’. The quality of his three reports has enabled the ILC to bring to a successful conclusion its first reading of the draft guidelines on settlement of disputes to which international organizations are parties.
+- The EU welcomes the adoption, by the ILC, of the draft guidelines together with commentaries thereto on first reading.
+- The EU moreover takes note of the ILC’s decision to transmit the draft guidelines, through the Secretary-General, to Governments and relevant international organisations for comments and observations, with the request that such comments and observations be submitted to the Secretary-General by 1 December 2027.
+- Accordingly, the EU may decide to submit comments and observations on the draft guidelines by 1 December 2027. Today, it will therefore limit itself to a few observations on the issue of disputes between international organisations and private parties, which is the focus of the Special Rapporteur’s third report and was discussed by the ILC mainly in 2026. As highlighted by the Special Rapporteur in his third report, “in practice, the most pressing questions relate to the settlement of disputes of a private law character”.
+- First, the EU welcomes the particularly thorough analysis of the available practice of the settlement of disputes between international organisations and private parties, including the references to the law and practice of regional economic integration organisations.
+- Second, the EU takes note of the carefully calibrated approach contained in draft guidelines 9 to 11, which balances the immunity of international organisations on the one hand with the requirement of access to justice on the other. Draft guideline 9 provides that the immunity of international organisations is to be respected, without implying that such immunity would prevail in every case. While this clarification is welcome, draft guideline 9 could also address the possibility of an exception to immunity in cases where the judicial proceedings at issue clearly do not impair the independent and effective performance of the functions of the international organisation concerned. At the same time, draft guideline 10 contains an obligation for international organisations enjoying immunity to endeavour to settle disputes with private parties and to make provision for appropriate modes of settlement of disputes. This provision constitutes an important building block in promoting access to justice in the event of disputes involving international organisations, which enjoy immunity.
+- While the expression “modes of settlement of disputes” is used in various treaties on privileges and immunities, it is only used in draft guideline 10, while the remainder of the draft guidelines consistently refer to “means of dispute settlement”. The latter notion is defined in draft guideline 2(d) in a broad manner, but the draft guidelines do not provide for a definition of “modes of settlement of disputes”. On the relationship between these two notions, the commentary states that “modes” (as well as “methods”) broadly overlap with “means” of dispute settlement. At the same time, for the purpose of the draft guidelines, the use of “modes of settlement of dispute” only in draft guideline 10 creates a degree of avoidable terminological uncertainty, in a guideline of considerable importance.
+- Third, draft guideline 12 provides that means of dispute settlement of an adjudicatory character shall conform to procedural rule of law as well as human rights requirements, including the independence and impartiality of adjudicators and due process. As confirmed by the commentary6, the references to independence and impartiality as well as due process in draft guideline 12 are illustrative. These references relate to core rule of law and human rights requirements do not constitute an exhaustive list.
+- Finally, the illustrative nature of the references in draft guideline 12 ensures that other rule of law and human rights requirements of a procedural nature are also within the scope of draft guideline 12. In the interest of clarity and legal certainty, the ILC could seek to expand on these “other rule of law and human rights requirements” in the commentary. This would appear to be particularly useful in view of the normative language used in draft guideline 12.
+- In conclusion, the European Union wishes to express its appreciation for the work done by the ILC on this topic leading up to the adoption of the draft guidelines on first reading. This topic is of particular importance for the European Union as an international organisation that is a regular party to disputes, including disputes with private parties. Thank you. 
+[6] Commentary on draft guideline 12, paragraph (16).</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:42:45.491025+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote: UN General Assembly 1st Committee: before the vote on Cluster III (Outer space)</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-explanation-vote-un-general-assembly-1st-committee-vote-cluster-iii-outer-space_en</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote: UN General Assembly 1st Committee: before the vote on Cluster III (Outer space)
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States to explain our vote against the proposals contained in documents L.54 "No First Placement of Weapons in Outer Space", and L.53 “Further Practical Measures on the Prevention of an Arms Race in Outer Space”.
+The Candidate Countries North Macedonia, Montenegro*, Albania*, Ukraine, the Republic of Moldova, Bosnia and Herzegovina* and Georgia align themselves with this statement.
+The EU and its Member States are actively engaged in promoting the preservation of a safe, stable, secure, and sustainable space environment and the peaceful use of outer space on an equitable and mutually acceptable basis for all. We remain strongly committed to the prevention of an arms race in outer space, thus safeguarding the free exploration and long-term use of the space environment for peaceful purposes.
+We share the view that we need further practical measures for PAROS in accordance with the spirit of the Outer Space Treaty, as it is also set out in the Final Document of the First SSOD in 1978. Such measures can be a combination of legally binding and non-legally binding ones and should cover all aspects of PAROS, including the prevention of the outbreak of conflicts in outer space. Draft resolution L.53, however, leaves ambiguity on definitions regarding the question of what constitutes a weapon in space. Almost every object could in one way or another be considered a weapon if used in an aggressive manner. In the same vein, draft resolution L.53 fails to address the reality of growing threats emanating from Earth to security and stability in space.
+Also, given the rapidly evolving space activities and threats, we do not believe that legally binding prohibitions would be the only tool to curb those. They can be addressed through a combination of legally binding and non-legally binding measures. While reaffirming the importance of developing effective, verifiable legally binding instruments in this field, the EU and its Member States believe that developing norms, rules and principles of responsible behaviours is the most pragmatic and immediate way forward to make progress on PAROS and improve space security. Only through considering various forms of measures can we build common understandings on key concepts and objectives and, eventually building on this, consider the negotiation of legally binding instruments on PAROS, avoiding as much as possible the duplication of efforts and redundancy of action. We hope to discuss these issues extensively at the ongoing substantive sessions of the OEWG on PAROS in all its aspects, as per its mandate adopted last year. Our goal is to reach a synthesis of different narratives there, in the interest of all, which this draft resolution does not help in our view.
+Chair.
+With regard to draft Resolution L.54, our position has been known for many years and remains unchanged. We stress that the no-first-placement approach neither addresses the difficult issue of defining what a weapon in outer space is, which continues to make this resolution ineffective, nor does it address threats from the malign use of space systems to interfere with other space systems. Ambiguities, regarding the use of certain objects and regarding intentions on their use, could lead to misinterpretations, misunderstandings and miscalculations, and could consequently increase the risk of conflict in space. Again, substantial in-detail discussions on this matter at the substantial sessions of the OEWG on PAROS in all its aspects are ongoing.
+Furthermore, with space being increasingly contested and congested, we remain concerned about the continued development and testing of anti-satellite weapons and the repeated threats as well as aggressive behavior by the Russian Federation against commercial satellites. We underline the importance of addressing such dangerous and highly destabilizing actions promptly, comprehensively, and as part of international efforts to prevent an arms race in outer space, something that this resolution does not do.
+Chair,
+New language added to both L.54 and L.53 undermines the mandated balance between different approaches to space security by setting the main call of one of those, notably on “the prohibition of placement of weapons in outer space”, as a main goal of the ongoing processes related to the prevention of an arms race in outer space in all its aspects, while omitting all others. This is even more regretful as we have a dedicated body, the Open-Ended Working Group on the Prevention of an Arms Race in Outer Space in all its aspects (OEWG PAROS) to deal with different narratives on the subject, mandated to discuss and put forward a final report with recommendations to the General Assembly. In our view, during its mandate between 2025 and 2028, it is primarily the OEWG to consider different narratives and possible measures and outcomes, be those proposed draft treaties or non-legally binding rules, norms and principles or other measures. Including one – and only one – of those into L.54 and L.53 prejudges, in our view, the outcome of the OEWG process, and attempts to guide Geneva deliberations from outside. The EU cannot accept such a move and therefore cannot support these resolutions. For this reason, the EU also cannot accept any further reference to any of the two draft resolutions, if adopted, as a valid argument in support of the necessity of a legally binding instrument on the subject mentioned in the upcoming deliberations in the OEWG PAROS, including on its final report.
+Chair,
+Against this background and as per UNGA resolution 77/41, the EU welcomes the national commitments made by an increasing number of UN Member States not to conduct destructive direct-ascent anti-satellite missile tests, including all EU Member States. This contributes to building the necessary confidence between States to reach our overarching goal of PAROS.
+The EU Member States will vote against these two resolutions and call on other Member States to do the same.
+Thank you.
+- North Macedonia, Montenegro, Albania and Bosnia and Herzegovina continue to be part of the Stabilisation and Association Process.</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:42:51.239332+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Remarks by HR/VP Kaja Kallas at the G20 Foreign Ministers Meeting – Plenary Session II: Energy</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/remarks-hrvp-kaja-kallas-g20-foreign-ministers-meeting-plenary-session-ii-energy_en</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+Energy security is a crucial issue for all countries. Disruptions to strategic routes and critical infrastructure quickly translate into higher prices, pressure on households and industry, and wider economic vulnerability. We see it in all our countries.
+From the Strait of Hormuz to Ukraine, geopolitics is shaping energy security and severely affecting people’s lives. All our economies have a critical interest in reliable supplies, affordable energy and resilient infrastructure.
+I welcome the G20’s work on energy security, resilient supply chains, critical minerals and access to clean cooking. These are practical areas in which international cooperation can deliver tangible benefits.
+Energy security, diversification and the clean energy transition reinforce one another, they are not contradicting. Our task is to address immediate needs while reducing our exposure to future crises.
+Secure energy flows are a fundamental concern for all of us. Attacks on energy infrastructure and the blocking of critical waterways should be strongly condemned by the G20.
+The G20 Energy Security Principles give us a useful basis for cooperation. We should build on the common ground they provide on affordability, diversification, connectivity, resilience and secure energy flows.
+Immediate crisis measures should be coordinated, targeted and temporary. I know it is very hard to do because how do you define the targeted and temporary part when you don’t know how long a crisis will take. Cooperation on emergency supplies and stock releases can ease market pressures, but we need to focus on restoring secure flows and addressing the geopolitical drivers of disruption.
+For the European Union, the energy transition is central to strengthening resilience. Faster deployment of renewables and low-carbon energy must go hand in hand with stronger grids, storage, energy efficiency and the capacity to maintain a reliable electricity system.
+This must be an international effort. We should strengthen cooperation on diversified and resilient energy infrastructure, and its protection against physical and cyber threats.
+Energy security must also mean access to affordable and reliable energy. The EU will continue its cooperation with partners of the Global South – on clean cooking and clean energy investment – as an integral part of our work.
+The EU stands ready to work with partners on practical measures that address today’s pressures and reduce tomorrow’s vulnerabilities.
+Energy security and the clean energy transition must advance together.</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:42:57.265648+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Russia: Statement by the Spokesperson on the Day of Remembrance of Victims of Political Repression</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/russia-statement-spokesperson-day-remembrance-victims-political-repression_en</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+On the day of remembrance of victims of the Soviet state terror, we pay tribute to the millions of repressed and to those in Russia who, at great personal cost, are preserving their names.
+The Kremlin is trying to erase the memory of the victims of Soviet terror and threatens with prosecution those who challenge the official version of the past.
+There are more than 1800 political prisoners in Russia, and the number keeps growing. Political activists, human rights defenders, journalists, historians, and scientists are subject to systematic, state-sponsored internal repression. Many face inhumane conditions and torture. Alexei Navalny paid with his life.
+The European Union calls for the immediate and unconditional release and effective rehabilitation of all political prisoners, including Alexei Gorinov, Ivan Safronov, Igor Baryshnikov, Maria Ponomarenko, Antonina Favorskaya, Nika Novak, Alexander Kynev and many others.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:03.163852+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Remarks by HR/VP Kaja Kallas at the G20 Foreign Ministers Meeting – Plenary Session I: Geopolitical Tensions</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/remarks-hrvp-kaja-kallas-g20-foreign-ministers-meeting-plenary-session-i-geopolitical-tensions_en</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Remarks by HR/VP Kaja Kallas at the G20 Foreign Ministers Meeting – Plenary Session I: Geopolitical Tensions
+Thank you dear Marco [Rubio] for gathering us here in Atlanta to discuss these important topics.
+From Ukraine to the Middle East, conflicts are disrupting food supplies, energy markets and international trade. We have a collective responsibility to address these global consequences. The G20 remains an essential forum for international cooperation in this regard.
+We must preserve the G20’s effectiveness. In this spirit, I share the concerns expressed over South Africa’s absence.
+A world divided into spheres of influence can only undermine global cooperation. Respect for sovereignty, territorial integrity and international law is the foundation of lasting peace and security.
+Russia’s war of aggression against Ukraine is a flagrant violation of the UN Charter. The EU will continue to support Ukraine and efforts towards a comprehensive, just and lasting peace, respecting Ukraine’s sovereignty, territorial integrity and right to choose its own future.
+We support Ukraine’s call for an immediate, full and unconditional ceasefire. Only Russia is disagreeing to it. It is for Russia to demonstrate a genuine willingness to end its military aggression and engage in meaningful negotiations.
+Russia’s attacks on Ukrainian ports, agricultural infrastructure and civilian shipping have consequences far beyond Ukraine. The Black Sea has become a choke point. Global grain prices are at their highest since 2023. As a representative from the African Union also pointed out, Russia’s activities in the Black Sea make it harder to put food on people’s plates across the world.
+Food must never be used as a weapon.
+At the recent G20 Trade Ministers’ meeting, we agreed to condemn the weaponisation of food. We must now translate that commitment into action.
+At the UN General Assembly, 51 countries came together to condemn Russia and call for Black Sea passage.
+I call on G20 partners who have not already done so, to support a freedom of navigation arrangement in the Black Sea, protecting civilian shipping and critical infrastructure and safeguarding the uninterrupted flow of agricultural exports. Ukraine has accepted this, Russia has rejected it. I urge partners to use their diplomatic engagement with Russia to advance this proposal.
+The security of other critical waterways also matters for food production. Disruption to fertiliser trade through the Strait of Hormuz risks increasing agricultural production costs, with consequences for farmers and consumers worldwide.
+Food-importing countries, particularly in Africa, have a direct stake in keeping these routes open. The EU strongly supports these countries in ensuring reliable and affordable supplies. It is a shared interest around which we should act together. I count on G20 members to use their influence with the parties concerned to protect food supplies, facilitate humanitarian access and prevent further disruption to agricultural trade.
+Conflict and coercion are threatening waterways on which all our economies and populations depend. Disruptions in the Strait of Hormuz and Bab al-Mandab put energy security, trade and supply chains at risk. Tensions in the South China Sea and the Taiwan Strait are also of concern to the European Union.
+International maritime routes are global lifelines. Attempts to alter the status quo through force or coercion, or unlawfully restrict access to key sea lanes, threaten stability and prosperity well beyond the regions concerned. We must uphold freedom of navigation in accordance with international law, including UNCLOS, and strengthen cooperation to protect commercial shipping and maritime security.
+I call on G20 partners to oppose unlawful restrictions and charges on international shipping. Over 60 countries have now signed our 'No Fees, No Tolls' pledge on maintaining the integrity of the International Law of the Sea. I urge others to do so, as well.
+Despite our differences, we must act where our interests converge: support a freedom of navigation arrangement in the Black Sea, uphold freedom of navigation more broadly and deliver on our commitment against the weaponisation of food.
+The EU stands ready to work with partners to take these proposals forward through concrete diplomatic follow-up. This is how the G20 can demonstrate its value in protecting global stability and prosperity to populations.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:09.060302+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Report of the Human Rights Council</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-report-human-rights-council_en</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Report of the Human Rights Council
+Mr. President,
+I have the honour to speak on behalf of the European Union and its Member States.
+The Candidate Countries Montenegro*, Albania*, the Republic of Moldova, Bosnia and Herzegovina*, Andorra, and San Marino and the align themselves with this statement.
+The European Union warmly thanks Ambassador Sidharto Reza Suryodipuro for presenting the Council’s annual report to the General Assembly. We thank you for your leadership of the Human Rights Council.
+We meet at a difficult time. Conflicts continue to claim lives and devastate communities, while violations and abuses of human rights, democratic backsliding and restrictions on civic space threaten hard-won progress. These challenges are interconnected. Human rights violations can fuel conflict and instability, while discrimination, poverty and exclusion undermine peace and sustainable development.
+The Human Rights Council cannot resolve these challenges alone. But it has an essential role in providing early warning, ensuring that human rights violations are documented, victims are heard, thereby contributing to fight against impunity, promote accountability and prevent future violations and abuses.
+This year marks twenty years since the Human Rights Council held its first session. Its establishment reflected a shared commitment to strengthening the United Nations’ capacity to promote and protect human rights worldwide.
+Over these two decades, the Council has developed important instruments to advance this mandate. The Universal Periodic Review brings every State’s human rights record under scrutiny. The Special Procedures provide independent expertise and early warning. Investigative mechanisms help establish facts and preserve evidence. The Council also provides a forum for dialogue, technical assistance and cooperation, and a vital space for civil society to contribute to the international human rights system.
+These mechanisms are complementary. Their value ultimately depends on whether States abide by their obligations, recommendations are implemented, violations are addressed and rights are protected. The twentieth anniversary is an opportunity to recognize progress, acknowledge the challenges that remain and renew our collective commitment to making the Council more effective.
+The EU and its Member States have sought to contribute to this shared effort, working with partners across regions and supporting initiatives that address the full range of human rights.
+During the past year, we supported several resolutions on economic, social and cultural rights, including the right to education, to adequate housing, and access to safe drinking water and sanitation.
+We led the work on the resolution on freedom of religion or belief and supported several other resolutions on civil and political rights, including on freedom of opinion and expression, countering disinformation, and efforts to combat torture and enforced disappearances.
+We continued to promote gender equality and the empowerment of all women and girls, including through efforts to address discrimination, harmful practices and structural barriers to full, equal and meaningful participation, including in the field of digital technologies.
+We supported work on the rights of the child, youth, older persons, Indigenous Peoples and persons with disabilities, the fight against racism, as well as the protection of human rights defenders and civic space.
+We also led and supported initiatives addressing the human rights implications of artificial intelligence and digital technologies, recognizing the critical importance of ensuring that technological progress respects human rights and fundamental freedoms.
+Across these areas, we recognize the importance of cooperation and inclusive dialogue. Progress requires listening to different experiences, addressing legitimate concerns and ensuring that commitments translate into practical improvements in people’s lives.
+Mr. President,
+The EU continues to protect and promote human rights both at home and abroad. We recognize that no country has an ideal human rights record, and that we all have work to do. For our part, we remain open to constructive criticism, dialogue and learning from others. This includes cooperating fully with the UN human rights mechanisms. All 27 EU Member States have issued a standing invitation to the UN Special Procedures, and we urge others to do the same. We also regularly invite OHCHR comments on legislative and policy initiatives at the Union level and remain open to dialogue on comments, or even criticism, received from the Office or Special Procedures mandate holders.
+The Universal Periodic Review is unique tool for promoting and protecting human rights globally. At a time when the international human rights system faces growing challenges, and as we move towards its 5th cycle, we must continue to safeguard the UPR as a credible, inclusive, universal and effective mechanism that enjoys the participation of all States.
+Mr President,
+The world cannot turn a blind eye to serious human rights violations and abuses taking place around the world. That is why the Council’s responsibility to respond to provide early warning and serious human rights situations remains a crucial part of its mandate.
+During the past year, the EU and its Member States continued to engage actively to ensure that the Council fulfills this responsibility, working with partners to sustain monitoring, investigations, and accountability.
+The majority of the Council’s country specific resolutions were adopted by consensus, including the EU-led resolution on the human rights situation in Afghanistan, which built on the creation, last year, of an independent investigative mechanism; but also the ones on Myanmar and DPRK. The resolutions on the situation in Georgia and Syria were also adopted by consensus.
+The EU also led initiatives in the Council to address grave human rights situations in Belarus, Burundi and Eritrea, renewing important mandates.
+The EU supported the renewal of the mandate of the Commission of Inquiry on the human rights situation in Ukraine, stemming from the Russian illegal war of aggression, which is essential to document and preserve evidence of Russia’s war crimes and human rights violations and ensure justice and accountability. This includes the documented deportation and forcible transfer of Ukrainian children, whose return remains unresolved.
+At the latest HRC session, the EU led the resolution renewing the mandate of the Special Rapporteur on the situation of human rights in the Russian Federation. The extent of human rights violations, including extrajudicial killings, torture, abuse of Interpol red notices and intensified transnational repression justifies continued monitoring by the mandate that remains a lifeline for Russian civil society.
+Last year, the Council responded to the reports of alarming human rights violations in Sudan, first by convening a special session following the atrocities committed in and around El Fasher in November last year, and by holding an urgent debate on situation in and around El Obeid in July, as the risk of further atrocities grew. The EU supported this timely response, including the decision for an urgent inquiry by the Independent International Fact-Finding Mission for the Sudan into alleged violations and abuses in El Fasher.
+These efforts do not diminish national responsibility. Rather, they support it by helping States meet their international obligations and by ensuring that serious human rights concerns receive the attention they require. Sovereign equality and non-interference in internal affairs do not exempt States from their obligations under international law. Cooperation with international human rights mechanisms is an integral part of the commitments States have accepted.
+Mr. President,
+The current global context makes the work of the Human Rights Council all the more necessary. It must remain equipped to perform its functions and its mandates adequately staffed and resourced.
+The UN80 Initiative is our common opportunity to improve the effectiveness of the United Nations, reduce unnecessary duplication and focus resources on implementation and impact. The EU and its Member States support these efforts. We also stress that reform must strengthen, not weaken, the human rights pillar, especially given its critical role and modest share of the UN budget, leaving it severely underfunded.
+The Council and OHCHR need adequate, predictable, increased and sustainable funding to respond to urgent situations, support States seeking assistance and carry out the mandates entrusted to them by Member States.
+We welcome efforts to improve working methods and rationalize initiatives.. Such efforts must be inclusive, equitable and shared by all. Efficiency should allow us to focus more on implementation, cooperation and tangible results for rights-holders.
+Protecting the UN human rights system also requires support for other institutions that uphold international law. Let me therefore reaffirm our unwavering support for the international criminal justice system, including the International Criminal Court, which was recently awarded the human rights Sakharov Award by the European Parliament. We strongly reject any attempts to undermine its independence and integrity.
+Mr. President,
+Twenty years after its establishment, the Human Rights Council remains a vital part of the multilateral system.
+The EU and its Member States will continue to work with all States and partners to strengthen the Council, support its mechanisms, protect civic space and advance all human rights — universal, indivisible, interdependent and interrelated.
+Our shared task is not simply to preserve the institutions we have built, but to ensure that they deliver meaningful results for the people they exist to serve.
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:14.805911+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>IOM Standing Committee on Programmes and Finance - EU Statement - Item 3(ii) Labour Mobility</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-geneva/iom-standing-committee-programmes-and-finance-eu-statement-item-3ii-labour-mobility_en</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>IOM Standing Committee on Programmes and Finance - EU Statement - Item 3(ii) Labour Mobility
+Statement on behalf of the European Union and its Member States
+International Organisation for Migration
+39th Session of the Standing Committee on Programmes and Finance
+29-30 October 2026
+________
+Item 3(ii)
+Labour Mobility
+________
+Geneva, 30 October 2026
+- CHECK AGAINST DELIVERY -
+International Organisation for Migration
+39th Session of the Standing Committee on Programmes and Finance
+29-30 October 2026
+Item 3(ii) – Labour Mobility
+Statement on behalf of the European Union and its Member States
+Chair,
+- The European Union and its Member States thank IOM for its paper on financing labour mobility. We recognise that access to adequate and sustainable financing is an important factor in enhancing and diversifying the availability of regular pathways for labour migration.
+- Such pathways are an important component of our comprehensive approach to migration. We support well-managed, human rights-based labour migration and regular pathways that promote decent work and respond to identified labour market and skills needs, while creating opportunities for regular migrant workers, protecting their human and labour rights and contributing to sustainable development in countries of origin and destination. Such pathways should be mutually beneficial partnerships, in accordance with national competences and applicable international labour standards.
+- Through Talent Partnerships and various EU- and Member State-funded initiatives, for example THAMM Plus, TVET programmes, labour mobility projects and circular migration initiatives, national programming funded by the Asylum Migration and Integration Fund, and others, we are already supporting skills development, institutional cooperation, fair recruitment and labour mobility. We are also developing new instruments to facilitate international recruitment and skills matching, including the EU Talent Pool and the first European Legal Gateway Office pilot in India in the ICT sector.
+- We agree with IOM that sustainable labour mobility requires moving beyond individual projects towards more coordinated and strategic initiatives and investments across the entire mobility pathway. This includes skills development, recognition of qualifications, fair recruitment, access to decent work and integration, as well as strengthening labour market institutions in countries of origin and destination.
+- We believe that sustainable financing requires greater involvement of the private sector, particularly employers, who directly benefit from labour mobility. Existing EU and Member State-supported initiatives provide valuable experience on the respective contributions of public authorities, employers and development partners across the labour mobility pathway. We also see potential for multilateral development banks, other financial institutions and philanthropic actors to help mobilise additional resources. Public and development funding should be used strategically to address financing gaps, strengthen institutional capacities and ensure development benefits for countries of origin, including by mitigating risks of brain drain and promoting skills development and skills circulation.
+- At the same time, innovative financing arrangements must be firmly grounded in international labour standards and fair recruitment principles. We particularly underline the need to prevent excessive indebtedness, debt bondage and other forms of exploitation, while ensuring appropriate safeguards for financing arrangements that envisage repayment through migrants' future earnings. Such arrangements should be subject to transparency, effective oversight and accessible grievance and remedy mechanisms.
+- We also encourage IOM to work closely with the ILO, drawing on its expertise in international labour standards, decent work, fair recruitment, social dialogue, skills development, labour-market needs assessment and anticipation, and strengthening labour market institutions, as well as its tripartite structure, to ensure the meaningful involvement of employers' and workers' organisations in developing sustainable labour mobility financing approaches.
+- Against this background, we would welcome IOM's views on two questions.
+- First, how does IOM envisage drawing on the experience of existing labour mobility partnerships, including EU- and Member State-supported programmes, to identify financing models that are genuinely sustainable and scalable?
+- Second, as IOM develops innovative financing mechanisms, how will it translate fair recruitment principles into concrete safeguards, particularly for arrangements involving repayment through future earnings?
+- We look forward to continued cooperation with IOM on this important agenda.
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:20.553867+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>EU Statement – UN Security Council: Briefing on Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-security-council-briefing-bosnia-and-herzegovina_en</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>EU Statement – UN Security Council: Briefing on Bosnia and Herzegovina
+Check against delivery
+President,
+I have the honour to speak on behalf of the European Union and its Member States. The Candidate Countries Türkiye, North Macedonia, Montenegro*, and the Republic of Moldova, as well as San Marino align themselves with this statement.
+The European Union welcomes the renewal of the mandate of EUFOR Althea by this Council.
+EUFOR Althea continues to play a key role in supporting the authorities of Bosnia and Herzegovina in maintaining a safe and secure environment for all its citizens. This operation demonstrates the EU’s long-lasting commitment to Bosnia and Herzegovina.
+On 4 October 2026 general elections took place in Bosnia and Herzegovina. The EU takes note of the preliminary OSCE/ODIHR assessment that the elections were competitive and orderly, despite shortcomings. The EU welcomes the overall successful deployment of new election technologies and commends the Central Election Commission’s efforts amid constraints. The EU calls for the swift formation of the new authorities and expects political leaders to engage constructively in line with citizens’ EU aspirations in order to build functional institutions.
+The EU emphasises that the sovereignty, territorial integrity, constitutional order, including Constitutional Court decisions, and international personality of Bosnia and Herzegovina need to be respected. The EU urges all political actors in Bosnia and Herzegovina to refrain from and renounce provocative divisive and secessionist rhetoric and actions.
+Regarding developments following the death of Ratko Mladić, a convicted war criminal responsible for genocide, war crimes, and crimes against humanity, the EU underlines that the presence and paying tribute by high-ranking politicians and officials at his funeral is deeply regrettable. The EU condemns any glorification of war criminals, genocide denial and revisionism, which contradicts the most fundamental European values and has no place in the EU or in partners who aspire to join the EU. Reconciliation and good neighbourly relations in the Western Balkans remain central to building a common future.
+L'UE réaffirme l'importance d'une coopération continue entre les acteurs internationaux et exprime son soutien à la mission du Haut Représentant et de son bureau, afin de mettre en œuvre l'agenda 5+2. Nous espérons qu'un ressortissant de l'Union européenne sera rapidement nommé comme prochain Haut Représentant, ce dernier incarnera le choix de la Bosnie-Herzégovine de postuler pour son adhésion à l'UE. Le Haut Représentant devra refléter le consensus au sein du Comité directeur du Conseil de mise en œuvre de la paix, être un acteur crédible auprès des acteurs locaux et traiter avec eux de manière inclusive.
+Following the European Council decision in March 2024 to open EU accession negotiations with Bosnia and Herzegovina, the EU urges all political actors to renew the country’s focus on progressing on the EU path and to intensify efforts to deliver EU reforms, taking all relevant steps. Bosnia and Herzegovina should without delay meet the requirements to benefit from the Reform and Growth Facility.
+The European Union reiterates its unequivocal commitment to Bosnia and Herzegovina’s EU perspective as a single, united and sovereign country.
+Thank you, President.
+- North Macedonia and Montenegro continue to be part of the Stabilisation and Association Process.</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:26.294076+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>EU Statement on International Day to End Impunity for Crimes against Journalists</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/council-europe/eu-statement-international-day-end-impunity-crimes-against-journalists-1_en</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>EU Statement on International Day to End Impunity for Crimes against Journalists
+I have the honour to speak on behalf of the European Union and its Member States, the Candidate Countries: Albania, Bosnia and Herzegovina, Georgia, Moldova, Montenegro, North Macedonia, Serbia, Ukraine, as well as Andorra, Armenia, Iceland, Liechtenstein, Monaco, Norway, San Marino and the United Kingdom are aligning with this statement.
+- Marking the International Day to End Impunity for Crimes against Journalists, the European Union reaffirms its steadfast commitment to freedom of expression and media freedom and recalls the indispensable role of free, independent and pluralistic media. Across the world, journalists and other media actors continue to face violence, intimidation, arbitrary detention and surveillance. Such acts not only undermine freedom of expression and the public’s right to receive information, but also weaken democratic accountability and the rule of law.
+- Journalists reporting from situations of armed conflict or investigating corruption, organised crime, human rights violations, migration, climate change and other matters of public interest remain particularly exposed. At the same time, the evolving digital environment has brought new and increasingly sophisticated threats, including online harassment, doxing, coordinated campaigns, misinformation and disinformation and AI-generated or manipulated content. Women journalists continue to be disproportionately targeted by gender-based and technology-facilitated violence. Transnational repression is becoming more common and more sophisticated, targeting also journalists in exile These challenges underscore the need for effective preventive measures and appropriate safeguards, both online and offline.
+- States have responsibility to prevent violence, ensure the safety of journalists at risk and conduct impartial and effective investigations into attacks against them. Those responsible must be brought to justice. Failure to ensure accountability risks fostering a climate of impunity, with a chilling effect on journalism and democratic participation.
+- Throughout 2026, the EU has continued to consolidate its legal and institutional framework: the implementation of the European Media Freedom Act strengthens safeguards for editorial independence and journalistic sources, including protection against unlawful surveillance. The Anti-SLAPP Directive, provides further safeguards for journalists, human rights defenders and other public watchdogs facing abusive legal proceedings. The EU remains equally committed to supporting journalists at risk, including in exile and in conflict environments.
+- The EU strongly supports the Council of Europe’s continued engagement in this field, notably through the “Journalists Matter” Campaign for the Safety of Journalists, with its emphasis on prevention in 2026, and the Platform to Promote the Protection of Journalism and Safety of Journalists. We remain fully committed to safeguarding freedom of expression, media freedom and pluralism, while - at the same time - welcoming efforts to strengthen democratic resilience against foreign information manipulation and interference (FIMI). We encourage all Member States to actively participate in the “Journalists Matter” Campaign, to engage constructively with the Platform and to provide timely and substantive responses to alerts.</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:32.110845+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>EU Statement on Ukraine</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/council-europe/eu-statement-ukraine-5_en</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+I have the honour to speak on behalf of the European Union and its Member States, the Candidate Countries: Albania, Bosnia and Herzegovina, Moldova, Montenegro, North Macedonia, Ukraine, as well as Andorra, Iceland, Liechtenstein, Monaco, Norway and the United Kingdom are aligning with this statement.
+The EU strongly condemns Russia´s escalated large-scale, deliberate and systematic missile and drone attacks against Ukraine’s civilians and civilian infrastructure. To help Ukraine prepare for winter, the EU calls for further intensified efforts and coordination to urgently strengthen Ukraine’s air and missile defence capabilities, the resilience of its critical infrastructure and energy system, including through the Ukraine Energy Support Fund, and to address other immediate needs. Enhanced regional energy cooperation and cross-border electricity interconnections play a pivotal role in this regard.
+By targeting Ukraine’s agricultural infrastructure, Black Sea and Danube ports, border crossing points, export facilities and vessels, by blocking shipping lanes, and by destroying grain storage facilities, Russia is once again weaponising food and undermining global food security, with severe consequences for the most vulnerable countries and populations around the globe.
+The EU remains determined to further increase pressure on Russia so that it stops its brutal war of aggression and engages in meaningful negotiations towards peace. The EU recently adopted its 21st sanctions package and a substantial number of further listings of individuals and entities. We regret the United States’ decision to temporarily lift sanctions on Russian diesel.
+The EU reaffirms its continued firm and unwavering support for Ukraine’s independence, sovereignty and territorial integrity within its internationally recognised borders. We will continue to provide, in coordination with like-minded partners and allies, comprehensive political, financial, economic, humanitarian, military and diplomatic support to Ukraine and its people.
+We reiterate our commitment to ensuring full accountability for war crimes and the other most serious crimes committed in connection with Russia’s war of aggression and fully support ongoing efforts within the framework of the Council of Europe towards the operationalisation of the International Claims Commission for Ukraine and the Special Tribunal for the Crime of Aggression against Ukraine. The EU urges Russia and Belarus to immediately ensure the safe and unconditional return to Ukraine of all unlawfully deported and transferred Ukrainian children and other civilians.</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:37.934087+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>EU Statement on the Current Issue raised by Romania: On the sabotage act in Brașov, Romania (September 14, 2026), OSCE Permanent Council No. 1583 - Vienna, 29 October 2026</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/vienna-international-organisations/eu-statement-current-issue-raised-romania-sabotage-act-brasov-romania-september-14-2026-osce_en</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>EU Statement on the Current Issue raised by Romania: On the sabotage act in Brașov, Romania (September 14, 2026), OSCE Permanent Council No. 1583 - Vienna, 29 October 2026
+- The European Union strongly condemns the act of sabotage in Brașov, Romania, on 14 September. After a thorough assessment, Romanian authorities confirmed that a network co-ordinated from the Russian Federation deliberately set fire to an industrial site, next to defence industry manufacturer Carfil.
+- What happened in Brașov was not an isolated incident. Since 2022, we have seen persistent, coordinated, and long-standing hybrid campaigns aimed at threatening and undermining the security, resilience and democratic foundations of the EU, its Member States and its partners, as well as undermining support to Ukraine and its ability to defend itself. Acts of sabotage, disruption of critical infrastructure, information manipulation and interference are becoming more frequent and more brazen.
+- We also condemn the repeated attacks against civilian shipping, merchant and commercial vessels in the Black Sea, such as the recent attacks against civilian ships in Romania’s territorial waters and in its exclusive economic zone, as well as in Bulgaria’s exclusive economic zone. These attacks constitute a serious violation of international and maritime law, including the United Nations Convention on the Law of the Sea (UNCLOS). We furthermore condemn the repeated violations of the airspace of EU Member States, most recently of Romania, and of the Republic of Moldova, in the context of Russia’s intensified attacks against Ukraine.
+- We stand in full solidarity with Romania and all EU Member States and countries that are affected by Russia’s actions.
+- The European Union and the Member States will make full use of all instruments and mechanisms available, including the EU hybrid toolbox, at the request of the Member State concerned, to prevent, deter and respond to hybrid attacks.
+- Russia’s attempts to sow distrust will fail. The EU is more united than ever in its support to Ukraine and will not cease to defend democracy, international law, the Charter of the UN and the Helsinki Final Act.
+Albania, Andorra, Bosnia and Herzegovina, Georgia, Iceland, Liechtenstein, Republic of Moldova, Montenegro, North Macedonia, Norway, San Marino, Ukraine, and the United Kingdom align themselves with this statement.</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:43.818540+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>EU Statement on the Russian Federation’s ongoing aggression against Ukraine, OSCE Permanent Council No. 1583 - Vienna, 29 October 2026</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/vienna-international-organisations/eu-statement-russian-federations-ongoing-aggression-against-ukraine-osce-permanent-council-no-1583_en</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>EU Statement on the Russian Federation’s ongoing aggression against Ukraine, OSCE Permanent Council No. 1583 - Vienna, 29 October 2026
+- The latest report of the UN Independent International Commission of Inquiry on Ukraine, published on 26 October 2026, concludes that Russia’s systematic attacks on Ukraine’s energy infrastructure constitute war crimes and crimes against humanity as they deliberately targeted civilian facilities under a state policy aimed at depriving civilians of essential services. As winter approaches, Russia continues to strike Ukraine’s energy system, causing damage and power cuts across several regions, including Kyiv, Vinnytsia, Odesa, Poltava, Volyn and Rivne.
+- Last week alone, Russia launched around 1,600 guided aerial bombs, 48 missiles of various types, including ballistic missiles, and nearly 2,300 attack drones against Ukraine. These large-scale combined missile and drone attacks against Ukraine have killed and injured civilians, including first responders, and damaged residential areas, energy and transport infrastructure, medical and educational facilities, commercial sites, grain storage facilities and logistics hubs. We strongly condemn them and demand that Russia immediately and unconditionally cease its aggression, withdraw all its forces and military equipment from the entire territory of Ukraine, and fully respect Ukraine’s sovereignty, independence and territorial integrity within its internationally recognised borders.
+- We are also deeply alarmed by Russia’s continued escalation in the Black Sea, which affects maritime security and undermines global food security. We strongly condemn repeated attacks on civilian vessels, including the attack on 23 October against the cargo ship Khoryv, carrying Ukrainian and Azerbaijani crew, in Romania’s exclusive economic zone, and the drone attack against a container ship in Bulgaria’s exclusive economic zone on 28 October. Such attacks are unacceptable and constitute a serious violation of international and maritime law, including UNCLOS.
+Mr Chair,
+- Behind every Russian missile striking Ukraine, there is a supply chain that makes its production possible. The EU’s latest sanctions target 1,569 individuals and entities linked to Russia’s military-industrial complex, to disrupt weapons production and limit Moscow’s ability to sustain its attacks. We will continue to increase pressure on Russia and unwaveringly support Ukraine.
+- We also reiterate our call on all countries to immediately cease any assistance to Russia in its war of aggression against Ukraine, whether direct or indirect, and notably through the provision of dual-use goods and components. In particular, we strongly condemn the deployment of the DPRK’s military forces in the war against Ukraine as well as the continued military support provided to Russia by Iran, Belarus and the DPRK, among others.
+- The European Union supports a comprehensive, just and lasting peace in Ukraine based on the principles of the UN Charter and international law and underpinned by robust and credible security guarantees for Ukraine. We support all diplomatic efforts aimed at achieving such a peace and urge Russia to agree to a full, unconditional and immediate ceasefire and to engage seriously in meaningful negotiations.
+- Humanitarian relief efforts and confidence-building measures, notably the exchange of prisoners of war and the return of unlawfully deported Ukrainian children and civilian detainees, including the three OSCE staff members — Vadym Golda, Maksym Petrov and Dmytro Shabanov, must continue as part of the pathway to peace. While we welcome the latest exchange of prisoners of war, which brought 270 Ukrainians home, some of whom had been in captivity since 2022, we remind Russia that it must fully comply with international humanitarian law in its treatment of prisoners of war.
+- We welcome the immediate localised ceasefire in temporarily occupied Oleshky. It is crucial that the ceasefire is upheld. Before Russia’s full-scale invasion, around 24,000 people lived in Oleshky. By July 2026, Ukrainian authorities estimated that just 2,000 remained. Those still trapped in the Russian-occupied city have been facing acute shortages of food, water and medicine, with humanitarian deliveries cut off and no safe means of escape. It is important to establish humanitarian corridors that allow people to relocate to areas of their choice.
+- We remain committed to ensuring full accountability for war crimes and the other most serious crimes committed in connection with Russia’s war of aggression against Ukraine. ODIHR, through its monitoring activities, and the OSCE human dimension mechanisms make important contributions to that end. The OSCE plays and will continue to play a role in view of a just and lasting peace in Ukraine.
+Albania, Andorra, Bosnia and Herzegovina, Georgia, Iceland, Liechtenstein, Republic of Moldova, Monaco, Montenegro, North Macedonia, Norway, San Marino, and Ukraine align themselves with this statement.</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:49.614893+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>EU Statement in response to the Report of ODIHR Director, Maria Telalian, OSCE Permanent Council No. 1583 - Vienna, 29 October 2026</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/vienna-international-organisations/eu-statement-response-report-odihr-director-maria-telalian-osce-permanent-council-no-1583-vienna-29_en</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>EU Statement in response to the Report of ODIHR Director, Maria Telalian, OSCE Permanent Council No. 1583 - Vienna, 29 October 2026
+- The European Union cordially welcomes ODIHR’s Director, Maria Telalian, back to the Permanent Council and thanks her for her concise report focused on key priorities and core implications.
+- We express EU’s continuous and firm support to ODIHR’s activities, autonomy and mandate for the promotion of democracy, the rule of law and human rights in the OSCE.
+- Russia’s war of aggression against Ukraine remains a devastating toll on human life. We recall that Russia has escalated its large-scale, deliberate and systematic missile and drone attacks against Ukraine’s civilians and civilian infrastructure.
+- In this regard, the EU commends ODIHR’s work on the Ukraine Human Rights Monitoring Initiative and thanks for the 9th Interim Report which documents and confirms Russia’s large-scale, coordinated air strikes on urban areas; unlawful conscription and forced mobilization of Ukrainian citizens into Russia’s armed forces; continuous pattern of physical and psychological abuse, intimidation, and coercion against Ukrainian POWs and detained civilians; suppression of Ukrainian identity in the temporary occupied Ukrainian territories.
+- We thank ODIHR for providing technical and administrative assistance to the expert mission under the Moscow Mechanism invoked in May 2026 on the indoctrination and militarisation of Ukrainian children by Russia. The EU underlines its commitment to ensuring full accountability, according to ODIHR and many other independent actors, Russia’s crimes may amount to war crimes and crimes against humanity.
+- The EU highly values ODIHR’s assistance to the OSCE Swiss Chairpersonship in organising the 2026 Warsaw Human Dimension Conference. As you underlined, Director Telalian, the readiness to engage in dialogue by representatives of participating States, civil society organisations and international stakeholders on key human dimension questions remains central when reviewing the implementation of our shared commitments.
+- In this context, we thank ODIHR as well as the Swiss Chairpersonship for expressing strong condemnation of the reprisals and intimidation of Georgian civil society members attending the Conference by the Georgian authorities and reiterate the importance of ensuring safe participation in OSCE events.
+- Director Telalian, the EU joins you in calling on all participating States to observe their commitments in the human dimension including an agreement to hold a Human Dimension Implementation Meeting annually. We also reaffirm our full trust in Poland as the host country of ODIHR and its events and reject any suggestions to relocate the seat of ODIHR from Warsaw.
+- The EU reiterates its support for ODIHR’s established election observation methodology. We underline ODIHR’s election observation missions provide a comprehensive, objective, and fact-based assessment of the entire electoral cycle, with recommendations serving as catalyst for electoral reform and enhancing public trust in elections in the participating States. In this context, we regret that not all participating States honour their commitment to invite ODIHR to observe the elections.
+- We recognise ODIHR's unique mandate and specialised expertise across the human dimension, including in legislative assistance, democratic governance, human rights and election observation. We encourage close co-operation across the OSCE, while fully respecting ODIHR's institutional autonomy and mandate.
+- The EU stresses that continued budgetary constraints and reductions risk undermining ODIHR's ability to fulfil its mandate. Therefore, we call for a sustainable and adequate budget that preserves ODIHR's operational capacity, expertise and institutional independence.
+- In closing, we wish Director Telalian and her dedicated team every success in their future work.
+Albania, Andorra, Bosnia and Herzegovina, Iceland, Liechtenstein, Republic of Moldova, Monaco, Montenegro, North Macedonia, San Marino, and Ukraine align themselves with this statement.</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:43:55.734694+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>EU Statement on the AOB raised by Montenegro: On Berlin Process Leaders’ Summit, held in Montenegro on October 22, 2026, OSCE Permanent Council No. 1583 - Vienna, 29 October 2026</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/vienna-international-organisations/eu-statement-aob-raised-montenegro-berlin-process-leaders-summit-held-montenegro-october-22-2026_en</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>EU Statement on the AOB raised by Montenegro: On Berlin Process Leaders’ Summit, held in Montenegro on October 22, 2026, OSCE Permanent Council No. 1583 - Vienna, 29 October 2026
+- The European Union and its Member States would like to commend Montenegro for its Chairmanship of the Berlin Process and for hosting last week’s Leaders’ Summit in Miločer.
+- The Berlin Process remains an important platform for strengthening regional cooperation and advancing the European integration of the Western Balkans, complementing the EU enlargement process.
+- The EU sees the integration of the Western Balkans as important for European stability and security, while maintaining a merit-based accession process. We welcome Montenegro’s commitment to regional cooperation and its continued progress on the path towards EU membership.
+- As underlined by the OSCE Secretary General during his remarks at the Summit, strong, resilient, democratic institutions, and public trust in building peaceful and stable societies, are of great importance in order to prevent new crises.
+- We use this opportunity to restate our support for the mandates and activities of the OSCE field operations. The Missions’ support has also been accompanying progress relevant to the European Union path for the countries of the region. They remain important and impartial partners for institutions, civil society and media actors alike.
+Albania, Bosnia and Herzegovina, Georgia, Iceland, Liechtenstein, Republic of Moldova, Montenegro, North Macedonia, Norway, Serbia, and Ukraine align themselves with this statement.</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:01.476552+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Supporting Merchant Shipping</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eunavfor-aspides/supporting-merchant-shipping-6_en</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Breadcrumb EEAS EUNAVFOR ASPIDES Supporting Merchant Shipping Share Facebook LinkedIn X Whatsapp E-mail Gmail Print Typepad Pinterest Blogger Pocket YahooMail Threads Weibo Viadeo Reddit Qzone Netvibes Yammer Tumblr Digg Mastodon BlueSky PRINT Supporting Merchant Shipping 30.10.2026 Press and information team - EUNAVFOR Operation ASPIDES 🇪🇺 EUNAVFOR ASPIDES helps maintain merchant shipping confidence to continue crossing vital yet challenged maritime routes. © European Union, 2026</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:07.282091+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>The EU stands with its partners against threats to global food security</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/senegal/eu-stands-its-partners-against-threats-global-food-security_en</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>The EU stands with its partners against threats to global food security
+War Drives Up Global Prices
+In Dakar, the price of a baguette might seem far removed from the tensions in the Strait of Hormuz, the Red Sea, or the Black Sea. Yet, when major maritime routes are threatened, the costs of grain, energy, fertilizers, and their transport rise globally. This has a direct impact on bakers, households, and—more broadly—food security in regions that rely on imports to meet domestic demand.
+This reality is particularly significant for Senegal, where wheat imports amounted to approximately 175 billion CFA francs in 2025. Any substantial reduction in the global wheat supply leads to an increase in the import bill. The recent debate over the price of bread provides a concrete illustration of this: bakers point to rising costs for flour, transport, diesel, yeast, salt, and electricity. It serves as a reminder of how essential the free movement of goods remains for maintaining purchasing power.
+The war of aggression waged by Russia against Ukraine is a major factor behind these rising costs. Before Russia’s full-scale invasion of Ukraine in February 2022, Ukraine accounted for roughly 10% of global wheat exports, 15–20% of barley exports, and nearly half of the world’s sunflower oil exports. Since then, Russia has intensified its attacks on port and logistics infrastructure in the Black Sea and along the Danube—a route used for approximately 90% of Ukraine’s agricultural exports. By early August, the volume of grain exports had fallen by about 47% compared to the same period the previous year. Storage capacities are also being targeted, which increases the risk of shortages and long-term price volatility.
+Escalating military tensions in the Middle East are also severely disrupting maritime traffic and oil production, with dramatic consequences for global prices and supply chains.
+The El Niño phenomenon constrains domestic agricultural production.
+Compounding the impact of war are the negative effects of the El Niño phenomenon. The World Meteorological Organization has warned of its return, bringing an increased risk of floods, droughts, and extreme heat across Africa. Forecasts suggest the phenomenon could persist until February 2027, potentially ranking among the most intense episodes since 1950. Previous occurrences in 2015–2016 and 2023–2024, combined with the effects of climate change, have already led to poor harvests, livestock losses, rising household debt, and population displacement. For Senegal, this could hinder the efforts toward food sovereignty that have been underway for several years.
+The European Union stands with its African partners.
+In West Africa, the UN estimates that nearly 55 million people are at risk of falling into acute food insecurity due to the combined impact of these crises. The European Union is working alongside its African partners to address these challenges.
+In response to Russia’s actions targeting food corridors, the European Union has established "solidarity lanes," which provide alternative routes for exporting Ukrainian grain via road, rail, and inland waterways. More than 2 billion euros have been mobilized for this purpose. The European Union also reiterates that its sanctions against Russia do not target the trade of agricultural products, food, grain, or fertilizers with third countries. Safeguards and exemptions are specifically in place to preserve global food security. The European Union also acts through diplomatic channels, in coordination with its international partners, to defend the free movement of vessels wherever it is threatened.
+The European Union also supports the expansion of grain storage capacity, as well as emergency responses and long-term resilience initiatives. In 2025, it mobilized 2.1 billion euros to strengthen food security in several regions of the world.
+To develop local production in Senegal and reduce dependence on imports, the European Union promotes local agricultural value chains for crops such as maize, rice, bananas, peanuts, millet, onions, and cashews. In 2025, this support contributed to a record banana harvest—allowing Senegal to suspend imports for three months—as well as an increase in the production of maize and rice. Furthermore, more than 4,000 producers, the majority of whom are women, have been assisted in adopting agroecological practices.
+For decades, the European Union has been actively committed to food security in Africa, and it will continue to support its partners in the face of the challenges that threaten them. Working alongside Senegal, the EU contributes both to climate resilience efforts and to initiatives aimed at preserving peace and the stability of food supplies.
+Ambassadors of the European Union and its 17 Member States represented in Senegal.</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:13.027839+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Interview by the Head of the EU Delegation and EU Special Representative in BiH, Luigi Soreca: "The door to EU membership is wide open for BiH"</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/bosnia-and-herzegovina/interview-head-eu-delegation-and-eu-special-representative-bih-luigi-soreca-door-eu-membership-wide_en</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Interview by the Head of the EU Delegation and EU Special Representative in BiH, Luigi Soreca: "The door to EU membership is wide open for BiH"
+Published by Oslobođenje
+~ As a reminder, the interview with the Head of the EU Delegation and EU Special Representative in BiH Luigi Soreca was conducted before the tragic accident in Brčko, where two members of the Italian Armed Forces and two members of the Italian Military Red Cross were killed in the crash of an Italian helicopter, while 11 people were injured.~
+Oslobođenje: More than two years ago, we received the green light to open EU accession negotiations for Bosnia and Herzegovina, yet ever since, only red lights have been showing—what is holding us back?
+Luigi Soreca: Indeed, that moment when Bosnia and Herzegovina received the green light for accession negotiations was a special one. I remember very clearly the reaction of BiH friends and interlocutors as well as the optimism among colleagues in Brussels.
+Nonetheless, when the green light for accession negotiations was given in March 2024, it came with the expectation that certain achievable steps would be fulfilled. These were clearly communicated at the time. Bosnia and Herzegovina has certainly made progress in fulfilling some of them. For example, in law enforcement cooperation, border security and border management, including the finalisation of the Agreement on Frontex. Nonetheless, certain other steps are still unfulfilled, most notably adopting the Law on Courts and Law on HJPC in line with European standards.
+Bosnia and Herzegovina has also not been able to appoint a Chief Negotiator that can represent the country with one voice. Accession negotiations are an intensely technical, demanding process involving thousands of pages of EU legislation. We need an expert, technically capable interlocutor who can coordinate across institutions and bridge the technical work between BiH and the EU. Every country conducting accession negotiations has a Chief Negotiator. Given the administrative complexity of Bosnia and Herzegovina, having a dedicated structure that can liaise with the EU on technical matters is even more critical.
+As to the question of what is holding BiH back, the requirements for membership of the EU are transparent and clearly communicated. Next week, the European Commission will publish its enlargement reports. Everything that Bosnia and Herzegovina needs to do to become an EU member state is comprehensively outlined in these yearly reports. The pace of movement towards EU membership is determined by the choices made by domestic political actors.
+Our hope, and indeed expectation, is that now the elections have concluded, political focus will return to fulfilling the conditions for progress on the EU path. Every single citizen in Bosnia and Herzegovina, wherever they live in the country, benefits from a closer relationship with the EU. A future in the EU remains the best guarantee of prosperity and stability for Bosnia and Herzegovina.
+Oslobođenje: What can the EU do to assist the citizens of BiH who believe in Brussels? It is clear to you, too, who opposes the EU—is the EU in a position to respond?
+Luigi Soreca: I think it’s important to underline to all citizens – whether they are in favour of EU accession or more sceptical - that the door to EU membership for Bosnia and Herzegovina is very much open. Russia’s full-scale war of aggression against Ukraine has brought home just how important enlarging the EU is for the long-term security of our whole continent. Enlargement is at the top of the EU’s priorities - I continually underline in my discussions with BiH political actors that they should seize this opportunity.
+The EU and its member states remain Bosnia and Herzegovina’s most loyal partner. We are not only the largest investor and provider of assistance, but also the people BiH citizens can most reliably count on in times of need, for example following the catastrophic floods of 2014 and 2024, or during the Covid-19 pandemic. Whether it’s young people taking advantage of educational opportunities through Erasmus+, researchers through Horizon Europe, or creative people through Creative Europe, thousands of BiH citizens understand that cooperation across borders is an essential component of success. We are stronger when we work together.
+We want to deepen that relationship. Tools like the Growth Plan for the Western Balkans were designed to provide many of the benefits of EU accession before membership, supporting convergence and gradual integration through modernised infrastructure, smoother cross-border trade, and lower transaction costs. The transformative power of EU integration is real. When Poland joined, its per capita GDP was less than half the EU average; in twenty years, its economy doubled and it became a magnet for talent. Romania’s real household income per capita grew by 134% between 2004 and 2024.
+These successes could be Bosnia and Herzegovina’s too. Not just economic growth, but knowing that your legal rights are better protected, a stronger fight against corruption, cleaner air and water, and more predictability for everyday life.
+As to the question about what our response should be to those who are opposed, I can only emphasise that EU membership is voluntary. The large majority of BiH citizens want a future in the EU, and the benefits are obvious. While the European Union is very much interested in having Bosnia and Herzegovina as a member because of the historical, cultural and economic ties with the rest of the continent, membership is a sovereign choice, not an imposition.
+What is not optional is alignment with the EU’s legislation and standards. A common framework, respected by every member state, is the only way that a Union of such diverse histories and cultures can work. Without political will to align with this framework, membership will not be possible, no matter how much we might want Bosnia and Herzegovina in the European family. Where political actors choose division and obstruction, they are not hurting Brussels, they are actively denying their own citizens the prosperity, security, and rights they deserve, rights which citizens in the rest of the continent have enjoyed since their countries joined the Union.
+Oslobođenje: Is Bosnia and Herzegovina at risk of losing out on funds from the Growth Plan for the Western Balkans? What can be done to prevent such a scenario?
+Luigi Soreca: Bosnia and Herzegovina is very much at risk of losing out on funds from the Growth Plan for the Western Balkans. Bosnia and Herzegovina was originally allocated €1.08 billion. This allocation was cut last year by €108 million. There is a very real risk that BiH will see its allocation further cut by €373 million at the end of the year. I can tell you that there are other countries in the region that have successfully used the existing opportunities in the Growth Plan. They would be very happy to use these funds.
+The way to avoid cuts is simple - fulfil the necessary legal framework and start implementing the reforms outlined in the Reform Agenda.
+These reforms should not be viewed as administrative technicalities, necessary for receiving EU funds. They have a transformative power of their own, accelerating digitalisation, cleaner energy, reforms to the business climate and other important changes that will make Bosnia and Herzegovina more competitive, more prosperous and more deeply integrated with the European Single Market.
+I think it is important to underline that the model of ‘investment for reforms’ is the model that will be increasingly applied to the large majority of EU spending in candidate countries in the next EU budget cycle 2028-2034. The expectation is that countries that wish to join the European Union, and receive large investment packages to support growth and development, also need to demonstrate commitment to aligning with the EU’s legislation and standards.
+Oslobođenje: The results of the General Elections in BiH have been certified. What is your message to the politicians who will hold office over the next four years?
+Luigi Soreca: My message to the new authorities would be: keep your focus on the long-term future of the country, and have the courage to find negotiated, consensus-driven, mutually beneficial solutions in the interests of BiH citizens.
+In Bosnia and Herzegovina compromise is too often misconstrued as weakness. Voters are frequently encouraged to reward intransigence. The long-term cost of political dysfunction and blockades is paid by citizens in terms of high rates of emigration, toxic air quality, and a lack of investment in key social services like education and healthcare. Real leadership is not demonstrated by an ability to block progress; it is demonstrated by an ability to deliver results.
+The EU path is a framework that will help Bosnia and Herzegovina to overcome many of the longstanding challenges that the country has faced. One of the main reasons that we are so keen to formally open accession negotiations as soon as possible is that it provides a structure to comprehensively discuss how to achieve a better future. The task ahead is to rebuild trust in public institutions and create an economy that delivers for citizens.
+It would be a tragedy for Bosnia and Herzegovina’s citizens if the next four years were again defined by obstruction, and blockades. We remain ready to provide technical advice, partnership, support and financial assistance. But the leadership and vision to make full use of the EU’s offer has to come from domestic actors. The EU is preparing to accept new members in the coming years. Bosnia and Herzegovina can still make up for lost time, but the work must start now.</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:18.794873+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue on the Right to Development</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-right-development_en</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue on the Right to Development
+Mr. Chair,
+I have the honour to speak on behalf of the European Union and its Member States.
+We thank the speakers for their presentations. We fully agree on the importance of the mutually reinforcing nexus between peace, human rights, development, gender equality and the environment outlined in the Special Rapporteur’s report.
+We underline our longstanding commitment to the right to development, which, as an integral part of the universal human rights framework, must be realised in full consistency with the universality, indivisibility, interrelation, interdependence, and mutually reinforcing nature of all human rights, ensuring that civil, cultural, economic, political and social rights are advanced with equal urgency. Its realisation requires placing human beings at the centre, and ensure their active, free and meaningful participation.
+We are also fully committed to implementing the 2030 Agenda, which is our collective roadmap in this regard, and the “Seville Commitment”, which we are working to translate into concrete action, in particular by improving access to financing for development.
+Working to realise the right to development, the EU and its Member States are dedicated to eradicating poverty in all its dimensions, tackling discrimination and inequalities, and ensuring that no one is left behind, both within and beyond the European Union. This remains at the centre of the EU’s international partnerships, as evidenced by the fact that the EU and its Member States are the world’s leading provider of official development assistance, accounting for almost half of all global ODA last year.
+The EU is working alongside partner countries in developing resilient economies aligned with the SDGs and through its Global Gateway strategy promotes investment in infrastructure, green energy, health, transport, trade, education and research for sustainable development around the world. We are committed to ensuring that these projects uphold international human rights norms and standards on the ground.
+In the context of growing challenges to the rules-based international order, it is of utmost importance that approaches to realising the right to development are grounded in international human rights law and reflect the diversity of views expressed by UN Member States. This must also apply to any future negotiation process on a potential legally binding instrument, as any such instrument cannot be effective without broad support. We consider that the existing human rights treaties, mechanisms and bodies provide a solid foundation to address the interlinkages between the right to development and other human rights.
+The EU will continue to constructively engage with all partners to effectively realise the right the development.
+Mr. Special Rapporteur, in line with the Seville Commitment, how can we most effectively close the SDG financing gap through innovative approaches mobilising public and private resources, while ensuring development effectiveness and leaving no one behind?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:24.612883+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote (EoV) before the vote: UN General Assembly 1st Committee: Draft Decision by the Russian Federation on Transparency and confidence-building measures in outer space activities</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-explanation-vote-eov-vote-un-general-assembly-1st-committee-draft-decision-russian-federation_en</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote (EoV) before the vote: UN General Assembly 1st Committee: Draft Decision by the Russian Federation on Transparency and confidence-building measures in outer space activities
+I have the honour to deliver this explanation of vote, before the vote, on behalf of the European Union and its Member States.
+The Candidate Countries North Macedonia, Montenegro*, Ukraine, the Republic of Moldova, Bosnia and Herzegovina* and Georgia align themselves with this statement.
+- Chair, given the importance of building trust in the current geopolitical context and thus avoiding miscalculations or unintended escalation, the EU considers it important that the First Committee addresses the decision on the draft decision proposed by Russia on transparency and confidence-building measures in outer space activities. The annual TCBM resolution has been agreed by consensus for many years at the First Committee. EU Member States joined this consensus.
+- We are also supportive of making resolutions biennial or triennial in an attempt to streamline the work of the First Committee. In the case with the TCBM resolution sponsored by Russia, this text is further informed by the fact that a dedicated body, the Open-Ended Working Group on the Prevention of an Arms Race in all its aspects (OEWG PAROS), is currently mandated to discuss space security matters, including TCBMs.
+- However, against this backdrop, we regret to note that the sponsor of this draft decision has continued a pattern of irresponsible behaviour in the outer space domain, for which we recall the provocative manoeuvring of the Russian military satellite KOSMOS-2612 in proximity to a commercial satellite ICEYE-X36 satellite last weekend as the latest example. Moreover, no explanatory information or messages have been received from Russian authorities about this incident, which runs contrary to the transparency and confidence-building that the current draft decision and its predecessor resolutions in the First Committee purport to promote.
+- On this basis, the European Union cannot support this draft Decision. By abstaining, EU Member States emphasize disapproval of Russia’s irresponsible behaviour in outer space.
+- North Macedonia, Montenegro, Serbia, Albania and Bosnia and Herzegovina continue to be part of the Stabilisation and Association Process.</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:30.353950+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote: UN General Assembly 1st Committee: Before the vote on A/C.1/81/L.69 “Promoting international cooperation on peaceful uses in the context of international security”</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-explanation-vote-un-general-assembly-1st-committee-vote-ac181l69-promoting-international_en</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>EU Explanation of Vote: UN General Assembly 1st Committee: Before the vote on A/C.1/81/L.69 “Promoting international cooperation on peaceful uses in the context of international security”
+Chair,
+I have the honour to deliver this explanation of vote on behalf of the EU and its Member States.
+The Candidate Countries North Macedonia, Montenegro*, Albania*, Ukraine, the Republic of Moldova and Bosnia and Herzegovina*, and the EFTA countries Iceland and Norway, members of the European Economic Area, as well as Australia, Canada, Japan, New Zealand, the Republic of Korea and the United Kingdom, align themselves with this statement.
+Our delegations will vote against draft resolution L.69, submitted to the First Committee by China and entitled “Promoting international cooperation on peaceful uses in the context of international security”. We also call upon other Member States to do so.
+This resolution builds upon resolutions 76/234, 77/96 and 79/80, reinforcing a central message with which we fundamentally disagree. Divergent views and serious concerns have been expressed consistently since the adoption of resolution 76/234 in 2021, including during the informal consultations this year. Several EU Member States took part in the consultations convened by the sponsor, both in Geneva and in New York, and we thank China for organising them. We proposed specific amendments. The concerns expressed are unfortunately insufficiently reflected in the draft text, and on several points this text has moved further away from what we could support.
+Our countries are committed to the fullest possible exchange of equipment, materials and scientific and technological information for peaceful purposes, and back that commitment with resources. We are among the largest contributors to the IAEA Technical Cooperation Programme and to the OPCW's international cooperation activities. We also support partner countries with capacity building for their own export control systems, as required by Security Council resolution 1540.
+We agree with preambular paragraph 6 that development and international security are mutually reinforcing. Our difficulty is that the resolution does not reflect some of the consequence of that statement. It continues to suggest a false dichotomy between peaceful uses and non-proliferation export controls. In fact, such controls serve as the conditions that allow sensitive items to be transferred with confidence. Multilateral export control arrangements set common guidelines and control lists, which give exporting States the assurance they need to supply trusted recipients.
+The multilateral export control arrangements, namely the Australia Group, the Missile Technology Control Regime, the Nuclear Suppliers Group and the Wassenaar Arrangement, together with the Zangger Committee, support the implementation of the NPT, the CWC, the BTWC, and Security Council resolution 1540. Through decades of technical work, they have identified the items, the misuse or unauthorised use of which could contribute to the development of weapons of mass destruction or their means of delivery. Their guidelines and lists facilitate international trade by providing exporting States with the assurance needed to supply sensitive items to trusted recipients. They contribute to international peace and security by preventing the diversion of sensitive materials, equipment, and technology to end-users of concern.
+No reliable evidence, including in the report of the Secretary-General contained in A/77/96, supports the claim that existing export controls are excessive or undue. The expertise built up in the arrangements cannot be recreated from scratch. An attempt to do so within the United Nations would put at risk a system that delivers for international security.
+On specific provisions:
+First, we cannot accept the suggestion in preambular paragraph 18 that non-proliferation arrangements are used to impose undue restrictions or unilateral coercive measures.
+Second, preambular paragraph 20 would apply uniform criteria to decisions taken under the export control arrangements. Licensing decisions, however, are national competence, case by case and risk based.
+Third, OP3 addresses the very instruments through which States implement their non-proliferation obligations, including under resolution 1540. Unlike OP1, it does not specify that it applies “without prejudice to their non-proliferation obligations”. Basic scientific research and information in the public domain are already excluded from control.
+Fourth, OP4 removes “as appropriate” from language agreed in resolution 79/80. It also places further dialogue “within the universal framework of the United Nations” and omits the reference in PP22 to existing mechanisms and arrangements.
+We remain ready to continue this dialogue with all delegations, including the sponsor.
+Thank you.
+- North Macedonia, Montenegro, Albania and Bosnia and Herzegovina continue to be part of the Stabilisation and Association Process.</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:36.565572+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>IOM Standing Committee on Programmes and Finance - EU Statement - Item 3(i) Return and Development</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-geneva/iom-standing-committee-programmes-and-finance-eu-statement-item-3i-return-and-development_en</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>IOM Standing Committee on Programmes and Finance - EU Statement - Item 3(i) Return and Development
+Statement on behalf of the European Union and its Member States
+International Organisation for Migration
+39th Session of the Standing Committee on Programmes and Finance
+29-30 October 2026
+________
+Item 3(i)
+Return and Development
+________
+Geneva, 29 October 2026
+- CHECK AGAINST DELIVERY -
+International Organisation for Migration
+39th Session of the Standing Committee on Programmes and Finance
+29-30 October 2026
+Item 3(i) - Return and Development
+Statement on behalf of the European Union and its Member States
+Chair,
+- The European Union and its Member States thank IOM for the paper and welcome the opportunity to discuss how sustainable reintegration can be better embedded in broader development processes.
+- Sustainable return and reintegration are an integral part of our comprehensive approach to migration governance. We recognise that successful reintegration requires more than short-term individual assistance. It depends on access to economic opportunities, public services and functioning institutions, as well as on the capacities of communities and countries of origin. It should be understood as a process that benefits not only returnees, but also local communities and broader development efforts.
+- The implementation of the EU Pact on Migration and Asylum is further shaping the EU’s comprehensive approach to migration, including effective return and readmission, cooperation with partner countries and sustainable reintegration. In this context, the EU Strategy on Voluntary Return and Reintegration of 2021, the newly adopted Return Regulation, which encompasses both voluntary return and removal, and the European Asylum and Migration Management Strategy, support the implementation of our objectives in this domain.
+- We stress the importance of credible and dignified return policies and effective cooperation with countries of origin on identification, documentation and readmission, which benefits from sustained diplomatic engagement. We encourage IOM, within its mandate, to continue supporting partner countries in strengthening their capacities in border management, identification, civil registration and the issuance of travel documents, as well as information and awareness raising on the risks of irregular migration in countries of origin and transit.
+- We have considerable experience in supporting sustainable reintegration, through both migration-specific programmes and broader development cooperation. At regional level, these include the EU-IOM Joint Initiative for Migrant Protection and Reintegration in Africa and its successor programme, Migrant Protection, Return and Reintegration (MPRR). At national level, the EU supports a wide range of initiatives in Africa and Asia, complemented by individual EU Member States programmes. All these initiatives support returnees from both the EU and third countries, strengthen national reintegration systems and promote socio-economic reintegration.
+- We are at a turning point in our approach to reintegration, with a shifting focus towards building national reintegration systems. The objective is to make our investments more sustainable, built on broad partnerships, and progressively embed reintegration support within national systems and services, reducing long-term dependence on project-based approaches where appropriate, taking account of context, capacities and returnee needs. In the countries where we support reintegration, tangible progress has already been made towards gradually transferring responsibility for reintegration assistance to national authorities. In several countries, the objective is to complete the transition to a national reintegration system by the end of 2027. To achieve these objectives, we count on enhanced cooperation with IOM and its proactive engagement in facilitating this transition.
+- We therefore welcome IOM's emphasis on further strengthening the links between sustainable return and reintegration and national and local development processes. Access to employment, skills development, social protection and public services is essential for sustainable outcomes. Reintegration support should also respond to individual circumstances and vulnerabilities, including through gender-responsive and context-sensitive approaches. Equally important is ensuring that investments benefit both returnees and receiving communities, contributing to social cohesion and local development.
+- We also see significant potential in strengthening cooperation with development actors, including the private sector, development finance institutions and other UN agencies, notably ILO and UNDP, building on their respective comparative advantages.
+- Against this background, we would appreciate IOM's reflections on a key question. How can IOM use its operational presence and expertise in reintegration to further support the transition towards national reintegration systems, so that returnees benefit from existing services and development investments and reintegration outcomes remain sustainable beyond the duration of donor-funded projects in a manner that actively promotes compliance with the obligation to readmit one’s own nationals?
+- We remain committed to working with IOM and partner countries to advance safe, dignified and sustainable return and reintegration, in full respect of fundamental rights and with benefits for returnees and their communities.
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:42.796392+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Israel: Statement by the Spokesperson on the elections</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/israel-statement-spokesperson-elections_en</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+The European Union congratulates the Israeli people on yesterday’s elections, which saw a high voter turnout, reflecting Israel’s vibrant democracy.
+There now begins a period of political negotiations to form the next Israeli government.
+The EU looks forward to engaging with the next government on the basis of our longstanding relationship and commitment to democratic principles and common values, as well as to further advancing people-to-people contacts.
+The EU approach will continue to be based on a frank and open dialogue in view of advancing our bilateral cooperation, addressing all issues of concern and working together to promote regional stability, security, and a just and lasting peace.</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:44:55.362585+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>EU Statement at the Trade Policy Review of the Democratic Republic of Congo, 28 October 2026</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/world-trade-organization-wto/eu-statement-trade-policy-review-democratic-republic-congo-28-october-2026_en</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>EU Statement at the Trade Policy Review of the Democratic Republic of Congo, 28 October 2026
+Madame la Présidente,
+Permettez-moi, tout d’abord, de souhaiter très chaleureusement la bienvenue à la délégation de la République démocratique du Congo, conduite par Son Excellence Monsieur Julien PALUKU KAHONGYA, Ministre du Commerce Extérieur, et mon collègue, Ambassadeur Paul EMPOLE LOSOKO EFAMBE, et son équipe à Genève.
+Nos remerciements vont aussi à l’Ambassadeur S.E. Mr Omar ZNIBER (Morocco) pour ses observations pertinentes, qui offrent un excellent point de départ à notre échange d’aujourd’hui.
+L'Union européenne salue l’examen de la politique commerciale de la République démocratique du Congo et remercie les autorités congolaises ainsi que le Secrétariat de l'OMC pour leurs rapports et pour l'engagement constructif tout au long de ce processus.
+La République démocratique du Congo possède un potentiel économique considérable. Le pays est doté d'immenses ressources naturelles, y compris des matières premières essentielles, et bénéficie d'une position stratégique en Afrique qui lui confère un rôle important dans les chaînes de valeur régionales et mondiales.
+Parallèlement, la RDC continue de faire face à de sérieux défis sécuritaires dans certaines parties de son territoire et reste limitée par d'importantes lacunes au niveau de ses infrastructures. Dans ce contexte l’Union européenne demeure convaincue de l’importance de son partenariat actif avec la RDC en matière d’infrastructure, bien illustré par les investissements dans les corridors de transport, dont le Corridor 6 (section Bangui-Gemena-Akula), la Route Nationale no 1 au Kasaï ainsi que le «Couloir Vert» associé non seulement avec la protection de la biodiversité mais aussi au développement de chaines de valeurs et la stimulation de pôles de développement.
+La République démocratique du Congo bénéficie de l'accord « Tout sauf les armes » (EBA) de l'UE, qui offre un accès hors droits et quotas au marché européen - de plus de 500 millions de consommateurs - pour tous les produits sauf les armes et les munitions. Bien que notre commerce croisse régulièrement, avec un excédent commercial très impressionnant du côté de la RDC (croissance de 61 % des importations de l'UE en 2025), nous souhaitons encourager la République démocratique du Congo, à tirer pleinement parti des opportunités de diversification des exportations offertes par cet arrangement avantageux.
+L'Union européenne considère cet examen comme une opportunité importante d'approfondir le dialogue sur les politiques qui pourraient aider la RDC à construire un environnement commercial et d'investissement plus prévisible, attractif, diversifié et compétitif.
+L'Union européenne prend note des engagements de la RDC, dans un climat difficile, pour mener des réformes économiques et institutionnelles visant à améliorer le milieu des affaires, accroître la prévisibilité réglementaire, renforcer la gouvernance publique et soutenir la diversification économique. Nous encourageons la RDC à poursuivre sur cette voie en simplifiant davantage les procédures administratives, en renforçant la transparence et la cohérence des réglementations, et en améliorant la coordination entre les institutions publiques.
+En outre, l’Union européenne a noté l’engagement de l’État dans la mise en place de plusieurs Zones Économiques Spéciales (ZES) et se tient prête à échanger avec la RDC sur la possibilité de développer d’autres zones dans le cadre du développement des corridors stratégiques.
+L'Union européenne encouragerait également la poursuite des travaux en faveur d'un cadre réglementaire transparent applicable aux minéraux critiques. À cet égard, de nouveaux progrès pourraient être réalisés grâce à la numérisation pour faciliter le commerce, l'administration publique et les opérations commerciales.
+La RDC participe à plusieurs initiatives régionales d'intégration économique, notamment la zone de libre-échange continentale africaine, le Marché commun pour l'Afrique de l'Est et australe, la Communauté d'Afrique de l'Est et la Communauté économique des États centrafricains. L'Union européenne encourage la RDC à rechercher la cohérence dans la mise en œuvre des engagements découlant de ces adhésions. Si ces cadres sont mis en œuvre efficacement, ils pourraient élargir l'accès au marché et soutenir le développement des chaînes de valeur régionales.
+L'UE valorise la contribution de la RDC au renforcement du système de l'OMC. La République démocratique du Congo a officiellement accepté l'Accord de l'OMC sur les subventions à la pêche. Elle fait également partie des membres de l'OMC qui ont coparrainé et soutenu l’Accord sur la facilitation des investissements pour le développement. Dans ce contexte, l'Union européenne salue l'ambition déclarée de la RDC à diversifier son économie au-delà du secteur extractif et de promouvoir une plus grande valeur ajoutée. Nous encourageons également les autorités à favoriser un environnement attractif et propice tant pour les investissements nationaux qu'étrangers. Garantir la transparence, la prévisibilité et l'égalité de traitement des investisseurs soutiendrait davantage les efforts de la RDC pour atteindre ses objectifs de développement intérieur.
+L'UE accueillerait une participation encore plus active de la RDC aux initiatives conjointes de l'OMC, ce qui serait également bénéfique pour l'économie du pays.
+L'UE encourage la RDC à soutenir l'Accord sur le commerce électronique. Cet accord bénéficierait à la RDC, car il répondrait à la croissance rapide des transactions numériques et pourrait aider le gouvernement dans ses efforts pour lever les obstacles qui fragmentent l'environnement commercial.
+Nous invitons la RDC à adhérer à l'arrangement d'arbitrage d'appel intérimaire multipartite (MPIA). La MPIA est une importante solution provisoire qui préserve un système de règlement des différends pleinement opérationnel et contribue à un commerce fondé sur des règles entre les membres qui le souhaitent.
+En outre, malgré les progrès réalisés depuis le précédent examen, les résultats de la RDC en matière de notifications demeurent limités et restent en deçà de ceux de la plupart des PMA. À cet égard, l’Union européenne encourage la RDC à tirer pleinement parti de l’assistance technique et des possibilités de renforcement des capacités offertes par le Secrétariat, et à poursuivre ses efforts en vue d’améliorer le respect de ses obligations en matière de transparence.
+Pour conclure, l’Union Européenne encourage une coordination efficace des priorités de la politique commerciale entre les ministères et agences, ainsi que l'implication des parties prenantes du secteur privé et de la société civile pour que la RDC réalise son ambition de construire une politique commerciale plus inclusive, résiliente et durable.
+L'Union européenne remercie la République démocratique du Congo pour ses réponses et se réjouit de poursuivre un engagement constructif lors de cet examen.</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:45:01.586807+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Media advisory: HR/VP Kallas attends the EU-Canada Summit Montreal 2026</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/media-advisory-hrvp-kallas-attends-eu-canada-summit-montreal-2026_en</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+On 29-30 October, High Representative/Vice-President Kallas will attend the EU-Canada Summit in Montreal.
+On Thursday, the HR/VP will visit the Montreal Vieux Port, followed by a bilateral meeting with Canadian Foreign Minister Anita Anand. HR/VP Kallas will then take part in a fireside chat together with Foreign Minister Anand.
+In the evening, the High Representative will participate in the Ceremony for the signature of the EU-Canada Agreement on the Establishment and the Privileges and Immunities of the Delegation of the European Union in Canada. She will then join the official dinner hosted by Canadian Prime Minister Mark Carney.
+Audiovisual coverage of the High Representative/Vice-President’s engagements will be provided on EBS and X.</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:45:07.509723+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Turkmenistan Delegation Concludes Study Visit to the UK on Methane Emissions Monitoring and Reduction</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/turkmenistan/turkmenistan-delegation-concludes-study-visit-uk-methane-emissions-monitoring-and-reduction_en</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Turkmenistan Delegation Concludes Study Visit to the UK on Methane Emissions Monitoring and Reduction
+During the visit, Turkmen specialists studied advanced British expertise, modern regulatory approaches, and innovative technologies for monitoring, verifying, and reducing methane emissions in the oil and gas sector. The itinerary covered key industrial, scientific, and governmental centers across the country, including London, Aberdeen, Peterhead, and the Teesside region.
+The intensive program included briefings with the UK Department for Energy Security and Net Zero (DESNZ) and other government bodies responsible for climate policy and the implementation of methane reduction measures. Furthermore, the delegation conducted technical visits to the Shell St Fergus gas plant and the CATS gas terminal, operated by Wood Group. Meetings were also held with OEUK (Offshore Energies UK), the leading trade association for the offshore energy sector, and key private companies that shared their expertise in methane abatement. As part of this engagement, the delegation visited the headquarters of Score Group Limited, a company specializing in valve manufacturing and fugitive emissions management. The program also encompassed academic institutions, including the Greenhouse Gas Research Group at Royal Holloway, University of London, a meeting with the management of GHGSat to discuss high-precision satellite monitoring, and a session with experts from BP, who presented their leading practices in methane emissions and flare management.
+European Union
+Special attention during the visit was paid to studying the UK’s experience in applying the standards of the EU Methane Regulation, which governs environmental requirements for fossil fuel imports. For Turkmenistan, gaining familiarity with these regulatory mechanisms holds significant importance in the context of exploring prospects for cooperation in the European energy market and adapting infrastructure to international environmental standards.
+The outcomes of the meetings and the technical expertise gained will be directed toward the practical implementation of methane emission reduction measures, directly contributing to global climate change goals and the fulfillment of the Global Methane Pledge.</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:45:14.282817+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Mayor of Colombo joins British High Commission and Delegation of the European Union to launch joint solar initiative</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/sri-lanka/mayor-colombo-joins-british-high-commission-and-delegation-european-union-launch-joint-solar_en</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Mayor of Colombo joins British High Commission and Delegation of the European Union to launch joint solar initiative
+Colombo, 28 October 2026: Mayor of Colombo Vraie Cally Balthazaar today joined the British High Commission Colombo and the Delegation of the European Union to Sri Lanka to launch their joint solar energy initiative, marking a practical partnership for more sustainable operations.
+The Mayor joined British High Commissioner Andrew Patrick and EU Ambassador-designate Sylvia Hartleif and Deputy High Commissioner Theresa O’Mahony for a ceremonial switch-on and a showcase of the High Commission’s wider greening initiatives.
+Approximately 240 kWp of installed solar capacity across the High Commission’s office estate is projected to generate 365,000 kWh of electricity annually, avoiding an estimated 193 tonnes of carbon dioxide emissions each year.
+British High Commissioner Andrew Patrick, subject to approval:
+“The UK and the European Union share a commitment to a cleaner future and a belief that we achieve more together. This joint solar initiative puts that commitment into practice here in Colombo, generating renewable energy and reducing our environmental footprint. It is a practical partnership we can build on.”
+The solar partnership forms part of a wider effort to reduce the High Commission’s environmental footprint. More efficient cooling, lighting and building systems, alongside solar water heating, offer estimated energy savings of 79,200 kWh a year.
+Other measures include 10,000 litres of rainwater storage capacity and a vehicle fleet that is 25% plug-in hybrid. Waste segregation and safe disposal, including recycling and composting, account for approximately 1.13 tonnes on an annualised basis.
+EU Ambassador-designate Sylvia Hartleif noted:
+“Transitioning to cleaner energy requires ambition, partnership and practical action. This joint solar initiative demonstrates how we can turn our shared climate commitments into tangible results, reducing emissions while making our operations more sustainable. It also reflects the European Union’s broader support for Sri Lanka’s Green Recovery, advancing renewable energy, fostering an inclusive and climate-resilient energy transition, and contributing to greater access to affordable, sustainable energy.”
+The solar partnership forms part of a wider effort to reduce the High Commission’s environmental footprint. More efficient cooling, lighting and building systems, alongside solar water heating, offer estimated energy savings of 79,200 kWh a year.
+Other measures include 10,000 litres of rainwater storage capacity and a vehicle fleet that is 25% plug-in hybrid. Waste segregation and safe disposal, including recycling and composting, account for approximately 1.13 tonnes on an annualised basis.
+Deputy High Commissioner Theresa O’Mahony said:
+“Greening our operations goes beyond installing solar panels. It is also about how we use water, manage waste, travel and care for our surroundings. Bringing these efforts together helps us make sustainability part of everyday life at the High Commission.”</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:45:20.423833+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>EU Film Festival “Stories Without Borders” Successfully Concludes in Osh</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/kyrgyz-republic/eu-film-festival-stories-without-borders-successfully-concludes-osh_en</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>EU Film Festival “Stories Without Borders” Successfully Concludes in Osh
+The festival was officially opened on October 25 by the Ambassador of the European Union to the Kyrgyz Republic, H.E. Rémi Duflot, alongside the Mayor of Osh City and the Rector of OshSU. The opening was marked by a welcome reception and the screening of the animated adventure film "Flow" (Latvia, France, Belgium), which sparked an engaging Q&amp;A session with the audience.
+Over the course of the festival, audiences enjoyed a diverse program that brought together European and local cinema. Highlights included the French drama "Skies of Lebanon," the German music and dance drama "Into the Beat," the Hungarian historical drama "Semmelweis," and the EU-supported Kyrgyz short film "Kochmondor oyundary" (Traditional Games).
+The festival culminated on October 27 at OshSU. The final day featured a dedicated screening for medical students, a musical performance by a Slovenian pianist performing film scores, and an open dialogue with Ambassador Duflot. During the grand closing ceremony, active participants were awarded, and organizers debriefed the event.
+The "Stories Without Borders" festival proved to be a vibrant space for dialogue, celebrating shared human values and demonstrating the power of art to unite cultures.</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:45:26.787182+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Media advisory: High Representative/Vice-President meets UK Secretary of State for Defence</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/eeas/media-advisory-high-representativevice-president-meets-uk-secretary-state-defence_en</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>The European External Action Service (EEAS) is the European Union’s diplomatic service. Since 2011, the EEAS carries out the EU’s Common Foreign and Security Policy to promote peace, prosperity, security, and the interests of Europeans across the globe.
+All over the world, the European External Action Service, in coordination with the European Union institutions, addresses EU foreign policy priorities, including civilian and military planning and crisis response.
+The EU maintains diplomatic relations with nearly all countries in the world and undertakes a range of actions with strategic partners, key international players, and emerging and developing powers.
+Since the first CSDP missions and operations were launched back in 2003, the EU has undertaken over 37 overseas operations, using civilian and military missions and operations in several countries in Europe, Africa and Asia. As of today, there are 20 ongoing EU CSDP missions and operations, including 11 civilian, eight military and one civilian and military initiative.
+Election observation missions (EOMs) provide a comprehensive, independent and impartial assessment of an electoral process according to international standards for democratic elections. The EU is a worldwide recognised credible actor in international election observation. Since 2000, the EU has deployed over 160 EOMs in more than 60 countries.
+Since 2006, the EU High Representative has led diplomatic efforts between the E3/EU+3 (China, France, Germany, Russia, the United Kingdom and the United States) and Iran, which led to the conclusion of the Joint Comprehensive Plan of Action on Iran’s nuclear program (JCPOA) in Vienna on 14 July 2015. The JCPOA is designed to ensure that Iran’s nuclear programme will be exclusively peaceful and provides for the comprehensive lifting of UN, EU and US nuclear-related sanctions.
+All over the world, the EU works to prevent and resolve conflicts, to support resilient democracies, to promote human rights and sustainable development, to fight climate change, and to contribute to a rules-based global order.
+In an increasingly interconnected world, Europe’s security starts abroad. European citizens expect and deserve to live in a safe and stable environment. In the face of increased global instability, the EU needs to take more responsibility for its own security and increase its capacity to act autonomously.
+Crises can affect EU citizens, staff and interests outside of the EU. To protect them, the EU is strengthening its response to security and consular crises. The EEAS Crisis Response Centre contributes to this work.
+In a shifting geopolitical landscape, the EU has remained a strong defender of human rights. New geopolitical rivalries only serve to underline its role as a reliable and stable partner, and a champion of the rules-based international order.
+Equality and non-discrimination are guiding principles of the European Union’s action on the international scene, as enshrined in the EU Treaties. Promoting gender equality, diversity and inclusion is a matter of human rights, but also of peace and security, social justice, and economic progress.
+The EEAS works in close collaboration with the European Commission and the EU Member States, and with the support of the EU Delegations, pursues climate, energy and environmental policy priorities through outreach and dialogue with partner countries, multilateralism and global action. This is known as EU Green Diplomacy.
+In today’s world marked by major geopolitical and economic power shifts, multilateralism is still the most effective means to govern global relations in a way that benefits all. The EU stands committed to a renewed multilateralism fit for the 21st century.
+Migration is a global phenomenon presenting a unique set of challenges while offering substantial benefits to countries of origin and destination as well as migrants. The EU works to ensure that migration takes place in a safe, regular and sustainable manner.
+The EU prioritises development and stability in the wider region and neighbourhood, working in close partnership with its neighbours to the East and South and supporting the reforms required by countries that want to become EU members.
+The European Union together with its Member States is the world’s leading humanitarian donor. New challenges, same principles, humanitarian aid is a key pillar of the EU’s external action and an important part of its ability to project its values globally.
+The European Union, more than ever, needs to work closely with partners to face the global challenges and build together a safer, greener, more prosperous and equal world.
+Cultural diversity is one of the emblems of the EU and its Member States and a tool to strengthen cultural relations beyond our borders, to connect people worldwide, to share values, to improve international relations and to learn from each other’s practice.
+The Global Gateway is a new European strategy to boost smart, clean and secure links in digital, energy and transport sectors and to strengthen health, education and research systems across the world.
+Digital technologies have brought new opportunities into the lives of people around the world. They have also become key competitive parameters that can shift the balance of power. The goal of EU Digital Diplomacy is to secure the EU global role in the digital world, to protect its strategic interests and to promote its dynamic, human-centric regulatory framework for an inclusive digital transformation.
+In its trade relations, the EU promotes a sustainable growth model as defined by the European Green Deal and the European Digital Strategy, which can help the recovery from the COVID-19 economic crisis.
+Since 2015, the EU has significantly improved its capacity to tackle Foreign Information Manipulation and Interference (FIMI), protecting the EU’s democratic processes, security and citizens.
+International days are key moments on the global calendar dedicated to celebrating, raising awareness and taking action on pressing issues that affect us all. From honouring human rights to championing environmental sustainability, these days unite organisations, communities, and individuals worldwide for change - one celebration, one cause, one action at a time.
+Grants can be awarded as donations to third parties that are engaged in external aid activities. Grants are managed by EuropeAid (DEVCO) or DG Near, the EEAS does not manage any grant.
+This is a machine translation provided by the European Commission’s eTranslation service to help you understand this page. Please read the conditions of use.
+On Monday, 2 November, EU High Representative/Vice-President Kaja Kallas will hold a Security and Defence Dialogue with the UK Secretary of State for Defence, the Rt Hon Wes Streeting MP.
+A doorstep will take place ahead of the meeting, at around 09:00 CEST. Media wishing to attend are invited to submit the following details to LAI Sophie-Le.LAI@ec.europa.eu and Ana.FARIA@ec.europa.eu by Thursday, 29 October, at 17:00 CEST:
+Full name
+Date of birth
+Nationality
+ID or passport number
+Media organisation
+Email address and mobile phone number
+Further details will be shared with confirmed participants.</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:45:32.692895+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>STATEMENTS AT THE REGULAR DSB MEETING, 27 OCTOBER 2026</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/world-trade-organization-wto/statements-regular-dsb-meeting-27-october-2026_en</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>STATEMENTS AT THE REGULAR DSB MEETING, 27 OCTOBER 2026
+AGENDA POINT 1: SURVEILLANCE OF IMPLEMENTATION OF RECOMMENDATIONS ADOPTED BY THE DSB
+1.2. UNITED STATES – SECTION 110(5) OF THE US COPYRIGHT ACT: STATUS REPORT BY THE UNITED STATES (WT/DS160/24/ADD.249)
+- We thank the United States for its status report and its statement today.
+- We refer to our previous statements. We would like to resolve this case as soon as possible.
+AGENDA POINT 1: SURVEILLANCE OF IMPLEMENTATION OF RECOMMENDATIONS ADOPTED BY THE DSB
+1.3. EUROPEAN COMMUNITIES – MEASURES AFFECTING THE APPROVAL AND MARKETING OF BIOTECH PRODUCTS: STATUS REPORT BY THE EUROPEAN UNION (WT/DS291/37/ADD.212)
+- We recall that the EU approval system is not covered by the DSB’s recommendations and rulings.
+- On 10 June 2026, the European Commission presented three draft decisions for a vote to the Standing Committee on Plants, Animals, Food and Feed. These decisions included authorising the placing on the market of two GM soybeans () and renewing one authorisation for GM maize (). The votes taken during the meeting resulted in ‘no opinion.’ The draft decisions were presented to the Appeal Committee on 15 July 2026. The vote taken during the meeting for the authorisations and renewal decisions resulted in ‘no opinion’. The Commission has adopted these decisions on 23 September 2026.
+- On 9 September 2026, the European Commission presented the draft decision renewing one authorisation for GM soybean () for a vote to the Standing Committee on Plants, Animals, Food and Feed. The vote taken during the meeting resulted in ‘no opinion.’ The draft decision was presented to the Appeal Committee on 20 October. The vote taken during the meeting resulted in ‘no opinion’. The Commission will proceed with the next steps for regulatory approval.
+AGENDA POINT 1: SURVEILLANCE OF IMPLEMENTATION OF RECOMMENDATIONS ADOPTED BY THE DSB
+1.7 EUROPEAN UNION AND CERTAIN MEMBER STATES – CERTAIN MEASURES CONCERNING PALM OIL AND OIL PALM CROP-BASED BIOFUELS: STATUS REPORT BY THE EUROPEAN UNION (WT/DS600/12/ADD.11)
+- The European Union refers to the status report that it provided for this meeting.
+- The European Union remains ready to engage with Malaysia on the next steps.
+AGENDA POINT 1: SURVEILLANCE OF IMPLEMENTATION OF RECOMMENDATIONS ADOPTED BY THE DSB
+1.8 EUROPEAN UNION – CERTAIN MEASURES CONCERNING PALM OIL AND OIL PALM CROP-BASED BIOFUELS: STATUS REPORT BY THE EUROPEAN UNION (WT/DS593/19/ADD.6)
+- The European Union refers to the status report that it provided for this meeting.
+- The European Union remains ready to engage with Indonesia on the next steps.
+AGENDA POINT 5: APPELLATE BODY APPOINTMENTS
+- The European Union refers to its previous statements on this issue and thanks all Members that have co-sponsored this proposal.
+- Since 11 December 2019, the WTO no longer guarantees access to a binding, two-tier, independent and impartial resolution of trade disputes.
+- A fully functioning WTO dispute settlement system is crucial to support rule-based international trade and a key priority. The present agenda item as well the large number of Members co-sponsoring the present proposal remind us of that every month.
+- The EU remains committed to reforming the dispute settlement system so that it meets the interests of all Members and supports rules-based trade. We welcome the statements of other Members to that effect.
+- That said, despite the substantial work done by Members in dispute settlement reform discussions since MC12, it has now been more than six years that the system is not functioning fully. That work should resume when the conditions are ripe.
+- Against this backdrop, the MPIA is ever more important.
+- In that respect, we refer to the ministerial statement issued by the MPIA participants in Yaoundé (WT/MIN(26)/30), highlighting the role of the MPIA in supporting the rules-based multilateral trading system, welcoming new Members and encouraging other WTO Members to join the MPIA.
+AGENDA POINT 6: STATEMENT BY COLOMBIA AND THE UNITED KINGDOM ON THE OCCASION OF THE TWENTY-FIFTH ANNIVERSARY OF THE ADVISORY CENTRE ON WTO LAW (ACWL)
+- The European Union highly appreciates the contribution of the Advisory Centre on WTO Law to the effective and fair functioning of the WTO’s dispute settlement system, as well as to the WTO more generally.
+- Access to the WTO’s dispute settlement system and, to that end, to high-quality legal advice and representation benefits the entire WTO Membership as it strengthens the rules-based trading system.
+- This is why the work of the ACWL is important. It provides developing countries, including least developed countries, with access to specialist legal capacity. And it plays an important role in capacity building on WTO law in developing-country governments.
+- Before giving the floor back to you Chair, I would like to invite the Netherlands WTO Ambassador, Ms Audrey Goosen, to add a few words on this agenda item as she is currently Chair of the General Assembly of the ACWL.
+Intervention by the Ambassador of the Netherlands
+Good morning everyone,
+- I’m taking the floor as Chair of the ACWL General Assembly and first of all want to warmly congratulate the ACWL and let me add: “still shining after 25 years”!
+- Just like a marriage, the ACWL is the product of two sides coming together to build something meaningful. Two officials from Colombia and the Netherlands had the great foresight that an organization providing accessible, independent, and non-political legal advice to developing and least-developed countries would strengthen the international trading system and benefit all.
+- The WTO is incredibly important to all of us. The World Trade Report of this year shows again what we stand to lose without it.
+- And that is where the ACWL plays such an indispensable role. Because no international rules-based system can survive, if not all participating countries feel they have a genuine opportunity to participate in it and to benefit from it.
+- The ACWL allows developing and least-developed countries to participate in the WTO on a more level playing field with developed countries, thereby ensuring they can benefit from the system.
+- Without this buy-in from all participants, the system will not endure.
+- It is therefore from a point of enlightened self-interest that several WTO members have been proud contributors to ACWL.
+- I see a lot of content recipients of ACWL’s services around the table. I also see important donors and I want to thank the UK, Ireland, Norway, Australia, and New Zealand for their recent contributions allowing for new accessions to the ACWL. I would be remiss if I would not also mention the important contributions made by other members and other contributors over the years: Canada, Denmark, Finland, Germany, Italy, Sweden, Switzerland and Chinese Taipei.
+- With the growing number of countries making use of ACWL’s services, we should not forget the need to finance the services that ACWL provides.
+- Contributing to ACWL is an investment in the sustainability and the credibility of the international trading system.
+- As donor countries gather this week to review Aid for Trade, we cannot think of a better or more worthy example of successful Aid for Trade than the ACWL.
+- Continued donor support is essential to sustaining the important work of the ACWL. I encourage everyone to continue investing in this unique institution. I call on new donors to help cement its future, so we can all be looking forward to celebrate the 50th anniversary of the ACWL in 25 years’ time.
+- Thank you Chair.
+AGENDA POINT 7: UPDATE BY THE DSB CHAIR REGARDING DS REFORM CONSULTATIONS
+- As stated under the previous agenda point, for the European Union, dispute settlement reform remains a matter of fundamental importance for the proper functioning of the rules-based multilateral trading system.
+- The EU remains ready to engage constructively, building on the substantial progress achieved in the discussions following MC12, when the conditions are ripe.
+- On the occasion of its 25th anniversary, we would therefore like to warmly congratulate the ACWL and to wish it continued success in the years to come. The European Union is proud that several of its Member States—namely Germany, the Netherlands, Finland, Ireland, Sweden, Denmark and Italy—are committed members of the ACWL. Their financial contributions and active support are a testament to the EU's broader commitment to ensuring that all WTO Members can effectively exercise their rights and perform their obligations.
+Re Russia/Ukraine
+- The EU reiterates its resolute condemnation of Russia’s war of aggression against Ukraine, which constitutes a manifest violation of the UN Charter, and reaffirms its continued and unwavering support for Ukraine’s independence, sovereignty and territorial integrity within its internationally recognised borders.
+- It also reconfirms the European Union’s unwavering commitment to providing continued political, financial, economic, humanitarian, military and diplomatic support to Ukraine and its people.
+- We underscore the need to reach, as soon as possible, a comprehensive, just, and lasting peace in Ukraine, in full respect of Ukraine’s sovereignty and territorial integrity, based on the principles of the Charter of the United Nations.
+- ([1]) GM soybeans MON 94313 and GMB151 x DAS-44406- 6.
+- ([2]) GM maize MON 87460.
+- ([3]) GM soybean MON 87769.</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:16.558655+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>The European Union supports humanitarian mine action in Thailand</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/thailand/european-union-supports-humanitarian-mine-action-thailand_en</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>The European Union supports humanitarian mine action in Thailand
+In Thailand, the European Union is partnering with the Geneva International Centre for Humanitarian Demining (GICHD) to strengthen the capacity of the Thailand Mine Action Centre (TMAC) in survey and land release activities.
+The European Union is committed to supporting practical, needs-based action that protects civilians and strengthens resilience in communities affected by conflict. In Thailand, our cooperation with TMAC and GICHD will help reinforce national mine action capacity, improve safety and support longer-term stabilisation efforts. In addition to capacity building and sharing of expertise, the European Union will assist TMAC with the provision of selected equipment for humanitarian demining. By working with trusted partners and national authorities, we aim to contribute to safer conditions for affected communities and to sustainable peace and security in the border areas.
+In Cambodia, assistance will focus on land survey and release through innovative techniques, with the aim to enable the safe return of displaced persons and restore access to livelihoods.
+The EU’s wider support programme will also include support for confidence-building processes between Cambodia and Thailand through dialogue initiatives involving relevant stakeholders from both sides.
+This regional engagement reflects the EU’s readiness to work with both countries in a balanced, respectful and impartial manner. The European Union stands ready to act as a neutral partner, promoting practical steps to reduce risks for civilians, helping to rebuild trust between the parties and stability in the affected border areas.
+Download the press release:</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:22.877069+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Foro de Inversiones y Negocios de la UE en Argentina 2026</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/argentina/foro-de-inversiones-y-negocios-de-la-ue-en-argentina-2026_und_en</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Foro de Inversiones y Negocios de la UE en Argentina 2026
+Foro de Inversiones y Negocios de la UE en Argentina 2026
+El Foro de Inversiones y Negocios de la Unión Europea en Argentina 2026 llega a Buenos Aires los días 30 de noviembre y 1 de diciembre de 2026.
+En un momento histórico para las relaciones UE–Argentina, con el Acuerdo de Asociación UE–Mercosur abriendo nuevas oportunidades para el comercio y la inversión, este evento insignia reunirá a líderes de alto nivel del sector público, empresarial y financiero de ambos lados del Atlántico para transformar oportunidades en acciones concretas.
+Cofinanciado por la Unión Europea e implementado por la Cámara de Industria y Comercio Argentino-Alemana (AHK Argentina), al frente del consorcio de Cámaras de Comercio de la UE en Argentina, con el apoyo de la Cancilleria Argentina y de PromArgentina, el Foro contará con la participación de altas autoridades institucionales, paneles temáticos, espacios de matchmaking empresarial y oportunidades exclusivas de networking con actores clave que están definiendo el futuro de la asociación entre la Unión Europea y Argentina.
+El programa puede ser consultado en la web del evento</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:29.303095+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Déclaration de l'UE – Assemblée Générale des Nations Unies 3ème Commission : Dialogue interactif avec l'Expert Indépendant sur la République centrafricaine, M. Aristide Nononsi</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/declaration-de-lue-assemblee-generale-des-nations-unies-3eme-commission-dialogue-interactif-avec_en</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Déclaration de l'UE – Assemblée Générale des Nations Unies 3ème Commission : Dialogue interactif avec l'Expert Indépendant sur la République centrafricaine, M. Aristide Nononsi
+Monsieur le Président,
+J'ai l'honneur de prendre la parole au nom de l'Union européenne et de ses États membres.
+Monsieur l'Expert Indépendant,
+Votre dernier rapport reconnaît des progrès réalisés en République centrafricaine dans les domaines du renforcement des institutions, de la lutte contre l'impunité, ainsi que dans la poursuite du processus électoral lancé en décembre 2025. Nous saluons les efforts déployés par le Gouvernement centrafricain à cet égard et reconnaissons le soutien précieux de la MINUSCA dans la conduite du processus électoral. Nous souhaitons également rappeler l'importance d'un dialogue politique inclusif ainsi que de la protection de l'espace civique.
+Malgré ces efforts et ces progrès vers la stabilité, le rapport souligne que la situation humanitaire et des droits de l'Homme dans le pays demeure fragile. [Votre rapport met en évidence que les femmes, les enfants, les personnes déplacées à l’intérieur du pays, les réfugiés et d’autres groupes vivant dans des situations vulnérables restent particulièrement exposés.] En 2026, l'Union européenne contribue à hauteur de plus de 20 millions d'euros en aide humanitaire, [y compris pour faire face aux conséquences du conflit au Soudan].
+L'Union européenne et ses États membres appellent tous les signataires à mettre pleinement en œuvre l'Accord politique pour la paix et la réconciliation de 2019 et les accords ultérieurs, [notamment ceux d'avril et de novembre 2025,] et à s’engager dans le cadre du programme de désarmement, de démobilisation et de réintégration. Nous saluons le rôle crucial joué par la MINUSCA, aux côtés d'autres organismes des Nations Unies, de partenaires régionaux et internationaux et d'organisations de la société civile, en appui du Gouvernement centrafricain [, dont les institutions assument désormais certaines missions auparavant assurées par la MINUSCA].
+L'UE encourage la République centrafricaine et ses partenaires à mettre en œuvre les recommandations formulées dans votre rapport. Les efforts déployés par le Gouvernement centrafricain pour renforcer les institutions judiciaires, soutenir les mécanismes de justice transitionnelle et promouvoir la réconciliation nationale doivent être poursuivis et consolidés, [afin d’atteindre la stabilité et favoriser une bonne gouvernance.]
+Nous saluons également le travail de la Cour pénale internationale et de la Cour pénale spéciale dans la lutte contre l'impunité. Dans ce contexte, permettez-moi de mentionner le soutien de longue date de l'UE et de ses États membres à la Cour pénale spéciale, y compris à travers un soutien financier et le détachement de juges.
+Monsieur l'Expert Indépendant,
+Quelles mesures prioritaires recommanderiez-vous pour renforcer la capacité de la République centrafricaine à lutter contre l'impunité, en particulier dans le domaine de la justice transitionnelle ?
+Je vous remercie.</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:35.766842+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with Ms Elizabeth Salmón, Special Rapporteur on the situation of human rights in the DPRK</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-ms-elizabeth-salmon-special_en</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with Ms Elizabeth Salmón, Special Rapporteur on the situation of human rights in the DPRK
+Mister President, Excellencies, colleagues,
+I have the honour to speak on behalf of the European Union and its Member States, and I welcome Ms. Nusseibeh to this dialogue
+At this critical juncture, the United Nations needs a Secretary-General that is prepared to defend and promote full respect for the UN Charter and international law, and all three UN pillars equally.
+This is precisely the EU’s approach to the UN’s work.
+On peace and security, the EU actively advances the implementation of key UN mandates through our security and defence missions around the world.
+On sustainable development, we provide close to 50% of all ODA and over one-third of all voluntary contributions to the UN system, safeguarding the SDGs and battling inequality.
+And on human rights, we are committed to protecting and defending all human rights - civil and political, economic, social, and cultural – with equal vigour.
+We are therefore deeply concerned with recent normative attacks on human rights – including on women’s and girls’ full enjoyment of human rights and on gender equality, as well as racial, religious, political, and other forms of discrimination and persecution- and also concerned with the fact that, remarkably, only 1% of the UN system spending is dedicated to human rights mandates, in a clear imbalance between the three UN pillars.
+Against this backdrop, we wish to ask the following questions:
+- First, as Secretary-General, can you commit to protect and to increase the funding of the human rights pillar to allow it to deliver all human rights for people on the ground, as explicitly mandated in the Pact for the Future?
+- Second, safeguarding and promoting gender equality and the full enjoyment of women’s and girls’ rights is explicitly mentioned in both Agenda 2030 and the Pact for the Future, but these rights are being increasingly challenged today, in both the UN context and on the ground. How would you ensure protecting them as Secretary-General and how would you go about re-building a common commitment among all UN MS around them?
+- And third, International humanitarian law is also increasingly violated with impunity in virtually every major conflict today, from Ukraine to Gaza and to Sudan and so many other places , in ways that cause inordinate suffering among civilian populations. As Secretary-General, how do you plan to secure full respect for International Humanitarian Law in all circumstances, to stop its politicization, and to ensure accountability for its gravest violations, including through the International Criminal Court?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:41.947456+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Commission on Human Rights in South Sudan</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-commission-human-rights-south_en</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive dialogue with the Commission on Human Rights in South Sudan
+Chair,
+The European Union thanks the Commission for its valuable work for the people in South Sudan, and for its most recent report. We appreciate South Sudan’s continued cooperation with the Commission. We acknowledge the C5+ Summit of 29 September 2026 and the Chair's commitment to elections on 22 December under a number of clearly stipulated pre-conditions. We also welcome the constitution of a C5 Task Force to monitor progress and provide political oversight. We stress the need to implement the Revitalised Agreement on the Resolution of the Conflict in South Sudan (R-ARCSS).
+At the same time, we share the deep disappointment of many South Sudanese at the continued violations of the ceasefire, widespread human rights abuses and violations, atrocities and war crimes, the open and continuous [MCS1] dismantlement of the peace agreement, unilateral appointments and the lack of any credible preparations for elections. We are concerned with the lack of protection of civilians, denial of humanitarian access and frequent attacks on aid workers. Rampant corruption directly affects the very basis of existence for people in South Sudan and violates their social and economic rights. Living conditions have not improved, but in certain areas worsened, in particular food security. Extremely high level of food insecurity, up to starvation persists.
+The political climate remains tense due to the detention of political prisoners and the ongoing trial against Riek Machar and his right to be tried fairly and without undue delay. The AU’s request – which the EU supports – to consider his release has not been met or addressed, nor has his request for access to legal counsel or visits by family. The lack of commitment to national reconciliation coupled with unresolved grievances leaves little prospect of an improvement of the security situation, but risks further deterioration. This is of grave concern to the EU, given that the regional security situation is becoming increasingly acute, characterised as it is by an increasing interconnection of conflicts. Neither elections nor a change in leadership alone will provide a lasting peace without reconciliation and the provision of basic services to the population.
+Mr Afako,
+What steps can national authorities take to safeguard political participation, agreements on human rights and transitional justice commitments, irrespective of electoral timetable?
+How can we help to safeguard in a post-election setting – in case elections happen – the acquis of the peace agreement, in particular the human rights provisions and transitional justice?
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:48.039679+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Special Envoy of the Secretary-General on Myanmar, Ms. Julie BISHOP, Head of the Independent Investigative Mechanism for Myanmar, Mr. Nicholas KOUMJIAN, Special Rapporteur on</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://www.eeas.europa.eu/delegations/un-new-york/eu-statement-un-general-assembly-3rd-committee-interactive-dialogue-special-envoy-secretary-general_en</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>EU Statement – UN General Assembly 3rd Committee: Interactive Dialogue with the Special Envoy of the Secretary-General on Myanmar, Ms. Julie BISHOP, Head of the Independent Investigative Mechanism for Myanmar, Mr. Nicholas KOUMJIAN, Special Rapporteur on
+Chair,
+I have the honour to speak on behalf of the European Union and its Member States.
+We welcome the Special Rapporteur’s report and thank the speakers for their presentations.
+We reiterate our deep concern over the deteriorating humanitarian and security situation in Myanmar and strongly condemn the ongoing violence and grave human rights violations and abuses. The Myanmar military bears the overwhelming responsibility for the crisis.
+Since 2017, the EU together with the OIC, has led a joint resolution on the “Situation of human rights of Rohingya Muslims and other minorities in Myanmar”. Our priority for this year is to reflect the most recent developments.
+Horrific and systematic violations and abuses of international human rights law and international humanitarian law persist, with recent reports indicating widespread aerial attacks, including on schools, clinics, displacement camps and a market in Rakhine State that reportedly killed more than 50 vendors, customers and other civilians.
+Myanmar must return to a truly pluralist and sincerely inclusive democratic path, respecting the will and aspirations of its people who continue to demonstrate remarkable courage and resilience. The military’s staged elections, that were neither free nor fair and conducted in a climate of violence, repression and exclusion - followed by the rebranding of military rule under a nominally civilian administration - do not confer legitimacy.
+Restricted humanitarian access continues to exacerbate suffering and risks pushing persons in vulnerable situations toward famine and malnutrition, including in Rakhine State. We strongly call on all parties to immediately grant full, safe, and unhindered access for humanitarian actors to deliver life-saving assistance.
+The conditions for the voluntary, safe, dignified, and sustainable return of all refugees and displaced persons remain non-existent and we commend Bangladesh’s generosity in providing shelter and safety to over 1.2 million Rohingya refugees and other minorities.
+We reaffirm our support for the United Nations and ASEAN’s efforts in seeking a peaceful solution, and we encourage the full and effective implementation of the Five-Point Consensus. Close coordination among all relevant actors remains essential to achieving a peaceful and democratic future for Myanmar.
+We urge for justice, accountability, and the full implementation of UNSC resolution 2669. We commend the work of the IIMM and ICC in pursuing accountability, and underline the important role of the ICJ in holding states responsible for the most serious violations of international law..
+Ms. Special Rapporteur, in your proposed priorities you describe that you will seek to document interconnected patterns of exploitation, including illicit financial flows, trafficking and forced labour. Could you further elaborate on the threat coming from such activities?
+Mr. Koumjian, the expected judgement by the ICJ on the Gambia case is one example that underlines the importance of collecting evidence for accountability-purposes. Where do you see the biggest challenges when it comes to delivering on the IIMM’s mandate and how can we collectively ensure that the evidence can be transformed into accountability for perpetrators and justice for victims?
+I thank you, Chair.</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:46:54.160167+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
